--- a/Versão5/SIS/Ontologia_Avac.xlsx
+++ b/Versão5/SIS/Ontologia_Avac.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AVAC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C84568C-3B2F-4161-B149-D37E0B69372D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C18E34-A1F3-4A2F-A48C-F832B071766B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1530,7 +1530,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1588,24 +1588,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="5"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Nova Cond Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="5"/>
-      <name val="Arial Nova Cond Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="5"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="5"/>
       <color rgb="FF000000"/>
@@ -1617,6 +1599,20 @@
       <color theme="1"/>
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="5"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="5"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="24">
@@ -1858,7 +1854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1967,12 +1963,6 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1988,7 +1978,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1997,7 +1987,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2027,20 +2017,11 @@
     <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2048,19 +2029,23 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="69">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2721,6 +2706,14 @@
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3154,58 +3147,58 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>47</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>48</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>49</v>
       </c>
@@ -3213,11 +3206,11 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>50</v>
       </c>
@@ -3225,155 +3218,155 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>56</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>58</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>59</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>63</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46244.684742361111</v>
-      </c>
-      <c r="C18" s="47" t="s">
+        <v>46249.440015509259</v>
+      </c>
+      <c r="C18" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>206</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>208</v>
       </c>
@@ -3381,11 +3374,11 @@
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="45" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>209</v>
       </c>
@@ -3393,55 +3386,55 @@
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Translations in Spanish and English incorporated. Translations must be constantly reviewed</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="45" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="45" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="14" t="s">
         <v>69</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="45" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="14" t="s">
         <v>200</v>
       </c>
@@ -3449,7 +3442,7 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize elements of the BIM project. HVAC.</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="45" t="s">
         <v>205</v>
       </c>
     </row>
@@ -3462,118 +3455,119 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA84"/>
-  <sheetFormatPr defaultColWidth="7.85546875" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="7.84375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="54" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="54" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="90.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="68.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="8.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.42578125" style="54" customWidth="1"/>
-    <col min="26" max="26" width="5.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="88.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="7.85546875" style="54"/>
+    <col min="1" max="1" width="2.3828125" style="57" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.4609375" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.15234375" style="52" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="5.765625" style="52" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.4609375" style="52" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="65.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="50.23046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.53515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12" style="52" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="64.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="7.84375" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="62" customFormat="1" ht="41.65" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="58">
+    <row r="1" spans="1:27" s="63" customFormat="1" ht="30.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="60">
         <v>1</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="61" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="H1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="I1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="K1" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="P1" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="39" t="s">
+      <c r="Q1" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="S1" s="39" t="s">
+      <c r="S1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="39" t="s">
+      <c r="T1" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="39" t="s">
+      <c r="U1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="39" t="s">
+      <c r="V1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="38" t="s">
+      <c r="W1" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="44" t="s">
+      <c r="X1" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="Y1" s="44" t="s">
+      <c r="Y1" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="Z1" s="44" t="s">
+      <c r="Z1" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="AA1" s="45" t="s">
+      <c r="AA1" s="43" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -3582,28 +3576,28 @@
       <c r="C2" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="53" t="s">
         <v>455</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="53" t="s">
         <v>454</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="53" t="s">
         <v>451</v>
       </c>
-      <c r="G2" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="63" t="s">
+      <c r="G2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="37" t="str">
@@ -3622,10 +3616,10 @@
         <f t="shared" ref="O2:O4" si="2">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
         <v>Circuito.Elétrico.de.Ar.Condicionado</v>
       </c>
-      <c r="P2" s="56" t="s">
+      <c r="P2" s="54" t="s">
         <v>271</v>
       </c>
-      <c r="Q2" s="56" t="s">
+      <c r="Q2" s="54" t="s">
         <v>274</v>
       </c>
       <c r="R2" s="32" t="s">
@@ -3646,7 +3640,7 @@
       <c r="V2" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W2" s="57" t="str">
+      <c r="W2" s="55" t="str">
         <f t="shared" ref="W2:W61" si="4">CONCATENATE("Key-AVAC-",A2)</f>
         <v>Key-AVAC-2</v>
       </c>
@@ -3664,8 +3658,8 @@
         <v>Electrical System for Air Conditioning</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="56">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -3674,28 +3668,28 @@
       <c r="C3" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="53" t="s">
         <v>455</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="53" t="s">
         <v>454</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="53" t="s">
         <v>452</v>
       </c>
-      <c r="G3" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="63" t="s">
+      <c r="G3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="37" t="str">
@@ -3714,10 +3708,10 @@
         <f t="shared" si="2"/>
         <v>Circuito.Elétrico.de.Aquecimento</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="Q3" s="56" t="s">
+      <c r="Q3" s="54" t="s">
         <v>275</v>
       </c>
       <c r="R3" s="32" t="s">
@@ -3738,7 +3732,7 @@
       <c r="V3" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W3" s="57" t="str">
+      <c r="W3" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-3</v>
       </c>
@@ -3756,8 +3750,8 @@
         <v>Electrical Heating System</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="59">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="56">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3766,28 +3760,28 @@
       <c r="C4" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="53" t="s">
         <v>455</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="53" t="s">
         <v>454</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="53" t="s">
         <v>453</v>
       </c>
-      <c r="G4" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="63" t="s">
+      <c r="G4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="37" t="str">
@@ -3806,10 +3800,10 @@
         <f t="shared" si="2"/>
         <v>Circuito.Elétrico.de.Exaustão</v>
       </c>
-      <c r="P4" s="56" t="s">
+      <c r="P4" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="Q4" s="56" t="s">
+      <c r="Q4" s="54" t="s">
         <v>276</v>
       </c>
       <c r="R4" s="32" t="s">
@@ -3830,7 +3824,7 @@
       <c r="V4" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W4" s="57" t="str">
+      <c r="W4" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-4</v>
       </c>
@@ -3848,8 +3842,8 @@
         <v>Electrical System for Air Exhaust</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="59">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="56">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -3858,7 +3852,7 @@
       <c r="C5" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -3867,19 +3861,19 @@
       <c r="F5" s="36" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="63" t="s">
+      <c r="G5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="37" t="str">
@@ -3922,7 +3916,7 @@
       <c r="V5" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W5" s="57" t="str">
+      <c r="W5" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-5</v>
       </c>
@@ -3940,8 +3934,8 @@
         <v>Air conditioning distribution system to maintain a range of temperatures in one or more spaces.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="56">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -3950,7 +3944,7 @@
       <c r="C6" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -3959,19 +3953,19 @@
       <c r="F6" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="63" t="s">
+      <c r="G6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="37" t="str">
@@ -4014,7 +4008,7 @@
       <c r="V6" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W6" s="57" t="str">
+      <c r="W6" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-6</v>
       </c>
@@ -4032,8 +4026,8 @@
         <v>Non-potable chilled water, such as that circulated through an evaporator.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="59">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -4042,7 +4036,7 @@
       <c r="C7" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -4051,19 +4045,19 @@
       <c r="F7" s="36" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="63" t="s">
+      <c r="G7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="37" t="str">
@@ -4106,7 +4100,7 @@
       <c r="V7" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W7" s="57" t="str">
+      <c r="W7" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-7</v>
       </c>
@@ -4124,8 +4118,8 @@
         <v>Non-potable water, such as that circulated through a condemner.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="56">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -4134,7 +4128,7 @@
       <c r="C8" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -4143,19 +4137,19 @@
       <c r="F8" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="G8" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="63" t="s">
+      <c r="G8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="37" t="str">
@@ -4198,7 +4192,7 @@
       <c r="V8" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W8" s="57" t="str">
+      <c r="W8" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-8</v>
       </c>
@@ -4216,8 +4210,8 @@
         <v>Compressed air system.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="59">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="56">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -4226,7 +4220,7 @@
       <c r="C9" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -4235,19 +4229,19 @@
       <c r="F9" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="G9" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="63" t="s">
+      <c r="G9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="37" t="str">
@@ -4290,7 +4284,7 @@
       <c r="V9" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W9" s="57" t="str">
+      <c r="W9" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-9</v>
       </c>
@@ -4308,8 +4302,8 @@
         <v>Exhaust air collection system to remove stale or harmful air from one or more spaces.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="59">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="56">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -4318,7 +4312,7 @@
       <c r="C10" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -4327,19 +4321,19 @@
       <c r="F10" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="G10" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="63" t="s">
+      <c r="G10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="37" t="str">
@@ -4382,7 +4376,7 @@
       <c r="V10" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W10" s="57" t="str">
+      <c r="W10" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-10</v>
       </c>
@@ -4400,8 +4394,8 @@
         <v>Water or steam heated from a boiler and circulated through radiators.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="59">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="56">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -4410,7 +4404,7 @@
       <c r="C11" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -4419,19 +4413,19 @@
       <c r="F11" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="G11" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="63" t="s">
+      <c r="G11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="37" t="str">
@@ -4474,7 +4468,7 @@
       <c r="V11" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W11" s="57" t="str">
+      <c r="W11" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-11</v>
       </c>
@@ -4492,8 +4486,8 @@
         <v>Ventilation air distribution system involved in the exchange of air to the outside.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="59">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="56">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -4502,7 +4496,7 @@
       <c r="C12" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -4511,19 +4505,19 @@
       <c r="F12" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="63" t="s">
+      <c r="G12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L12" s="37" t="str">
@@ -4566,7 +4560,7 @@
       <c r="V12" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W12" s="57" t="str">
+      <c r="W12" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-12</v>
       </c>
@@ -4584,8 +4578,8 @@
         <v>A refrigerant distribution system for the purpose of fulfilling all or part of a refrigeration cycle.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="59">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="56">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -4594,7 +4588,7 @@
       <c r="C13" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -4603,19 +4597,19 @@
       <c r="F13" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="G13" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="63" t="s">
+      <c r="G13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="37" t="str">
@@ -4658,7 +4652,7 @@
       <c r="V13" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W13" s="57" t="str">
+      <c r="W13" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-13</v>
       </c>
@@ -4676,8 +4670,8 @@
         <v>Distribution system that forms the intended path for the supply current.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="59">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="56">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -4686,7 +4680,7 @@
       <c r="C14" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D14" s="55" t="s">
+      <c r="D14" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -4695,19 +4689,19 @@
       <c r="F14" s="36" t="s">
         <v>450</v>
       </c>
-      <c r="G14" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="63" t="s">
+      <c r="G14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="37" t="str">
@@ -4750,7 +4744,7 @@
       <c r="V14" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W14" s="57" t="str">
+      <c r="W14" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-14</v>
       </c>
@@ -4768,8 +4762,8 @@
         <v>Distribution system that forms the intended path for the return current.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="59">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="56">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -4778,7 +4772,7 @@
       <c r="C15" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="53" t="s">
         <v>456</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -4787,19 +4781,19 @@
       <c r="F15" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="G15" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="63" t="s">
+      <c r="G15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="37" t="str">
@@ -4842,7 +4836,7 @@
       <c r="V15" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W15" s="57" t="str">
+      <c r="W15" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-15</v>
       </c>
@@ -4860,8 +4854,8 @@
         <v>Vacuum distribution system.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="56">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -4879,19 +4873,19 @@
       <c r="F16" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="63" t="s">
+      <c r="G16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L16" s="37" t="str">
@@ -4934,7 +4928,7 @@
       <c r="V16" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W16" s="57" t="str">
+      <c r="W16" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-16</v>
       </c>
@@ -4952,8 +4946,8 @@
         <v>Duct connection is a junction or transition in the flow distribution system in pipelines.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="59">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="56">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -4971,19 +4965,19 @@
       <c r="F17" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G17" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="63" t="s">
+      <c r="G17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="37" t="str">
@@ -5026,7 +5020,7 @@
       <c r="V17" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W17" s="57" t="str">
+      <c r="W17" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-17</v>
       </c>
@@ -5044,8 +5038,8 @@
         <v>Flexible segments are a continuous nonlinear segment of the duct that can be deformed.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="59">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="56">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -5063,19 +5057,19 @@
       <c r="F18" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="G18" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="63" t="s">
+      <c r="G18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="37" t="str">
@@ -5118,7 +5112,7 @@
       <c r="V18" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W18" s="57" t="str">
+      <c r="W18" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-18</v>
       </c>
@@ -5136,8 +5130,8 @@
         <v>Duct segments are typically used to join two sections of the duct network.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="59">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="56">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -5155,19 +5149,19 @@
       <c r="F19" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="G19" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="63" t="s">
+      <c r="G19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="37" t="str">
@@ -5210,7 +5204,7 @@
       <c r="V19" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W19" s="57" t="str">
+      <c r="W19" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-19</v>
       </c>
@@ -5228,8 +5222,8 @@
         <v>Duct muffler is a device that is usually installed inside distribution system.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="56">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -5247,19 +5241,19 @@
       <c r="F20" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G20" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="63" t="s">
+      <c r="G20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="37" t="str">
@@ -5302,7 +5296,7 @@
       <c r="V20" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W20" s="57" t="str">
+      <c r="W20" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-20</v>
       </c>
@@ -5320,8 +5314,8 @@
         <v>Duct insulator type.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="59">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="56">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -5339,19 +5333,19 @@
       <c r="F21" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="G21" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="63" t="s">
+      <c r="G21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="37" t="str">
@@ -5394,7 +5388,7 @@
       <c r="V21" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W21" s="57" t="str">
+      <c r="W21" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-21</v>
       </c>
@@ -5412,8 +5406,8 @@
         <v>Pipe connection is a junction or transition in the pipe flow distribution system.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="59">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="56">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -5431,19 +5425,19 @@
       <c r="F22" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="G22" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="63" t="s">
+      <c r="G22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L22" s="37" t="str">
@@ -5486,7 +5480,7 @@
       <c r="V22" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W22" s="57" t="str">
+      <c r="W22" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-22</v>
       </c>
@@ -5504,8 +5498,8 @@
         <v>Pipe segments is used to typically join two sections of a plumbing network.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="59">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="56">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -5523,19 +5517,19 @@
       <c r="F23" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="G23" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="63" t="s">
+      <c r="G23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="37" t="str">
@@ -5578,7 +5572,7 @@
       <c r="V23" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W23" s="57" t="str">
+      <c r="W23" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-23</v>
       </c>
@@ -5596,8 +5590,8 @@
         <v>Valve is used in plumbing distribution system for construction services.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="59">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="56">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -5615,19 +5609,19 @@
       <c r="F24" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G24" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="63" t="s">
+      <c r="G24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L24" s="37" t="str">
@@ -5670,7 +5664,7 @@
       <c r="V24" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W24" s="57" t="str">
+      <c r="W24" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-24</v>
       </c>
@@ -5688,8 +5682,8 @@
         <v>Duct terminal, it can be a diffuser or a return mouth.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="59">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="56">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -5707,19 +5701,19 @@
       <c r="F25" s="36" t="s">
         <v>402</v>
       </c>
-      <c r="G25" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="63" t="s">
+      <c r="G25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L25" s="37" t="str">
@@ -5762,7 +5756,7 @@
       <c r="V25" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W25" s="57" t="str">
+      <c r="W25" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-25</v>
       </c>
@@ -5780,8 +5774,8 @@
         <v>Junction box is a compartment where ducts are connected.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="59">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="56">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -5799,19 +5793,19 @@
       <c r="F26" s="36" t="s">
         <v>403</v>
       </c>
-      <c r="G26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="63" t="s">
+      <c r="G26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L26" s="37" t="str">
@@ -5854,7 +5848,7 @@
       <c r="V26" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W26" s="57" t="str">
+      <c r="W26" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-26</v>
       </c>
@@ -5872,8 +5866,8 @@
         <v>Air terminal box is usually part of HVAC duct distribution system.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="56">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -5891,19 +5885,19 @@
       <c r="F27" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="63" t="s">
+      <c r="G27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L27" s="37" t="str">
@@ -5946,7 +5940,7 @@
       <c r="V27" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W27" s="57" t="str">
+      <c r="W27" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-27</v>
       </c>
@@ -5964,8 +5958,8 @@
         <v>A compressor is a device that compresses a fluid normally used in a refrigeration circuit.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="59">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="56">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -5983,19 +5977,19 @@
       <c r="F28" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="G28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="63" t="s">
+      <c r="G28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L28" s="37" t="str">
@@ -6038,7 +6032,7 @@
       <c r="V28" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W28" s="57" t="str">
+      <c r="W28" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-28</v>
       </c>
@@ -6056,8 +6050,8 @@
         <v>A filter is a device used to remove particles or gaseous matter from fluids and gases.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="59">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="56">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -6075,19 +6069,19 @@
       <c r="F29" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="G29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J29" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K29" s="63" t="s">
+      <c r="G29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L29" s="37" t="str">
@@ -6130,7 +6124,7 @@
       <c r="V29" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W29" s="57" t="str">
+      <c r="W29" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-29</v>
       </c>
@@ -6148,8 +6142,8 @@
         <v>Unitary equipment usually combines several components into a single product, such as an air handle.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="59">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="56">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -6167,19 +6161,19 @@
       <c r="F30" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="G30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="63" t="s">
+      <c r="G30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L30" s="37" t="str">
@@ -6222,7 +6216,7 @@
       <c r="V30" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W30" s="57" t="str">
+      <c r="W30" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-30</v>
       </c>
@@ -6240,8 +6234,8 @@
         <v>Bundle of tubes is a device consisting of tubes and bundles of tubes used for heat transfer and containment.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="59">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="56">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -6259,19 +6253,19 @@
       <c r="F31" s="36" t="s">
         <v>345</v>
       </c>
-      <c r="G31" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I31" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J31" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K31" s="63" t="s">
+      <c r="G31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L31" s="37" t="str">
@@ -6314,7 +6308,7 @@
       <c r="V31" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W31" s="57" t="str">
+      <c r="W31" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-31</v>
       </c>
@@ -6332,8 +6326,8 @@
         <v>A boiler is a closed piece of equipment, rated for pressure, in which water or other fluid.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="59">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="56">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -6351,19 +6345,19 @@
       <c r="F32" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="G32" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I32" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K32" s="63" t="s">
+      <c r="G32" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L32" s="37" t="str">
@@ -6406,7 +6400,7 @@
       <c r="V32" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W32" s="57" t="str">
+      <c r="W32" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-32</v>
       </c>
@@ -6424,8 +6418,8 @@
         <v>Generally vertical ducts, used to exhaust gases from equipment such as boilers.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="59">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="56">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -6443,19 +6437,19 @@
       <c r="F33" s="36" t="s">
         <v>347</v>
       </c>
-      <c r="G33" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H33" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K33" s="63" t="s">
+      <c r="G33" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L33" s="37" t="str">
@@ -6498,7 +6492,7 @@
       <c r="V33" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W33" s="57" t="str">
+      <c r="W33" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-33</v>
       </c>
@@ -6516,8 +6510,8 @@
         <v>A device used to remove heat from a liquid through a refrigeration cycle.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="59">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="56">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -6535,19 +6529,19 @@
       <c r="F34" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="G34" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J34" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" s="63" t="s">
+      <c r="G34" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L34" s="37" t="str">
@@ -6590,7 +6584,7 @@
       <c r="V34" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W34" s="57" t="str">
+      <c r="W34" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-34</v>
       </c>
@@ -6608,8 +6602,8 @@
         <v>A device used to dissipate heat, usually by condensing a substance.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="59">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="56">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -6627,19 +6621,19 @@
       <c r="F35" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="G35" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H35" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J35" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K35" s="63" t="s">
+      <c r="G35" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I35" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J35" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L35" s="37" t="str">
@@ -6682,7 +6676,7 @@
       <c r="V35" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W35" s="57" t="str">
+      <c r="W35" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-35</v>
       </c>
@@ -6700,8 +6694,8 @@
         <v>A device in which a refrigerant fluid is vaporized that absorbs heat from the fluid.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="59">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="56">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -6719,19 +6713,19 @@
       <c r="F36" s="36" t="s">
         <v>351</v>
       </c>
-      <c r="G36" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H36" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J36" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K36" s="63" t="s">
+      <c r="G36" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L36" s="37" t="str">
@@ -6774,7 +6768,7 @@
       <c r="V36" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W36" s="57" t="str">
+      <c r="W36" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-36</v>
       </c>
@@ -6792,8 +6786,8 @@
         <v>A device that converts fuel into heat through combustion.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="59">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="56">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -6811,19 +6805,19 @@
       <c r="F37" s="36" t="s">
         <v>350</v>
       </c>
-      <c r="G37" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H37" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J37" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K37" s="63" t="s">
+      <c r="G37" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L37" s="37" t="str">
@@ -6866,7 +6860,7 @@
       <c r="V37" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W37" s="57" t="str">
+      <c r="W37" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-37</v>
       </c>
@@ -6884,8 +6878,8 @@
         <v>Air-to-air heat recovery device uses a countercurrent heat exchanger.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="59">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="56">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -6903,19 +6897,19 @@
       <c r="F38" s="36" t="s">
         <v>352</v>
       </c>
-      <c r="G38" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J38" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K38" s="63" t="s">
+      <c r="G38" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L38" s="37" t="str">
@@ -6958,7 +6952,7 @@
       <c r="V38" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W38" s="57" t="str">
+      <c r="W38" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-38</v>
       </c>
@@ -6976,8 +6970,8 @@
         <v>A device that cools the air by saturating it with water vapor.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="59">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="56">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -6995,19 +6989,19 @@
       <c r="F39" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="G39" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J39" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K39" s="63" t="s">
+      <c r="G39" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L39" s="37" t="str">
@@ -7050,7 +7044,7 @@
       <c r="V39" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W39" s="57" t="str">
+      <c r="W39" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-39</v>
       </c>
@@ -7068,8 +7062,8 @@
         <v>Coil is a device used to provide heat transfer between the unmixed media.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="59">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="56">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -7087,19 +7081,19 @@
       <c r="F40" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="G40" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H40" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I40" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J40" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K40" s="63" t="s">
+      <c r="G40" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L40" s="37" t="str">
@@ -7142,7 +7136,7 @@
       <c r="V40" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W40" s="57" t="str">
+      <c r="W40" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-40</v>
       </c>
@@ -7160,8 +7154,8 @@
         <v>Cooling tower is a device that rejects heat into ambient air by circulating a fluid.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="59">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="56">
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -7179,19 +7173,19 @@
       <c r="F41" s="36" t="s">
         <v>356</v>
       </c>
-      <c r="G41" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H41" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J41" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K41" s="63" t="s">
+      <c r="G41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L41" s="37" t="str">
@@ -7234,7 +7228,7 @@
       <c r="V41" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W41" s="57" t="str">
+      <c r="W41" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-41</v>
       </c>
@@ -7252,8 +7246,8 @@
         <v>Heat exchanger is a device used to provide heat transfer between media.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="59">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="56">
         <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -7271,19 +7265,19 @@
       <c r="F42" s="36" t="s">
         <v>355</v>
       </c>
-      <c r="G42" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H42" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I42" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J42" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K42" s="63" t="s">
+      <c r="G42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L42" s="37" t="str">
@@ -7326,7 +7320,7 @@
       <c r="V42" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W42" s="57" t="str">
+      <c r="W42" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-42</v>
       </c>
@@ -7344,8 +7338,8 @@
         <v>Device that adds moisture to the air.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="59">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="56">
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -7363,19 +7357,19 @@
       <c r="F43" s="36" t="s">
         <v>357</v>
       </c>
-      <c r="G43" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H43" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I43" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J43" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K43" s="63" t="s">
+      <c r="G43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L43" s="37" t="str">
@@ -7418,7 +7412,7 @@
       <c r="V43" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W43" s="57" t="str">
+      <c r="W43" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-43</v>
       </c>
@@ -7436,8 +7430,8 @@
         <v>A fan is a device that transmits mechanical work to a gas.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="59">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="56">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -7455,19 +7449,19 @@
       <c r="F44" s="36" t="s">
         <v>466</v>
       </c>
-      <c r="G44" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I44" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J44" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K44" s="63" t="s">
+      <c r="G44" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J44" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L44" s="37" t="str">
@@ -7510,7 +7504,7 @@
       <c r="V44" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W44" s="57" t="str">
+      <c r="W44" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-44</v>
       </c>
@@ -7528,8 +7522,8 @@
         <v>Space heaters use a combination of natural radiation and/or convection.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="59">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="56">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -7547,19 +7541,19 @@
       <c r="F45" s="36" t="s">
         <v>467</v>
       </c>
-      <c r="G45" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H45" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I45" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J45" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K45" s="63" t="s">
+      <c r="G45" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J45" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K45" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L45" s="37" t="str">
@@ -7602,7 +7596,7 @@
       <c r="V45" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W45" s="57" t="str">
+      <c r="W45" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-45</v>
       </c>
@@ -7620,8 +7614,8 @@
         <v>Heat distribution unit that operates with air circulated by gravity.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="59">
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="56">
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -7639,19 +7633,19 @@
       <c r="F46" s="36" t="s">
         <v>468</v>
       </c>
-      <c r="G46" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H46" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I46" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J46" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K46" s="63" t="s">
+      <c r="G46" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I46" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J46" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K46" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L46" s="37" t="str">
@@ -7694,7 +7688,7 @@
       <c r="V46" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W46" s="57" t="str">
+      <c r="W46" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-46</v>
       </c>
@@ -7712,8 +7706,8 @@
         <v>Heat distribution unit that operates with thermal radiation.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="59">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="56">
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -7731,19 +7725,19 @@
       <c r="F47" s="36" t="s">
         <v>358</v>
       </c>
-      <c r="G47" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H47" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I47" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J47" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K47" s="63" t="s">
+      <c r="G47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K47" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L47" s="37" t="str">
@@ -7786,7 +7780,7 @@
       <c r="V47" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W47" s="57" t="str">
+      <c r="W47" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-47</v>
       </c>
@@ -7804,8 +7798,8 @@
         <v>Damper typically participates in HVAC duct distribution system and is used to control or modulate.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="59">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="56">
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -7823,19 +7817,19 @@
       <c r="F48" s="36" t="s">
         <v>359</v>
       </c>
-      <c r="G48" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H48" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I48" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J48" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K48" s="63" t="s">
+      <c r="G48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L48" s="37" t="str">
@@ -7878,7 +7872,7 @@
       <c r="V48" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W48" s="57" t="str">
+      <c r="W48" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-48</v>
       </c>
@@ -7896,8 +7890,8 @@
         <v>Vibration damper is a device used to minimize the effects of vibration on a structure.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="59">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="56">
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -7915,19 +7909,19 @@
       <c r="F49" s="36" t="s">
         <v>360</v>
       </c>
-      <c r="G49" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H49" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I49" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J49" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K49" s="63" t="s">
+      <c r="G49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K49" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L49" s="37" t="str">
@@ -7970,7 +7964,7 @@
       <c r="V49" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W49" s="57" t="str">
+      <c r="W49" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-49</v>
       </c>
@@ -7988,8 +7982,8 @@
         <v>Vibration isolator is a device used to minimize the transmissibility effects of vibrations.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="59">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="56">
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -8007,19 +8001,19 @@
       <c r="F50" s="36" t="s">
         <v>361</v>
       </c>
-      <c r="G50" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H50" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I50" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J50" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K50" s="63" t="s">
+      <c r="G50" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H50" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I50" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J50" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K50" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L50" s="37" t="str">
@@ -8062,7 +8056,7 @@
       <c r="V50" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W50" s="57" t="str">
+      <c r="W50" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-50</v>
       </c>
@@ -8080,8 +8074,8 @@
         <v>A sensor is a device that measures a physical quantity and converts it into a signal that can be read. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="59">
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="56">
         <v>51</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -8099,19 +8093,19 @@
       <c r="F51" s="36" t="s">
         <v>362</v>
       </c>
-      <c r="G51" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H51" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I51" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J51" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K51" s="63" t="s">
+      <c r="G51" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H51" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I51" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J51" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K51" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L51" s="37" t="str">
@@ -8154,7 +8148,7 @@
       <c r="V51" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W51" s="57" t="str">
+      <c r="W51" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-51</v>
       </c>
@@ -8172,8 +8166,8 @@
         <v>A device that identifies or detects carbon monoxide. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="59">
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="56">
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -8191,19 +8185,19 @@
       <c r="F52" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="G52" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H52" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I52" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J52" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K52" s="63" t="s">
+      <c r="G52" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H52" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I52" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K52" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L52" s="37" t="str">
@@ -8246,7 +8240,7 @@
       <c r="V52" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W52" s="57" t="str">
+      <c r="W52" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-52</v>
       </c>
@@ -8264,8 +8258,8 @@
         <v>A device that identifies or detects carbon dioxide. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="59">
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="56">
         <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -8283,19 +8277,19 @@
       <c r="F53" s="36" t="s">
         <v>364</v>
       </c>
-      <c r="G53" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H53" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I53" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J53" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K53" s="63" t="s">
+      <c r="G53" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J53" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K53" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L53" s="37" t="str">
@@ -8338,7 +8332,7 @@
       <c r="V53" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W53" s="57" t="str">
+      <c r="W53" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-53</v>
       </c>
@@ -8356,8 +8350,8 @@
         <v>A device that detects or detects electrical conductance. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="59">
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="56">
         <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -8375,19 +8369,19 @@
       <c r="F54" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="G54" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H54" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I54" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J54" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K54" s="63" t="s">
+      <c r="G54" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J54" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K54" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L54" s="37" t="str">
@@ -8430,7 +8424,7 @@
       <c r="V54" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W54" s="57" t="str">
+      <c r="W54" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-54</v>
       </c>
@@ -8448,8 +8442,8 @@
         <v>A device that senses or detects contact, such as to detect if a door is closed. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="59">
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="56">
         <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -8467,19 +8461,19 @@
       <c r="F55" s="36" t="s">
         <v>366</v>
       </c>
-      <c r="G55" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H55" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I55" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J55" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K55" s="63" t="s">
+      <c r="G55" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J55" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K55" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L55" s="37" t="str">
@@ -8522,7 +8516,7 @@
       <c r="V55" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W55" s="57" t="str">
+      <c r="W55" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-55</v>
       </c>
@@ -8540,8 +8534,8 @@
         <v>A device that senses or detects the seismic wave and measures the seismic intensity in the event of an earthquake. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="59">
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="56">
         <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -8559,19 +8553,19 @@
       <c r="F56" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="G56" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H56" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I56" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J56" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K56" s="63" t="s">
+      <c r="G56" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J56" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K56" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L56" s="37" t="str">
@@ -8614,7 +8608,7 @@
       <c r="V56" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W56" s="57" t="str">
+      <c r="W56" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-56</v>
       </c>
@@ -8632,8 +8626,8 @@
         <v>Combined detector device (multi-criteria). It can detect the presence of heat, fire and smoke. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="59">
+    <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="56">
         <v>57</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -8651,19 +8645,19 @@
       <c r="F57" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="G57" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H57" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I57" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J57" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K57" s="63" t="s">
+      <c r="G57" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K57" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L57" s="37" t="str">
@@ -8706,7 +8700,7 @@
       <c r="V57" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W57" s="57" t="str">
+      <c r="W57" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-57</v>
       </c>
@@ -8724,8 +8718,8 @@
         <v>A device that identifies or detects flow in a fluid. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="59">
+    <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="56">
         <v>58</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -8743,19 +8737,19 @@
       <c r="F58" s="36" t="s">
         <v>369</v>
       </c>
-      <c r="G58" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H58" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I58" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J58" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K58" s="63" t="s">
+      <c r="G58" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J58" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K58" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L58" s="37" t="str">
@@ -8798,7 +8792,7 @@
       <c r="V58" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W58" s="57" t="str">
+      <c r="W58" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-58</v>
       </c>
@@ -8816,8 +8810,8 @@
         <v>A device that senses or detects foreign objects that interfere with the power grid. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="59">
+    <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="56">
         <v>59</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -8835,19 +8829,19 @@
       <c r="F59" s="36" t="s">
         <v>370</v>
       </c>
-      <c r="G59" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H59" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I59" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J59" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K59" s="63" t="s">
+      <c r="G59" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H59" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I59" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J59" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K59" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L59" s="37" t="str">
@@ -8890,7 +8884,7 @@
       <c r="V59" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W59" s="57" t="str">
+      <c r="W59" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-59</v>
       </c>
@@ -8908,8 +8902,8 @@
         <v>Device that identifies or detects freezing in a window. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="59">
+    <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="56">
         <v>60</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -8927,19 +8921,19 @@
       <c r="F60" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="G60" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H60" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I60" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J60" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K60" s="63" t="s">
+      <c r="G60" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H60" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I60" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J60" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K60" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L60" s="37" t="str">
@@ -8982,7 +8976,7 @@
       <c r="V60" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W60" s="57" t="str">
+      <c r="W60" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-60</v>
       </c>
@@ -9000,8 +8994,8 @@
         <v>A device that detects or detects gas concentration (except CO2). Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="59">
+    <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="56">
         <v>61</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -9019,19 +9013,19 @@
       <c r="F61" s="36" t="s">
         <v>372</v>
       </c>
-      <c r="G61" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H61" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I61" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J61" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K61" s="63" t="s">
+      <c r="G61" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H61" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I61" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J61" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K61" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L61" s="37" t="str">
@@ -9074,7 +9068,7 @@
       <c r="V61" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W61" s="57" t="str">
+      <c r="W61" s="55" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-61</v>
       </c>
@@ -9092,8 +9086,8 @@
         <v>A device that identifies or detects heat. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="59">
+    <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="56">
         <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -9111,19 +9105,19 @@
       <c r="F62" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="G62" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H62" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I62" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J62" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K62" s="63" t="s">
+      <c r="G62" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H62" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I62" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J62" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K62" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L62" s="37" t="str">
@@ -9166,7 +9160,7 @@
       <c r="V62" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W62" s="57" t="str">
+      <c r="W62" s="55" t="str">
         <f t="shared" ref="W62:W84" si="18">CONCATENATE("Key-AVAC-",A62)</f>
         <v>Key-AVAC-62</v>
       </c>
@@ -9184,8 +9178,8 @@
         <v>Device that identifies or detects moisture. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="59">
+    <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="56">
         <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -9203,19 +9197,19 @@
       <c r="F63" s="36" t="s">
         <v>374</v>
       </c>
-      <c r="G63" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H63" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I63" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J63" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K63" s="63" t="s">
+      <c r="G63" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H63" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I63" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J63" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K63" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L63" s="37" t="str">
@@ -9258,7 +9252,7 @@
       <c r="V63" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W63" s="57" t="str">
+      <c r="W63" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-63</v>
       </c>
@@ -9276,8 +9270,8 @@
         <v>A device that reads a label, such as to gain access to a door or elevator. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="59">
+    <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="56">
         <v>64</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -9295,19 +9289,19 @@
       <c r="F64" s="36" t="s">
         <v>375</v>
       </c>
-      <c r="G64" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H64" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I64" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J64" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K64" s="63" t="s">
+      <c r="G64" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H64" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I64" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J64" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K64" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L64" s="37" t="str">
@@ -9350,7 +9344,7 @@
       <c r="V64" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W64" s="57" t="str">
+      <c r="W64" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-64</v>
       </c>
@@ -9368,8 +9362,8 @@
         <v>A device that senses or detects the concentration of ion, such as to measure the hardness of water. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="59">
+    <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="56">
         <v>65</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -9387,19 +9381,19 @@
       <c r="F65" s="36" t="s">
         <v>376</v>
       </c>
-      <c r="G65" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H65" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I65" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J65" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K65" s="63" t="s">
+      <c r="G65" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H65" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I65" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J65" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K65" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L65" s="37" t="str">
@@ -9442,7 +9436,7 @@
       <c r="V65" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W65" s="57" t="str">
+      <c r="W65" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-65</v>
       </c>
@@ -9460,8 +9454,8 @@
         <v>A device that senses or detects the fill level, such as for a tank. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="59">
+    <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="56">
         <v>66</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -9479,19 +9473,19 @@
       <c r="F66" s="36" t="s">
         <v>377</v>
       </c>
-      <c r="G66" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H66" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I66" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J66" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K66" s="63" t="s">
+      <c r="G66" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H66" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I66" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J66" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K66" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L66" s="37" t="str">
@@ -9534,7 +9528,7 @@
       <c r="V66" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W66" s="57" t="str">
+      <c r="W66" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-66</v>
       </c>
@@ -9552,8 +9546,8 @@
         <v>A device that identifies or detects light. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="59">
+    <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="56">
         <v>67</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -9571,19 +9565,19 @@
       <c r="F67" s="36" t="s">
         <v>378</v>
       </c>
-      <c r="G67" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H67" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I67" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J67" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K67" s="63" t="s">
+      <c r="G67" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H67" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I67" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J67" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K67" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L67" s="37" t="str">
@@ -9626,7 +9620,7 @@
       <c r="V67" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W67" s="57" t="str">
+      <c r="W67" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-67</v>
       </c>
@@ -9644,8 +9638,8 @@
         <v>Device that senses or detects moisture. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="59">
+    <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="56">
         <v>68</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -9663,19 +9657,19 @@
       <c r="F68" s="36" t="s">
         <v>379</v>
       </c>
-      <c r="G68" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H68" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I68" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J68" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K68" s="63" t="s">
+      <c r="G68" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H68" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I68" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J68" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K68" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L68" s="37" t="str">
@@ -9718,7 +9712,7 @@
       <c r="V68" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W68" s="57" t="str">
+      <c r="W68" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-68</v>
       </c>
@@ -9736,8 +9730,8 @@
         <v>A device that identifies or detects motion. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="59">
+    <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="56">
         <v>69</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -9755,19 +9749,19 @@
       <c r="F69" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="G69" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H69" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I69" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J69" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K69" s="63" t="s">
+      <c r="G69" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H69" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I69" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J69" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K69" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L69" s="37" t="str">
@@ -9810,7 +9804,7 @@
       <c r="V69" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W69" s="57" t="str">
+      <c r="W69" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-69</v>
       </c>
@@ -9828,8 +9822,8 @@
         <v>Device that detects or detects any obstacles. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="59">
+    <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="56">
         <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -9847,19 +9841,19 @@
       <c r="F70" s="36" t="s">
         <v>381</v>
       </c>
-      <c r="G70" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H70" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I70" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J70" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K70" s="63" t="s">
+      <c r="G70" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H70" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I70" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J70" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K70" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L70" s="37" t="str">
@@ -9902,7 +9896,7 @@
       <c r="V70" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W70" s="57" t="str">
+      <c r="W70" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-70</v>
       </c>
@@ -9920,8 +9914,8 @@
         <v>Device that identifies or detects acidity. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="59">
+    <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="56">
         <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -9939,19 +9933,19 @@
       <c r="F71" s="36" t="s">
         <v>382</v>
       </c>
-      <c r="G71" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H71" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I71" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J71" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K71" s="63" t="s">
+      <c r="G71" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H71" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I71" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J71" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K71" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L71" s="37" t="str">
@@ -9994,7 +9988,7 @@
       <c r="V71" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W71" s="57" t="str">
+      <c r="W71" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-71</v>
       </c>
@@ -10012,8 +10006,8 @@
         <v>Device that senses or senses pressure. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="59">
+    <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="56">
         <v>72</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -10031,19 +10025,19 @@
       <c r="F72" s="36" t="s">
         <v>383</v>
       </c>
-      <c r="G72" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H72" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I72" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J72" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K72" s="63" t="s">
+      <c r="G72" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H72" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I72" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J72" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K72" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L72" s="37" t="str">
@@ -10086,7 +10080,7 @@
       <c r="V72" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W72" s="57" t="str">
+      <c r="W72" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-72</v>
       </c>
@@ -10104,8 +10098,8 @@
         <v>A device that senses or detects radiation. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="59">
+    <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="56">
         <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -10123,19 +10117,19 @@
       <c r="F73" s="36" t="s">
         <v>384</v>
       </c>
-      <c r="G73" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H73" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I73" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J73" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K73" s="63" t="s">
+      <c r="G73" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H73" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I73" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J73" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K73" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L73" s="37" t="str">
@@ -10178,7 +10172,7 @@
       <c r="V73" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W73" s="57" t="str">
+      <c r="W73" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-73</v>
       </c>
@@ -10196,8 +10190,8 @@
         <v>A device that senses or detects atomic decay. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="59">
+    <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="56">
         <v>74</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -10215,19 +10209,19 @@
       <c r="F74" s="36" t="s">
         <v>385</v>
       </c>
-      <c r="G74" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H74" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I74" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J74" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K74" s="63" t="s">
+      <c r="G74" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H74" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I74" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J74" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K74" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L74" s="37" t="str">
@@ -10270,7 +10264,7 @@
       <c r="V74" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W74" s="57" t="str">
+      <c r="W74" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-74</v>
       </c>
@@ -10288,8 +10282,8 @@
         <v>A device that perceives or collects information related to rainfall. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="59">
+    <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="56">
         <v>75</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -10307,19 +10301,19 @@
       <c r="F75" s="36" t="s">
         <v>386</v>
       </c>
-      <c r="G75" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H75" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I75" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J75" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K75" s="63" t="s">
+      <c r="G75" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H75" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I75" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J75" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K75" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L75" s="37" t="str">
@@ -10362,7 +10356,7 @@
       <c r="V75" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W75" s="57" t="str">
+      <c r="W75" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-75</v>
       </c>
@@ -10380,8 +10374,8 @@
         <v>Device that identifies or detects smoke. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="59">
+    <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="56">
         <v>76</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -10399,19 +10393,19 @@
       <c r="F76" s="36" t="s">
         <v>387</v>
       </c>
-      <c r="G76" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H76" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I76" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J76" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K76" s="63" t="s">
+      <c r="G76" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H76" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I76" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J76" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K76" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L76" s="37" t="str">
@@ -10454,7 +10448,7 @@
       <c r="V76" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W76" s="57" t="str">
+      <c r="W76" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-76</v>
       </c>
@@ -10472,8 +10466,8 @@
         <v>A device that perceives or measures the depth of accumulated snow. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="59">
+    <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="56">
         <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -10491,19 +10485,19 @@
       <c r="F77" s="36" t="s">
         <v>388</v>
       </c>
-      <c r="G77" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H77" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I77" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J77" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K77" s="63" t="s">
+      <c r="G77" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H77" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I77" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J77" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K77" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L77" s="37" t="str">
@@ -10546,7 +10540,7 @@
       <c r="V77" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W77" s="57" t="str">
+      <c r="W77" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-77</v>
       </c>
@@ -10564,8 +10558,8 @@
         <v>A device that identifies or detects sound. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="59">
+    <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="56">
         <v>78</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -10583,19 +10577,19 @@
       <c r="F78" s="36" t="s">
         <v>389</v>
       </c>
-      <c r="G78" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H78" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I78" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J78" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K78" s="63" t="s">
+      <c r="G78" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H78" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I78" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J78" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K78" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L78" s="37" t="str">
@@ -10638,7 +10632,7 @@
       <c r="V78" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W78" s="57" t="str">
+      <c r="W78" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-78</v>
       </c>
@@ -10656,8 +10650,8 @@
         <v>Device that identifies or detects temperature. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="59">
+    <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="56">
         <v>79</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -10675,19 +10669,19 @@
       <c r="F79" s="36" t="s">
         <v>390</v>
       </c>
-      <c r="G79" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H79" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I79" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J79" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K79" s="63" t="s">
+      <c r="G79" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I79" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K79" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L79" s="37" t="str">
@@ -10730,7 +10724,7 @@
       <c r="V79" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W79" s="57" t="str">
+      <c r="W79" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-79</v>
       </c>
@@ -10748,8 +10742,8 @@
         <v>A device that is placed at the rear end of the last car of a train acting on a fixed equipment. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="59">
+    <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="56">
         <v>80</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -10767,19 +10761,19 @@
       <c r="F80" s="36" t="s">
         <v>391</v>
       </c>
-      <c r="G80" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H80" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I80" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J80" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K80" s="63" t="s">
+      <c r="G80" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H80" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I80" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J80" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K80" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L80" s="37" t="str">
@@ -10822,7 +10816,7 @@
       <c r="V80" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W80" s="57" t="str">
+      <c r="W80" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-80</v>
       </c>
@@ -10840,8 +10834,8 @@
         <v>A device that detects or detects the position of a blade of an AMV. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="59">
+    <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="56">
         <v>81</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -10859,19 +10853,19 @@
       <c r="F81" s="36" t="s">
         <v>392</v>
       </c>
-      <c r="G81" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H81" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I81" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J81" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K81" s="63" t="s">
+      <c r="G81" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H81" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I81" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J81" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K81" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L81" s="37" t="str">
@@ -10914,7 +10908,7 @@
       <c r="V81" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W81" s="57" t="str">
+      <c r="W81" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-81</v>
       </c>
@@ -10932,8 +10926,8 @@
         <v>A device that senses or detects the passage of a wheel. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="59">
+    <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="56">
         <v>82</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -10951,19 +10945,19 @@
       <c r="F82" s="36" t="s">
         <v>393</v>
       </c>
-      <c r="G82" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H82" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I82" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="J82" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K82" s="63" t="s">
+      <c r="G82" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H82" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I82" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J82" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K82" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L82" s="37" t="str">
@@ -11006,7 +11000,7 @@
       <c r="V82" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W82" s="57" t="str">
+      <c r="W82" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-82</v>
       </c>
@@ -11024,8 +11018,8 @@
         <v>A device that perceives or senses the speed and direction of airflow. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="59">
+    <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="56">
         <v>83</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -11043,19 +11037,19 @@
       <c r="F83" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="G83" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H83" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I83" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J83" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K83" s="63" t="s">
+      <c r="G83" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H83" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I83" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K83" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L83" s="37" t="str">
@@ -11098,7 +11092,7 @@
       <c r="V83" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W83" s="57" t="str">
+      <c r="W83" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-83</v>
       </c>
@@ -11116,8 +11110,8 @@
         <v>HVAC duct accessories.</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="59">
+    <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="56">
         <v>84</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -11135,19 +11129,19 @@
       <c r="F84" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="G84" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H84" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="I84" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="J84" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="K84" s="63" t="s">
+      <c r="G84" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H84" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I84" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J84" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K84" s="58" t="s">
         <v>9</v>
       </c>
       <c r="L84" s="37" t="str">
@@ -11190,7 +11184,7 @@
       <c r="V84" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="W84" s="57" t="str">
+      <c r="W84" s="55" t="str">
         <f t="shared" si="18"/>
         <v>Key-AVAC-84</v>
       </c>
@@ -11210,121 +11204,121 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A84">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:F82 L50:Q82 S50:U82 X50:Y82 E83:E84">
-    <cfRule type="cellIs" dxfId="68" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="38" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="66" priority="2321"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="67" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="65" priority="2321"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4">
-    <cfRule type="duplicateValues" dxfId="64" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F15">
-    <cfRule type="duplicateValues" dxfId="62" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F43 F47:F84">
-    <cfRule type="duplicateValues" dxfId="61" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F17 F83:F84">
-    <cfRule type="duplicateValues" dxfId="60" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F17">
-    <cfRule type="duplicateValues" dxfId="59" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F24">
-    <cfRule type="duplicateValues" dxfId="58" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F26">
-    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
     <cfRule type="duplicateValues" dxfId="53" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F28">
-    <cfRule type="duplicateValues" dxfId="52" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F43">
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F43">
-    <cfRule type="duplicateValues" dxfId="47" priority="49"/>
     <cfRule type="duplicateValues" dxfId="46" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:F46 L44:Q46 S44:U46 X44:Y46 AA44:XFD46">
-    <cfRule type="cellIs" dxfId="45" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:F46">
-    <cfRule type="duplicateValues" dxfId="44" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F49">
-    <cfRule type="duplicateValues" dxfId="34" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="62"/>
     <cfRule type="duplicateValues" dxfId="28" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50:F82">
-    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="37"/>
     <cfRule type="duplicateValues" dxfId="22" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84 F5:F43 F47:F49">
-    <cfRule type="duplicateValues" dxfId="21" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84 F16:F26">
-    <cfRule type="duplicateValues" dxfId="20" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84">
-    <cfRule type="duplicateValues" dxfId="19" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F85:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="18" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2323"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F85:F1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="2326"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2328"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="2329"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2330"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2326"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2328"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2329"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2330"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA5:AA43 AA47:AA84">
-    <cfRule type="cellIs" dxfId="11" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11336,15 +11330,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="1.3046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="15.45" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -11409,7 +11403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -11474,7 +11468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -11541,7 +11535,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11557,15 +11551,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.15234375" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="33">
         <v>0</v>
       </c>
@@ -11588,7 +11582,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="34">
         <v>2</v>
       </c>
@@ -11614,22 +11608,22 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:G1 C2:G2">
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:G1048576">
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11641,33 +11635,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:W4"/>
-  <sheetFormatPr defaultColWidth="64.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="64.3046875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.69140625" customWidth="1"/>
+    <col min="5" max="5" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.84375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="43.42578125" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="63.42578125" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.15234375" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.53515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="43.3828125" customWidth="1"/>
+    <col min="20" max="20" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="63.3828125" customWidth="1"/>
+    <col min="22" max="22" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -11738,32 +11732,32 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>2</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="51" t="s">
         <v>477</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="51" t="s">
+      <c r="D2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="22" t="s">
@@ -11772,179 +11766,179 @@
       <c r="K2" s="23" t="s">
         <v>448</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="39" t="s">
         <v>77</v>
       </c>
       <c r="M2" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="N2" s="41" t="s">
+      <c r="N2" s="39" t="s">
         <v>473</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="P2" s="41" t="s">
+      <c r="P2" s="39" t="s">
         <v>75</v>
       </c>
       <c r="Q2" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="R2" s="42" t="s">
+      <c r="R2" s="40" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="42" t="s">
+      <c r="T2" s="40" t="s">
         <v>9</v>
       </c>
       <c r="U2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="V2" s="42" t="s">
+      <c r="V2" s="40" t="s">
         <v>9</v>
       </c>
       <c r="W2" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="50" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="48" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>3</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="50" t="s">
         <v>446</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="F3" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="42" t="s">
+      <c r="F3" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="40" t="s">
         <v>74</v>
       </c>
       <c r="K3" s="23" t="s">
         <v>480</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="L3" s="40" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="40" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="P3" s="40" t="s">
         <v>9</v>
       </c>
       <c r="Q3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="42" t="s">
+      <c r="R3" s="40" t="s">
         <v>210</v>
       </c>
       <c r="S3" s="25" t="s">
         <v>482</v>
       </c>
-      <c r="T3" s="42" t="s">
+      <c r="T3" s="40" t="s">
         <v>211</v>
       </c>
       <c r="U3" s="25" t="s">
         <v>483</v>
       </c>
-      <c r="V3" s="42" t="s">
+      <c r="V3" s="40" t="s">
         <v>474</v>
       </c>
       <c r="W3" s="25" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="50" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="48" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>4</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="50" t="s">
         <v>447</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="38" t="s">
         <v>477</v>
       </c>
-      <c r="F4" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="42" t="s">
+      <c r="F4" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="40" t="s">
         <v>74</v>
       </c>
       <c r="K4" s="23" t="s">
         <v>481</v>
       </c>
-      <c r="L4" s="42" t="s">
+      <c r="L4" s="40" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="42" t="s">
+      <c r="N4" s="40" t="s">
         <v>9</v>
       </c>
       <c r="O4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="42" t="s">
+      <c r="P4" s="40" t="s">
         <v>9</v>
       </c>
       <c r="Q4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="42" t="s">
+      <c r="R4" s="40" t="s">
         <v>210</v>
       </c>
       <c r="S4" s="25" t="s">
         <v>482</v>
       </c>
-      <c r="T4" s="42" t="s">
+      <c r="T4" s="40" t="s">
         <v>211</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>483</v>
       </c>
-      <c r="V4" s="42" t="s">
+      <c r="V4" s="40" t="s">
         <v>474</v>
       </c>
       <c r="W4" s="25" t="s">
@@ -11954,15 +11948,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B3:B4">
-    <cfRule type="duplicateValues" dxfId="3" priority="2236"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:I2 L3:Q4 V3:XFD4">
-    <cfRule type="cellIs" dxfId="2" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:W2 B3:B4 D3:J4 R2:U4">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+  <conditionalFormatting sqref="V2:W2 R2:U4 B3:B4 D3:J4">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Avac.xlsx
+++ b/Versão5/SIS/Ontologia_Avac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C66BE2B-B6D8-44EF-8168-4F98EA58BD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF25C54-F1C2-4B3D-8C2A-EBCF53503512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -2297,7 +2297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2449,9 +2449,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3993,7 +3990,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46260.402199189812</v>
+        <v>46260.407161921299</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>200</v>
@@ -4129,38 +4126,38 @@
     <col min="30" max="16384" width="7.85546875" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="57" customFormat="1" ht="30.4" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="54">
+    <row r="1" spans="1:29" s="56" customFormat="1" ht="30.4" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="53">
         <v>1</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="54" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="I1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="J1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="55" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="41" t="s">
@@ -4199,7 +4196,7 @@
       <c r="W1" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="X1" s="55" t="s">
+      <c r="X1" s="54" t="s">
         <v>8</v>
       </c>
       <c r="Y1" s="40" t="s">
@@ -4302,13 +4299,13 @@
       <c r="Y2" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="Z2" s="60" t="s">
+      <c r="Z2" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="AB2" s="60" t="s">
+      <c r="AB2" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
@@ -4399,13 +4396,13 @@
       <c r="Y3" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="Z3" s="60" t="s">
+      <c r="Z3" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="AB3" s="60" t="s">
+      <c r="AB3" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
@@ -4496,13 +4493,13 @@
       <c r="Y4" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="Z4" s="60" t="s">
+      <c r="Z4" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="AB4" s="60" t="s">
+      <c r="AB4" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
@@ -4593,13 +4590,13 @@
       <c r="Y5" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z5" s="60" t="s">
+      <c r="Z5" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="AB5" s="60" t="s">
+      <c r="AB5" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
@@ -4690,13 +4687,13 @@
       <c r="Y6" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z6" s="60" t="s">
+      <c r="Z6" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="AB6" s="60" t="s">
+      <c r="AB6" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
@@ -4787,13 +4784,13 @@
       <c r="Y7" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z7" s="60" t="s">
+      <c r="Z7" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="AB7" s="60" t="s">
+      <c r="AB7" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
@@ -4884,13 +4881,13 @@
       <c r="Y8" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z8" s="60" t="s">
+      <c r="Z8" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="AB8" s="60" t="s">
+      <c r="AB8" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
@@ -4981,13 +4978,13 @@
       <c r="Y9" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z9" s="60" t="s">
+      <c r="Z9" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="AB9" s="60" t="s">
+      <c r="AB9" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
@@ -5078,13 +5075,13 @@
       <c r="Y10" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z10" s="60" t="s">
+      <c r="Z10" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="AB10" s="60" t="s">
+      <c r="AB10" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
@@ -5175,13 +5172,13 @@
       <c r="Y11" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z11" s="60" t="s">
+      <c r="Z11" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="AB11" s="60" t="s">
+      <c r="AB11" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
@@ -5272,13 +5269,13 @@
       <c r="Y12" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z12" s="60" t="s">
+      <c r="Z12" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="AB12" s="60" t="s">
+      <c r="AB12" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
@@ -5369,13 +5366,13 @@
       <c r="Y13" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z13" s="60" t="s">
+      <c r="Z13" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="AB13" s="60" t="s">
+      <c r="AB13" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
@@ -5466,13 +5463,13 @@
       <c r="Y14" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z14" s="60" t="s">
+      <c r="Z14" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="AB14" s="60" t="s">
+      <c r="AB14" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
@@ -5563,13 +5560,13 @@
       <c r="Y15" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="Z15" s="60" t="s">
+      <c r="Z15" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="AB15" s="60" t="s">
+      <c r="AB15" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
@@ -5660,13 +5657,13 @@
       <c r="Y16" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="Z16" s="60" t="s">
+      <c r="Z16" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="AB16" s="60" t="s">
+      <c r="AB16" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
@@ -5757,13 +5754,13 @@
       <c r="Y17" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="Z17" s="60" t="s">
+      <c r="Z17" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="AB17" s="60" t="s">
+      <c r="AB17" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
@@ -5854,13 +5851,13 @@
       <c r="Y18" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="Z18" s="60" t="s">
+      <c r="Z18" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="AB18" s="60" t="s">
+      <c r="AB18" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
@@ -5951,13 +5948,13 @@
       <c r="Y19" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="Z19" s="60" t="s">
+      <c r="Z19" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="AB19" s="60" t="s">
+      <c r="AB19" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
@@ -6048,13 +6045,13 @@
       <c r="Y20" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="Z20" s="60" t="s">
+      <c r="Z20" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="AB20" s="60" t="s">
+      <c r="AB20" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
@@ -6145,13 +6142,13 @@
       <c r="Y21" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="Z21" s="60" t="s">
+      <c r="Z21" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="AB21" s="60" t="s">
+      <c r="AB21" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC21" s="30" t="s">
@@ -6242,13 +6239,13 @@
       <c r="Y22" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="Z22" s="60" t="s">
+      <c r="Z22" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="AB22" s="60" t="s">
+      <c r="AB22" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
@@ -6339,13 +6336,13 @@
       <c r="Y23" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="Z23" s="60" t="s">
+      <c r="Z23" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="AB23" s="60" t="s">
+      <c r="AB23" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
@@ -6436,13 +6433,13 @@
       <c r="Y24" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="Z24" s="60" t="s">
+      <c r="Z24" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="AB24" s="60" t="s">
+      <c r="AB24" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
@@ -6533,13 +6530,13 @@
       <c r="Y25" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="Z25" s="60" t="s">
+      <c r="Z25" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="AB25" s="60" t="s">
+      <c r="AB25" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC25" s="30" t="s">
@@ -6630,13 +6627,13 @@
       <c r="Y26" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="Z26" s="60" t="s">
+      <c r="Z26" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="AB26" s="60" t="s">
+      <c r="AB26" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC26" s="30" t="s">
@@ -6727,13 +6724,13 @@
       <c r="Y27" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z27" s="60" t="s">
+      <c r="Z27" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="AB27" s="60" t="s">
+      <c r="AB27" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC27" s="30" t="s">
@@ -6824,13 +6821,13 @@
       <c r="Y28" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z28" s="60" t="s">
+      <c r="Z28" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA28" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="AB28" s="60" t="s">
+      <c r="AB28" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC28" s="30" t="s">
@@ -6921,13 +6918,13 @@
       <c r="Y29" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z29" s="60" t="s">
+      <c r="Z29" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA29" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="AB29" s="60" t="s">
+      <c r="AB29" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC29" s="30" t="s">
@@ -7018,13 +7015,13 @@
       <c r="Y30" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z30" s="60" t="s">
+      <c r="Z30" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="AB30" s="60" t="s">
+      <c r="AB30" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC30" s="30" t="s">
@@ -7115,13 +7112,13 @@
       <c r="Y31" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z31" s="60" t="s">
+      <c r="Z31" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA31" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="AB31" s="60" t="s">
+      <c r="AB31" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC31" s="30" t="s">
@@ -7212,13 +7209,13 @@
       <c r="Y32" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z32" s="60" t="s">
+      <c r="Z32" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA32" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="AB32" s="60" t="s">
+      <c r="AB32" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC32" s="30" t="s">
@@ -7309,13 +7306,13 @@
       <c r="Y33" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z33" s="60" t="s">
+      <c r="Z33" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="AB33" s="60" t="s">
+      <c r="AB33" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC33" s="30" t="s">
@@ -7406,13 +7403,13 @@
       <c r="Y34" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z34" s="60" t="s">
+      <c r="Z34" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="AB34" s="60" t="s">
+      <c r="AB34" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC34" s="30" t="s">
@@ -7503,13 +7500,13 @@
       <c r="Y35" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z35" s="60" t="s">
+      <c r="Z35" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="AB35" s="60" t="s">
+      <c r="AB35" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC35" s="30" t="s">
@@ -7600,13 +7597,13 @@
       <c r="Y36" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z36" s="60" t="s">
+      <c r="Z36" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA36" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="AB36" s="60" t="s">
+      <c r="AB36" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC36" s="30" t="s">
@@ -7697,13 +7694,13 @@
       <c r="Y37" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z37" s="60" t="s">
+      <c r="Z37" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA37" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="AB37" s="60" t="s">
+      <c r="AB37" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC37" s="30" t="s">
@@ -7794,13 +7791,13 @@
       <c r="Y38" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z38" s="60" t="s">
+      <c r="Z38" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA38" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="AB38" s="60" t="s">
+      <c r="AB38" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC38" s="30" t="s">
@@ -7891,13 +7888,13 @@
       <c r="Y39" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z39" s="60" t="s">
+      <c r="Z39" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA39" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="AB39" s="60" t="s">
+      <c r="AB39" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC39" s="30" t="s">
@@ -7988,13 +7985,13 @@
       <c r="Y40" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z40" s="60" t="s">
+      <c r="Z40" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA40" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="AB40" s="60" t="s">
+      <c r="AB40" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC40" s="30" t="s">
@@ -8085,13 +8082,13 @@
       <c r="Y41" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z41" s="60" t="s">
+      <c r="Z41" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA41" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="AB41" s="60" t="s">
+      <c r="AB41" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC41" s="30" t="s">
@@ -8182,13 +8179,13 @@
       <c r="Y42" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z42" s="60" t="s">
+      <c r="Z42" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA42" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AB42" s="60" t="s">
+      <c r="AB42" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC42" s="30" t="s">
@@ -8279,13 +8276,13 @@
       <c r="Y43" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="Z43" s="60" t="s">
+      <c r="Z43" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA43" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB43" s="60" t="s">
+      <c r="AB43" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC43" s="30" t="s">
@@ -8314,10 +8311,10 @@
       <c r="G44" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H44" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I44" s="53" t="s">
+      <c r="H44" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J44" s="52" t="s">
@@ -8376,13 +8373,13 @@
       <c r="Y44" s="30" t="s">
         <v>459</v>
       </c>
-      <c r="Z44" s="60" t="s">
+      <c r="Z44" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA44" s="29" t="s">
         <v>460</v>
       </c>
-      <c r="AB44" s="60" t="s">
+      <c r="AB44" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC44" s="30" t="s">
@@ -8411,10 +8408,10 @@
       <c r="G45" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H45" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I45" s="53" t="s">
+      <c r="H45" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J45" s="52" t="s">
@@ -8473,13 +8470,13 @@
       <c r="Y45" s="30" t="s">
         <v>459</v>
       </c>
-      <c r="Z45" s="60" t="s">
+      <c r="Z45" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA45" s="29" t="s">
         <v>461</v>
       </c>
-      <c r="AB45" s="60" t="s">
+      <c r="AB45" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC45" s="30" t="s">
@@ -8508,10 +8505,10 @@
       <c r="G46" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H46" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I46" s="53" t="s">
+      <c r="H46" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I46" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J46" s="52" t="s">
@@ -8570,13 +8567,13 @@
       <c r="Y46" s="30" t="s">
         <v>459</v>
       </c>
-      <c r="Z46" s="60" t="s">
+      <c r="Z46" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA46" s="29" t="s">
         <v>462</v>
       </c>
-      <c r="AB46" s="60" t="s">
+      <c r="AB46" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC46" s="30" t="s">
@@ -8667,13 +8664,13 @@
       <c r="Y47" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="Z47" s="60" t="s">
+      <c r="Z47" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA47" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="AB47" s="60" t="s">
+      <c r="AB47" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC47" s="30" t="s">
@@ -8764,13 +8761,13 @@
       <c r="Y48" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="Z48" s="60" t="s">
+      <c r="Z48" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA48" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="AB48" s="60" t="s">
+      <c r="AB48" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC48" s="30" t="s">
@@ -8861,13 +8858,13 @@
       <c r="Y49" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="Z49" s="60" t="s">
+      <c r="Z49" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA49" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="AB49" s="60" t="s">
+      <c r="AB49" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC49" s="30" t="s">
@@ -8899,7 +8896,7 @@
       <c r="H50" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="I50" s="53" t="s">
+      <c r="I50" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J50" s="52" t="s">
@@ -8958,13 +8955,13 @@
       <c r="Y50" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z50" s="60" t="s">
+      <c r="Z50" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA50" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="AB50" s="60" t="s">
+      <c r="AB50" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC50" s="30" t="s">
@@ -8993,10 +8990,10 @@
       <c r="G51" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H51" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I51" s="53" t="s">
+      <c r="H51" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I51" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J51" s="52" t="s">
@@ -9055,13 +9052,13 @@
       <c r="Y51" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z51" s="60" t="s">
+      <c r="Z51" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA51" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="AB51" s="60" t="s">
+      <c r="AB51" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC51" s="30" t="s">
@@ -9090,10 +9087,10 @@
       <c r="G52" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H52" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I52" s="53" t="s">
+      <c r="H52" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I52" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J52" s="52" t="s">
@@ -9152,13 +9149,13 @@
       <c r="Y52" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z52" s="60" t="s">
+      <c r="Z52" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA52" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="AB52" s="60" t="s">
+      <c r="AB52" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC52" s="30" t="s">
@@ -9187,10 +9184,10 @@
       <c r="G53" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H53" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I53" s="53" t="s">
+      <c r="H53" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J53" s="52" t="s">
@@ -9249,13 +9246,13 @@
       <c r="Y53" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z53" s="60" t="s">
+      <c r="Z53" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA53" s="29" t="s">
         <v>311</v>
       </c>
-      <c r="AB53" s="60" t="s">
+      <c r="AB53" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC53" s="30" t="s">
@@ -9284,10 +9281,10 @@
       <c r="G54" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I54" s="53" t="s">
+      <c r="H54" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J54" s="52" t="s">
@@ -9346,13 +9343,13 @@
       <c r="Y54" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z54" s="60" t="s">
+      <c r="Z54" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA54" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="AB54" s="60" t="s">
+      <c r="AB54" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC54" s="30" t="s">
@@ -9381,10 +9378,10 @@
       <c r="G55" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H55" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I55" s="53" t="s">
+      <c r="H55" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J55" s="52" t="s">
@@ -9443,13 +9440,13 @@
       <c r="Y55" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z55" s="60" t="s">
+      <c r="Z55" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA55" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="AB55" s="60" t="s">
+      <c r="AB55" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC55" s="30" t="s">
@@ -9478,10 +9475,10 @@
       <c r="G56" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H56" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I56" s="53" t="s">
+      <c r="H56" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J56" s="52" t="s">
@@ -9540,13 +9537,13 @@
       <c r="Y56" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z56" s="60" t="s">
+      <c r="Z56" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA56" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="AB56" s="60" t="s">
+      <c r="AB56" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC56" s="30" t="s">
@@ -9575,10 +9572,10 @@
       <c r="G57" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H57" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I57" s="53" t="s">
+      <c r="H57" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J57" s="52" t="s">
@@ -9637,13 +9634,13 @@
       <c r="Y57" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z57" s="60" t="s">
+      <c r="Z57" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA57" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="AB57" s="60" t="s">
+      <c r="AB57" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC57" s="30" t="s">
@@ -9672,10 +9669,10 @@
       <c r="G58" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H58" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I58" s="53" t="s">
+      <c r="H58" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J58" s="52" t="s">
@@ -9734,13 +9731,13 @@
       <c r="Y58" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z58" s="60" t="s">
+      <c r="Z58" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA58" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="AB58" s="60" t="s">
+      <c r="AB58" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC58" s="30" t="s">
@@ -9769,10 +9766,10 @@
       <c r="G59" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H59" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I59" s="53" t="s">
+      <c r="H59" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I59" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J59" s="52" t="s">
@@ -9831,13 +9828,13 @@
       <c r="Y59" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z59" s="60" t="s">
+      <c r="Z59" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA59" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="AB59" s="60" t="s">
+      <c r="AB59" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC59" s="30" t="s">
@@ -9866,10 +9863,10 @@
       <c r="G60" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H60" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I60" s="53" t="s">
+      <c r="H60" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I60" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J60" s="52" t="s">
@@ -9928,13 +9925,13 @@
       <c r="Y60" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z60" s="60" t="s">
+      <c r="Z60" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA60" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="AB60" s="60" t="s">
+      <c r="AB60" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC60" s="30" t="s">
@@ -9963,10 +9960,10 @@
       <c r="G61" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H61" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I61" s="53" t="s">
+      <c r="H61" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I61" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J61" s="52" t="s">
@@ -10025,13 +10022,13 @@
       <c r="Y61" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z61" s="60" t="s">
+      <c r="Z61" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA61" s="29" t="s">
         <v>319</v>
       </c>
-      <c r="AB61" s="60" t="s">
+      <c r="AB61" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC61" s="30" t="s">
@@ -10060,10 +10057,10 @@
       <c r="G62" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H62" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I62" s="53" t="s">
+      <c r="H62" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I62" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J62" s="52" t="s">
@@ -10122,13 +10119,13 @@
       <c r="Y62" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z62" s="60" t="s">
+      <c r="Z62" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA62" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="AB62" s="60" t="s">
+      <c r="AB62" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC62" s="30" t="s">
@@ -10157,10 +10154,10 @@
       <c r="G63" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H63" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I63" s="53" t="s">
+      <c r="H63" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I63" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J63" s="52" t="s">
@@ -10219,13 +10216,13 @@
       <c r="Y63" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z63" s="60" t="s">
+      <c r="Z63" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA63" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="AB63" s="60" t="s">
+      <c r="AB63" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC63" s="30" t="s">
@@ -10254,10 +10251,10 @@
       <c r="G64" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H64" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I64" s="53" t="s">
+      <c r="H64" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I64" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J64" s="52" t="s">
@@ -10316,13 +10313,13 @@
       <c r="Y64" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z64" s="60" t="s">
+      <c r="Z64" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA64" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="AB64" s="60" t="s">
+      <c r="AB64" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC64" s="30" t="s">
@@ -10351,10 +10348,10 @@
       <c r="G65" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H65" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I65" s="53" t="s">
+      <c r="H65" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I65" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J65" s="52" t="s">
@@ -10413,13 +10410,13 @@
       <c r="Y65" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z65" s="60" t="s">
+      <c r="Z65" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA65" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="AB65" s="60" t="s">
+      <c r="AB65" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC65" s="30" t="s">
@@ -10448,10 +10445,10 @@
       <c r="G66" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H66" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I66" s="53" t="s">
+      <c r="H66" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I66" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J66" s="52" t="s">
@@ -10510,13 +10507,13 @@
       <c r="Y66" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z66" s="60" t="s">
+      <c r="Z66" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA66" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="AB66" s="60" t="s">
+      <c r="AB66" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC66" s="30" t="s">
@@ -10545,10 +10542,10 @@
       <c r="G67" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H67" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I67" s="53" t="s">
+      <c r="H67" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I67" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J67" s="52" t="s">
@@ -10607,13 +10604,13 @@
       <c r="Y67" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z67" s="60" t="s">
+      <c r="Z67" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA67" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="AB67" s="60" t="s">
+      <c r="AB67" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC67" s="30" t="s">
@@ -10642,10 +10639,10 @@
       <c r="G68" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H68" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I68" s="53" t="s">
+      <c r="H68" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I68" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J68" s="52" t="s">
@@ -10704,13 +10701,13 @@
       <c r="Y68" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z68" s="60" t="s">
+      <c r="Z68" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA68" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="AB68" s="60" t="s">
+      <c r="AB68" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC68" s="30" t="s">
@@ -10739,10 +10736,10 @@
       <c r="G69" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H69" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I69" s="53" t="s">
+      <c r="H69" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I69" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J69" s="52" t="s">
@@ -10801,13 +10798,13 @@
       <c r="Y69" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z69" s="60" t="s">
+      <c r="Z69" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA69" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="AB69" s="60" t="s">
+      <c r="AB69" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC69" s="30" t="s">
@@ -10836,10 +10833,10 @@
       <c r="G70" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H70" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I70" s="53" t="s">
+      <c r="H70" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I70" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J70" s="52" t="s">
@@ -10898,13 +10895,13 @@
       <c r="Y70" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z70" s="60" t="s">
+      <c r="Z70" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA70" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="AB70" s="60" t="s">
+      <c r="AB70" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC70" s="30" t="s">
@@ -10933,10 +10930,10 @@
       <c r="G71" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H71" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I71" s="53" t="s">
+      <c r="H71" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I71" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J71" s="52" t="s">
@@ -10995,13 +10992,13 @@
       <c r="Y71" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z71" s="60" t="s">
+      <c r="Z71" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA71" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="AB71" s="60" t="s">
+      <c r="AB71" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC71" s="30" t="s">
@@ -11030,10 +11027,10 @@
       <c r="G72" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H72" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I72" s="53" t="s">
+      <c r="H72" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I72" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J72" s="52" t="s">
@@ -11092,13 +11089,13 @@
       <c r="Y72" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z72" s="60" t="s">
+      <c r="Z72" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA72" s="29" t="s">
         <v>330</v>
       </c>
-      <c r="AB72" s="60" t="s">
+      <c r="AB72" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC72" s="30" t="s">
@@ -11127,10 +11124,10 @@
       <c r="G73" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H73" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I73" s="53" t="s">
+      <c r="H73" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I73" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J73" s="52" t="s">
@@ -11189,13 +11186,13 @@
       <c r="Y73" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z73" s="60" t="s">
+      <c r="Z73" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA73" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="AB73" s="60" t="s">
+      <c r="AB73" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC73" s="30" t="s">
@@ -11224,10 +11221,10 @@
       <c r="G74" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H74" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I74" s="53" t="s">
+      <c r="H74" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I74" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J74" s="52" t="s">
@@ -11286,13 +11283,13 @@
       <c r="Y74" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z74" s="60" t="s">
+      <c r="Z74" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA74" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="AB74" s="60" t="s">
+      <c r="AB74" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC74" s="30" t="s">
@@ -11321,10 +11318,10 @@
       <c r="G75" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H75" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I75" s="53" t="s">
+      <c r="H75" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I75" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J75" s="52" t="s">
@@ -11383,13 +11380,13 @@
       <c r="Y75" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z75" s="60" t="s">
+      <c r="Z75" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA75" s="29" t="s">
         <v>333</v>
       </c>
-      <c r="AB75" s="60" t="s">
+      <c r="AB75" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC75" s="30" t="s">
@@ -11418,10 +11415,10 @@
       <c r="G76" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H76" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I76" s="53" t="s">
+      <c r="H76" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I76" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J76" s="52" t="s">
@@ -11480,13 +11477,13 @@
       <c r="Y76" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z76" s="60" t="s">
+      <c r="Z76" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA76" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="AB76" s="60" t="s">
+      <c r="AB76" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC76" s="30" t="s">
@@ -11515,10 +11512,10 @@
       <c r="G77" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H77" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I77" s="53" t="s">
+      <c r="H77" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I77" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J77" s="52" t="s">
@@ -11577,13 +11574,13 @@
       <c r="Y77" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z77" s="60" t="s">
+      <c r="Z77" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA77" s="29" t="s">
         <v>335</v>
       </c>
-      <c r="AB77" s="60" t="s">
+      <c r="AB77" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC77" s="30" t="s">
@@ -11612,10 +11609,10 @@
       <c r="G78" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H78" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I78" s="53" t="s">
+      <c r="H78" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I78" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J78" s="52" t="s">
@@ -11674,13 +11671,13 @@
       <c r="Y78" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z78" s="60" t="s">
+      <c r="Z78" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA78" s="29" t="s">
         <v>336</v>
       </c>
-      <c r="AB78" s="60" t="s">
+      <c r="AB78" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC78" s="30" t="s">
@@ -11709,10 +11706,10 @@
       <c r="G79" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H79" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I79" s="53" t="s">
+      <c r="H79" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I79" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J79" s="52" t="s">
@@ -11771,13 +11768,13 @@
       <c r="Y79" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z79" s="60" t="s">
+      <c r="Z79" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA79" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="AB79" s="60" t="s">
+      <c r="AB79" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC79" s="30" t="s">
@@ -11806,10 +11803,10 @@
       <c r="G80" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H80" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I80" s="53" t="s">
+      <c r="H80" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I80" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J80" s="52" t="s">
@@ -11868,13 +11865,13 @@
       <c r="Y80" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z80" s="60" t="s">
+      <c r="Z80" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA80" s="29" t="s">
         <v>338</v>
       </c>
-      <c r="AB80" s="60" t="s">
+      <c r="AB80" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC80" s="30" t="s">
@@ -11903,10 +11900,10 @@
       <c r="G81" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H81" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I81" s="53" t="s">
+      <c r="H81" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I81" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J81" s="52" t="s">
@@ -11965,13 +11962,13 @@
       <c r="Y81" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z81" s="60" t="s">
+      <c r="Z81" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA81" s="29" t="s">
         <v>339</v>
       </c>
-      <c r="AB81" s="60" t="s">
+      <c r="AB81" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC81" s="30" t="s">
@@ -12000,10 +11997,10 @@
       <c r="G82" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H82" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="I82" s="53" t="s">
+      <c r="H82" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I82" s="52" t="s">
         <v>9</v>
       </c>
       <c r="J82" s="52" t="s">
@@ -12062,13 +12059,13 @@
       <c r="Y82" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="Z82" s="60" t="s">
+      <c r="Z82" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA82" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="AB82" s="60" t="s">
+      <c r="AB82" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC82" s="30" t="s">
@@ -12159,13 +12156,13 @@
       <c r="Y83" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="Z83" s="60" t="s">
+      <c r="Z83" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA83" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="AB83" s="60" t="s">
+      <c r="AB83" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC83" s="30" t="s">
@@ -12256,36 +12253,36 @@
       <c r="Y84" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="Z84" s="60" t="s">
+      <c r="Z84" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AA84" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="AB84" s="60" t="s">
+      <c r="AB84" s="59" t="s">
         <v>9</v>
       </c>
       <c r="AC84" s="30" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="85" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="50">
         <v>85</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C85" s="62" t="s">
+      <c r="C85" s="61" t="s">
         <v>560</v>
       </c>
-      <c r="D85" s="62" t="s">
+      <c r="D85" s="61" t="s">
         <v>561</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="E85" s="61" t="s">
         <v>562</v>
       </c>
-      <c r="F85" s="62" t="s">
+      <c r="F85" s="61" t="s">
         <v>563</v>
       </c>
       <c r="G85" s="52" t="s">
@@ -12322,11 +12319,11 @@
       <c r="P85" s="30" t="s">
         <v>564</v>
       </c>
-      <c r="Q85" s="58" t="str">
+      <c r="Q85" s="57" t="str">
         <f t="shared" ref="Q85:Q87" si="21">_xlfn.TRANSLATE(P85,"pt","es")</f>
         <v>Aplicación Revit</v>
       </c>
-      <c r="R85" s="58" t="str">
+      <c r="R85" s="57" t="str">
         <f t="shared" ref="R85:R87" si="22">_xlfn.TRANSLATE(P85,"pt","en")</f>
         <v>Revit App</v>
       </c>
@@ -12341,7 +12338,7 @@
         <f t="shared" si="23"/>
         <v>Métodos</v>
       </c>
-      <c r="V85" s="59" t="str">
+      <c r="V85" s="58" t="str">
         <f t="shared" si="23"/>
         <v>Macros</v>
       </c>
@@ -12352,39 +12349,39 @@
         <f t="shared" si="17"/>
         <v>Key-AVAC-85</v>
       </c>
-      <c r="Y85" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z85" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA85" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB85" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC85" s="60" t="s">
+      <c r="Y85" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z85" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA85" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB85" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC85" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="50">
         <v>86</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C86" s="62" t="s">
+      <c r="C86" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="D86" s="62" t="s">
+      <c r="D86" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E86" s="62" t="s">
+      <c r="E86" s="61" t="s">
         <v>586</v>
       </c>
-      <c r="F86" s="62" t="s">
+      <c r="F86" s="61" t="s">
         <v>572</v>
       </c>
       <c r="G86" s="52" t="s">
@@ -12421,11 +12418,11 @@
       <c r="P86" s="30" t="s">
         <v>574</v>
       </c>
-      <c r="Q86" s="58" t="str">
+      <c r="Q86" s="57" t="str">
         <f t="shared" si="21"/>
         <v>Proyecto de instalación de calefacción de aire.</v>
       </c>
-      <c r="R86" s="58" t="str">
+      <c r="R86" s="57" t="str">
         <f t="shared" si="22"/>
         <v>Air heating installation project.</v>
       </c>
@@ -12440,7 +12437,7 @@
         <f t="shared" si="23"/>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V86" s="59" t="str">
+      <c r="V86" s="58" t="str">
         <f t="shared" si="23"/>
         <v>Circulação de Ar Interior</v>
       </c>
@@ -12451,39 +12448,39 @@
         <f t="shared" ref="X86:X87" si="24">CONCATENATE("Key-AVAC-",A86)</f>
         <v>Key-AVAC-86</v>
       </c>
-      <c r="Y86" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z86" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA86" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB86" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC86" s="60" t="s">
+      <c r="Y86" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z86" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA86" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB86" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC86" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="50">
         <v>87</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C87" s="62" t="s">
+      <c r="C87" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="D87" s="62" t="s">
+      <c r="D87" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="E87" s="61" t="s">
         <v>586</v>
       </c>
-      <c r="F87" s="62" t="s">
+      <c r="F87" s="61" t="s">
         <v>577</v>
       </c>
       <c r="G87" s="52" t="s">
@@ -12520,11 +12517,11 @@
       <c r="P87" s="30" t="s">
         <v>580</v>
       </c>
-      <c r="Q87" s="58" t="str">
+      <c r="Q87" s="57" t="str">
         <f t="shared" si="21"/>
         <v>Proyecto de instalación de refrigeración por aire (inflado).</v>
       </c>
-      <c r="R87" s="58" t="str">
+      <c r="R87" s="57" t="str">
         <f t="shared" si="22"/>
         <v>Air cooling installation project (Inflated).</v>
       </c>
@@ -12539,7 +12536,7 @@
         <f t="shared" si="23"/>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V87" s="59" t="str">
+      <c r="V87" s="58" t="str">
         <f t="shared" si="23"/>
         <v>Circulação de Ar Interior</v>
       </c>
@@ -12550,39 +12547,39 @@
         <f t="shared" si="24"/>
         <v>Key-AVAC-87</v>
       </c>
-      <c r="Y87" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z87" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA87" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB87" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC87" s="60" t="s">
+      <c r="Y87" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z87" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA87" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB87" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC87" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="50">
         <v>88</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C88" s="62" t="s">
+      <c r="C88" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="D88" s="62" t="s">
+      <c r="D88" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E88" s="62" t="s">
+      <c r="E88" s="61" t="s">
         <v>586</v>
       </c>
-      <c r="F88" s="62" t="s">
+      <c r="F88" s="61" t="s">
         <v>625</v>
       </c>
       <c r="G88" s="52" t="s">
@@ -12619,11 +12616,11 @@
       <c r="P88" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="Q88" s="58" t="str">
+      <c r="Q88" s="57" t="str">
         <f t="shared" ref="Q88:Q91" si="29">_xlfn.TRANSLATE(P88,"pt","es")</f>
         <v>Proyecto de instalación de refrigeración por aire (Retorno).</v>
       </c>
-      <c r="R88" s="58" t="str">
+      <c r="R88" s="57" t="str">
         <f t="shared" ref="R88:R91" si="30">_xlfn.TRANSLATE(P88,"pt","en")</f>
         <v>Air Cooling Installation Project (Return).</v>
       </c>
@@ -12638,7 +12635,7 @@
         <f t="shared" ref="U88:U91" si="32">SUBSTITUTE(D88, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V88" s="59" t="str">
+      <c r="V88" s="58" t="str">
         <f t="shared" ref="V88:V91" si="33">SUBSTITUTE(E88, ".", " ")</f>
         <v>Circulação de Ar Interior</v>
       </c>
@@ -12649,39 +12646,39 @@
         <f t="shared" si="17"/>
         <v>Key-AVAC-88</v>
       </c>
-      <c r="Y88" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z88" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA88" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB88" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC88" s="60" t="s">
+      <c r="Y88" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z88" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA88" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB88" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC88" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="50">
         <v>89</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C89" s="62" t="s">
+      <c r="C89" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="D89" s="62" t="s">
+      <c r="D89" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E89" s="62" t="s">
+      <c r="E89" s="61" t="s">
         <v>586</v>
       </c>
-      <c r="F89" s="62" t="s">
+      <c r="F89" s="61" t="s">
         <v>588</v>
       </c>
       <c r="G89" s="52" t="s">
@@ -12718,11 +12715,11 @@
       <c r="P89" s="30" t="s">
         <v>565</v>
       </c>
-      <c r="Q89" s="58" t="str">
+      <c r="Q89" s="57" t="str">
         <f t="shared" si="29"/>
         <v>Proyecto de instalación de escapes mecánicos.</v>
       </c>
-      <c r="R89" s="58" t="str">
+      <c r="R89" s="57" t="str">
         <f t="shared" si="30"/>
         <v>Mechanical exhaust installation project.</v>
       </c>
@@ -12737,7 +12734,7 @@
         <f t="shared" si="32"/>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V89" s="59" t="str">
+      <c r="V89" s="58" t="str">
         <f t="shared" si="33"/>
         <v>Circulação de Ar Interior</v>
       </c>
@@ -12748,39 +12745,39 @@
         <f t="shared" si="17"/>
         <v>Key-AVAC-89</v>
       </c>
-      <c r="Y89" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z89" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA89" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB89" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC89" s="60" t="s">
+      <c r="Y89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC89" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="50">
         <v>90</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C90" s="62" t="s">
+      <c r="C90" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="D90" s="62" t="s">
+      <c r="D90" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="61" t="s">
         <v>586</v>
       </c>
-      <c r="F90" s="62" t="s">
+      <c r="F90" s="61" t="s">
         <v>573</v>
       </c>
       <c r="G90" s="52" t="s">
@@ -12817,11 +12814,11 @@
       <c r="P90" s="30" t="s">
         <v>575</v>
       </c>
-      <c r="Q90" s="58" t="str">
+      <c r="Q90" s="57" t="str">
         <f t="shared" ref="Q90" si="38">_xlfn.TRANSLATE(P90,"pt","es")</f>
         <v>Proyecto de instalación de ventilación del aire interior.</v>
       </c>
-      <c r="R90" s="58" t="str">
+      <c r="R90" s="57" t="str">
         <f t="shared" ref="R90" si="39">_xlfn.TRANSLATE(P90,"pt","en")</f>
         <v>Indoor air ventilation installation project.</v>
       </c>
@@ -12836,7 +12833,7 @@
         <f t="shared" ref="U90" si="41">SUBSTITUTE(D90, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V90" s="59" t="str">
+      <c r="V90" s="58" t="str">
         <f t="shared" ref="V90" si="42">SUBSTITUTE(E90, ".", " ")</f>
         <v>Circulação de Ar Interior</v>
       </c>
@@ -12847,39 +12844,39 @@
         <f t="shared" ref="X90" si="43">CONCATENATE("Key-AVAC-",A90)</f>
         <v>Key-AVAC-90</v>
       </c>
-      <c r="Y90" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z90" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA90" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB90" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC90" s="60" t="s">
+      <c r="Y90" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z90" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA90" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB90" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC90" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="50">
         <v>91</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C91" s="62" t="s">
+      <c r="C91" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="D91" s="62" t="s">
+      <c r="D91" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E91" s="62" t="s">
+      <c r="E91" s="61" t="s">
         <v>586</v>
       </c>
-      <c r="F91" s="62" t="s">
+      <c r="F91" s="61" t="s">
         <v>578</v>
       </c>
       <c r="G91" s="52" t="s">
@@ -12916,11 +12913,11 @@
       <c r="P91" s="30" t="s">
         <v>582</v>
       </c>
-      <c r="Q91" s="58" t="str">
+      <c r="Q91" s="57" t="str">
         <f t="shared" si="29"/>
         <v>Proyecto de instalación de filtración de aire interior.</v>
       </c>
-      <c r="R91" s="58" t="str">
+      <c r="R91" s="57" t="str">
         <f t="shared" si="30"/>
         <v>Indoor air filtration installation project.</v>
       </c>
@@ -12935,7 +12932,7 @@
         <f t="shared" si="32"/>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V91" s="59" t="str">
+      <c r="V91" s="58" t="str">
         <f t="shared" si="33"/>
         <v>Circulação de Ar Interior</v>
       </c>
@@ -12946,39 +12943,39 @@
         <f t="shared" si="17"/>
         <v>Key-AVAC-91</v>
       </c>
-      <c r="Y91" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z91" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA91" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB91" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC91" s="60" t="s">
+      <c r="Y91" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z91" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA91" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB91" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC91" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="50">
         <v>92</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C92" s="62" t="s">
+      <c r="C92" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="D92" s="62" t="s">
+      <c r="D92" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E92" s="62" t="s">
+      <c r="E92" s="61" t="s">
         <v>585</v>
       </c>
-      <c r="F92" s="62" t="s">
+      <c r="F92" s="61" t="s">
         <v>579</v>
       </c>
       <c r="G92" s="52" t="s">
@@ -13015,11 +13012,11 @@
       <c r="P92" s="30" t="s">
         <v>576</v>
       </c>
-      <c r="Q92" s="58" t="str">
+      <c r="Q92" s="57" t="str">
         <f t="shared" ref="Q92" si="48">_xlfn.TRANSLATE(P92,"pt","es")</f>
         <v>Proyecto de instalación de filtración de aire exterior.</v>
       </c>
-      <c r="R92" s="58" t="str">
+      <c r="R92" s="57" t="str">
         <f t="shared" ref="R92" si="49">_xlfn.TRANSLATE(P92,"pt","en")</f>
         <v>Outdoor air filtration installation project.</v>
       </c>
@@ -13034,7 +13031,7 @@
         <f t="shared" ref="U92" si="51">SUBSTITUTE(D92, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V92" s="59" t="str">
+      <c r="V92" s="58" t="str">
         <f t="shared" ref="V92" si="52">SUBSTITUTE(E92, ".", " ")</f>
         <v>Captação de Ar Exterior</v>
       </c>
@@ -13045,39 +13042,39 @@
         <f t="shared" ref="X92" si="53">CONCATENATE("Key-AVAC-",A92)</f>
         <v>Key-AVAC-92</v>
       </c>
-      <c r="Y92" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z92" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA92" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB92" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC92" s="60" t="s">
+      <c r="Y92" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z92" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA92" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB92" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC92" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:29" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="50">
         <v>93</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C93" s="62" t="s">
+      <c r="C93" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="D93" s="62" t="s">
+      <c r="D93" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E93" s="62" t="s">
+      <c r="E93" s="61" t="s">
         <v>585</v>
       </c>
-      <c r="F93" s="62" t="s">
+      <c r="F93" s="61" t="s">
         <v>587</v>
       </c>
       <c r="G93" s="52" t="s">
@@ -13114,11 +13111,11 @@
       <c r="P93" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="Q93" s="58" t="str">
+      <c r="Q93" s="57" t="str">
         <f t="shared" ref="Q93" si="58">_xlfn.TRANSLATE(P93,"pt","es")</f>
         <v>Proyecto de instalación de la toma de aire exterior.</v>
       </c>
-      <c r="R93" s="58" t="str">
+      <c r="R93" s="57" t="str">
         <f t="shared" ref="R93" si="59">_xlfn.TRANSLATE(P93,"pt","en")</f>
         <v>Outdoor air intake installation project.</v>
       </c>
@@ -13133,7 +13130,7 @@
         <f t="shared" ref="U93" si="61">SUBSTITUTE(D93, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V93" s="59" t="str">
+      <c r="V93" s="58" t="str">
         <f t="shared" ref="V93" si="62">SUBSTITUTE(E93, ".", " ")</f>
         <v>Captação de Ar Exterior</v>
       </c>
@@ -13144,19 +13141,19 @@
         <f t="shared" ref="X93" si="63">CONCATENATE("Key-AVAC-",A93)</f>
         <v>Key-AVAC-93</v>
       </c>
-      <c r="Y93" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z93" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA93" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB93" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC93" s="60" t="s">
+      <c r="Y93" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z93" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA93" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB93" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC93" s="59" t="s">
         <v>9</v>
       </c>
     </row>
@@ -13749,7 +13746,7 @@
       <c r="A2" s="19">
         <v>2</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="66" t="s">
         <v>467</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -13758,7 +13755,7 @@
       <c r="D2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="68" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="20" t="s">
@@ -13773,7 +13770,7 @@
       <c r="I2" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="J2" s="63" t="s">
+      <c r="J2" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K2" s="23" t="s">
@@ -13785,7 +13782,7 @@
       <c r="M2" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="N2" s="63" t="s">
+      <c r="N2" s="62" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="23" t="s">
@@ -13797,19 +13794,19 @@
       <c r="Q2" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="R2" s="63" t="s">
+      <c r="R2" s="62" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="63" t="s">
+      <c r="T2" s="62" t="s">
         <v>9</v>
       </c>
       <c r="U2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="V2" s="63" t="s">
+      <c r="V2" s="62" t="s">
         <v>9</v>
       </c>
       <c r="W2" s="23" t="s">
@@ -13824,31 +13821,31 @@
       <c r="Z2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="69" t="s">
+      <c r="AA2" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC2" s="69" t="s">
+      <c r="AC2" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE2" s="69" t="s">
+      <c r="AE2" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG2" s="69" t="s">
+      <c r="AG2" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI2" s="69" t="s">
+      <c r="AI2" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -13856,7 +13853,7 @@
       <c r="A3" s="19">
         <v>3</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>590</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -13880,25 +13877,25 @@
       <c r="I3" s="23" t="s">
         <v>595</v>
       </c>
-      <c r="J3" s="63" t="s">
+      <c r="J3" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K3" s="21" t="s">
         <v>619</v>
       </c>
-      <c r="L3" s="63" t="s">
+      <c r="L3" s="62" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="63" t="s">
+      <c r="N3" s="62" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="63" t="s">
+      <c r="P3" s="62" t="s">
         <v>621</v>
       </c>
       <c r="Q3" s="23" t="s">
@@ -13931,31 +13928,31 @@
       <c r="Z3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="69" t="s">
+      <c r="AA3" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC3" s="69" t="s">
+      <c r="AC3" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="69" t="s">
+      <c r="AE3" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG3" s="69" t="s">
+      <c r="AG3" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI3" s="69" t="s">
+      <c r="AI3" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -13963,7 +13960,7 @@
       <c r="A4" s="19">
         <v>4</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="67" t="s">
         <v>589</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -13987,25 +13984,25 @@
       <c r="I4" s="23" t="s">
         <v>595</v>
       </c>
-      <c r="J4" s="63" t="s">
+      <c r="J4" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K4" s="21" t="s">
         <v>619</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="62" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="63" t="s">
+      <c r="N4" s="62" t="s">
         <v>9</v>
       </c>
       <c r="O4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="63" t="s">
+      <c r="P4" s="62" t="s">
         <v>621</v>
       </c>
       <c r="Q4" s="23" t="s">
@@ -14038,31 +14035,31 @@
       <c r="Z4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="69" t="s">
+      <c r="AA4" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" s="69" t="s">
+      <c r="AC4" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE4" s="69" t="s">
+      <c r="AE4" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG4" s="69" t="s">
+      <c r="AG4" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI4" s="69" t="s">
+      <c r="AI4" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -14070,7 +14067,7 @@
       <c r="A5" s="19">
         <v>5</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="67" t="s">
         <v>591</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -14094,25 +14091,25 @@
       <c r="I5" s="23" t="s">
         <v>595</v>
       </c>
-      <c r="J5" s="63" t="s">
+      <c r="J5" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K5" s="21" t="s">
         <v>620</v>
       </c>
-      <c r="L5" s="63" t="s">
+      <c r="L5" s="62" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="N5" s="62" t="s">
         <v>9</v>
       </c>
       <c r="O5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="63" t="s">
+      <c r="P5" s="62" t="s">
         <v>621</v>
       </c>
       <c r="Q5" s="23" t="s">
@@ -14145,31 +14142,31 @@
       <c r="Z5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA5" s="69" t="s">
+      <c r="AA5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC5" s="69" t="s">
+      <c r="AC5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE5" s="69" t="s">
+      <c r="AE5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG5" s="69" t="s">
+      <c r="AG5" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI5" s="69" t="s">
+      <c r="AI5" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -14177,43 +14174,43 @@
       <c r="A6" s="19">
         <v>6</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="66" t="s">
         <v>596</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="61" t="s">
         <v>563</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="64" t="s">
+      <c r="E6" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="63" t="s">
         <v>73</v>
       </c>
       <c r="G6" s="23" t="s">
         <v>600</v>
       </c>
-      <c r="H6" s="63" t="s">
+      <c r="H6" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I6" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="J6" s="63" t="s">
+      <c r="J6" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>599</v>
       </c>
-      <c r="L6" s="63" t="s">
+      <c r="L6" s="62" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N6" s="63" t="s">
+      <c r="N6" s="62" t="s">
         <v>598</v>
       </c>
       <c r="O6" s="23" t="s">
@@ -14243,41 +14240,41 @@
       <c r="W6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="X6" s="65" t="str">
+      <c r="X6" s="64" t="str">
         <f t="shared" ref="X6:X10" si="0">IF(Y6="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="Y6" s="66" t="s">
+      <c r="Y6" s="65" t="s">
         <v>601</v>
       </c>
       <c r="Z6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA6" s="69" t="s">
+      <c r="AA6" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC6" s="69" t="s">
+      <c r="AC6" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE6" s="69" t="s">
+      <c r="AE6" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG6" s="69" t="s">
+      <c r="AG6" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI6" s="69" t="s">
+      <c r="AI6" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -14285,43 +14282,43 @@
       <c r="A7" s="19">
         <v>7</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="66" t="s">
         <v>602</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="61" t="s">
         <v>563</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="64" t="s">
+      <c r="E7" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="63" t="s">
         <v>73</v>
       </c>
       <c r="G7" s="23" t="s">
         <v>604</v>
       </c>
-      <c r="H7" s="63" t="s">
+      <c r="H7" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="J7" s="63" t="s">
+      <c r="J7" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K7" s="23" t="s">
         <v>603</v>
       </c>
-      <c r="L7" s="63" t="s">
+      <c r="L7" s="62" t="s">
         <v>9</v>
       </c>
       <c r="M7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N7" s="63" t="s">
+      <c r="N7" s="62" t="s">
         <v>598</v>
       </c>
       <c r="O7" s="23" t="s">
@@ -14351,41 +14348,41 @@
       <c r="W7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="X7" s="65" t="str">
+      <c r="X7" s="64" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Y7" s="66" t="s">
+      <c r="Y7" s="65" t="s">
         <v>605</v>
       </c>
       <c r="Z7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA7" s="69" t="s">
+      <c r="AA7" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC7" s="69" t="s">
+      <c r="AC7" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE7" s="69" t="s">
+      <c r="AE7" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG7" s="69" t="s">
+      <c r="AG7" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI7" s="69" t="s">
+      <c r="AI7" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -14393,43 +14390,43 @@
       <c r="A8" s="19">
         <v>8</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="66" t="s">
         <v>606</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="61" t="s">
         <v>563</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="64" t="s">
+      <c r="E8" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="63" t="s">
         <v>73</v>
       </c>
       <c r="G8" s="23" t="s">
         <v>608</v>
       </c>
-      <c r="H8" s="63" t="s">
+      <c r="H8" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="J8" s="63" t="s">
+      <c r="J8" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K8" s="23" t="s">
         <v>607</v>
       </c>
-      <c r="L8" s="63" t="s">
+      <c r="L8" s="62" t="s">
         <v>9</v>
       </c>
       <c r="M8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="63" t="s">
+      <c r="N8" s="62" t="s">
         <v>598</v>
       </c>
       <c r="O8" s="23" t="s">
@@ -14459,41 +14456,41 @@
       <c r="W8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="X8" s="65" t="str">
+      <c r="X8" s="64" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Y8" s="66" t="s">
+      <c r="Y8" s="65" t="s">
         <v>609</v>
       </c>
       <c r="Z8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA8" s="69" t="s">
+      <c r="AA8" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC8" s="69" t="s">
+      <c r="AC8" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE8" s="69" t="s">
+      <c r="AE8" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG8" s="69" t="s">
+      <c r="AG8" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI8" s="69" t="s">
+      <c r="AI8" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -14501,43 +14498,43 @@
       <c r="A9" s="19">
         <v>9</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="66" t="s">
         <v>610</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="61" t="s">
         <v>563</v>
       </c>
       <c r="D9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="64" t="s">
+      <c r="E9" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="63" t="s">
         <v>73</v>
       </c>
       <c r="G9" s="23" t="s">
         <v>612</v>
       </c>
-      <c r="H9" s="63" t="s">
+      <c r="H9" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I9" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="J9" s="63" t="s">
+      <c r="J9" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K9" s="23" t="s">
         <v>611</v>
       </c>
-      <c r="L9" s="63" t="s">
+      <c r="L9" s="62" t="s">
         <v>9</v>
       </c>
       <c r="M9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N9" s="63" t="s">
+      <c r="N9" s="62" t="s">
         <v>598</v>
       </c>
       <c r="O9" s="23" t="s">
@@ -14567,41 +14564,41 @@
       <c r="W9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="X9" s="65" t="str">
+      <c r="X9" s="64" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Y9" s="66" t="s">
+      <c r="Y9" s="65" t="s">
         <v>613</v>
       </c>
       <c r="Z9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA9" s="69" t="s">
+      <c r="AA9" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC9" s="69" t="s">
+      <c r="AC9" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE9" s="69" t="s">
+      <c r="AE9" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG9" s="69" t="s">
+      <c r="AG9" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI9" s="69" t="s">
+      <c r="AI9" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -14609,43 +14606,43 @@
       <c r="A10" s="19">
         <v>10</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="66" t="s">
         <v>614</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="61" t="s">
         <v>563</v>
       </c>
       <c r="D10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="64" t="s">
+      <c r="E10" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="63" t="s">
         <v>73</v>
       </c>
       <c r="G10" s="23" t="s">
         <v>616</v>
       </c>
-      <c r="H10" s="63" t="s">
+      <c r="H10" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="J10" s="63" t="s">
+      <c r="J10" s="62" t="s">
         <v>598</v>
       </c>
       <c r="K10" s="23" t="s">
         <v>615</v>
       </c>
-      <c r="L10" s="63" t="s">
+      <c r="L10" s="62" t="s">
         <v>9</v>
       </c>
       <c r="M10" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="63" t="s">
+      <c r="N10" s="62" t="s">
         <v>598</v>
       </c>
       <c r="O10" s="23" t="s">
@@ -14675,41 +14672,41 @@
       <c r="W10" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="X10" s="65" t="str">
+      <c r="X10" s="64" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Y10" s="66" t="s">
+      <c r="Y10" s="65" t="s">
         <v>617</v>
       </c>
       <c r="Z10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AA10" s="69" t="s">
+      <c r="AA10" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AB10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AC10" s="69" t="s">
+      <c r="AC10" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AD10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AE10" s="69" t="s">
+      <c r="AE10" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AF10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AG10" s="69" t="s">
+      <c r="AG10" s="68" t="s">
         <v>9</v>
       </c>
       <c r="AH10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="AI10" s="69" t="s">
+      <c r="AI10" s="68" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Versão5/SIS/Ontologia_Avac.xlsx
+++ b/Versão5/SIS/Ontologia_Avac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF25C54-F1C2-4B3D-8C2A-EBCF53503512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3284A1-BDFF-4CDE-85D1-CA7F24C74A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -2503,7 +2503,24 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="90">
+  <dxfs count="81">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2540,86 +2557,6 @@
         <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2727,6 +2664,22 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2774,22 +2727,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3788,14 +3725,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>43</v>
       </c>
@@ -3806,7 +3743,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>45</v>
       </c>
@@ -3817,7 +3754,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>47</v>
       </c>
@@ -3828,7 +3765,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>48</v>
       </c>
@@ -3839,7 +3776,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>49</v>
       </c>
@@ -3851,7 +3788,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>50</v>
       </c>
@@ -3863,7 +3800,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>51</v>
       </c>
@@ -3874,7 +3811,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>53</v>
       </c>
@@ -3885,7 +3822,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>54</v>
       </c>
@@ -3896,7 +3833,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>56</v>
       </c>
@@ -3907,7 +3844,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>58</v>
       </c>
@@ -3918,7 +3855,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>59</v>
       </c>
@@ -3929,7 +3866,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>60</v>
       </c>
@@ -3940,7 +3877,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>61</v>
       </c>
@@ -3951,7 +3888,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>62</v>
       </c>
@@ -3962,7 +3899,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>63</v>
       </c>
@@ -3973,7 +3910,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>64</v>
       </c>
@@ -3984,19 +3921,19 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46260.407161921299</v>
+        <v>46264.570104513892</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>203</v>
       </c>
@@ -4007,7 +3944,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>205</v>
       </c>
@@ -4019,7 +3956,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>206</v>
       </c>
@@ -4031,7 +3968,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>66</v>
       </c>
@@ -4042,7 +3979,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>67</v>
       </c>
@@ -4053,7 +3990,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>68</v>
       </c>
@@ -4064,7 +4001,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="14" t="s">
         <v>69</v>
       </c>
@@ -4075,7 +4012,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="14" t="s">
         <v>197</v>
       </c>
@@ -4096,37 +4033,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC93"/>
-  <sheetFormatPr defaultColWidth="7.85546875" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="7.84375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="51" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" style="46" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="5.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="90.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="68.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="88.42578125" style="46" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="46" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" style="46" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="46" customWidth="1"/>
-    <col min="27" max="27" width="22.28515625" style="46" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" style="51" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.15234375" style="46" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.3828125" style="46" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="5.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.15234375" style="46" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="90.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="68.84375" style="46" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="88.3828125" style="46" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.15234375" style="46" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.53515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="46" customWidth="1"/>
+    <col min="27" max="27" width="22.3046875" style="46" customWidth="1"/>
     <col min="28" max="28" width="6" style="46" customWidth="1"/>
-    <col min="29" max="29" width="5.5703125" style="46" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="7.85546875" style="46"/>
+    <col min="29" max="29" width="5.53515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="7.84375" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="56" customFormat="1" ht="30.4" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" s="56" customFormat="1" ht="30.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="53">
         <v>1</v>
       </c>
@@ -4215,7 +4152,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -4312,7 +4249,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -4409,7 +4346,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -4506,7 +4443,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -4603,7 +4540,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -4700,7 +4637,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -4797,7 +4734,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -4894,7 +4831,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -4991,7 +4928,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -5088,7 +5025,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -5185,7 +5122,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -5282,7 +5219,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -5379,7 +5316,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -5476,7 +5413,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -5573,7 +5510,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -5670,7 +5607,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -5767,7 +5704,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -5864,7 +5801,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -5961,7 +5898,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -6058,7 +5995,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -6155,7 +6092,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -6252,7 +6189,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -6349,7 +6286,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -6446,7 +6383,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -6543,7 +6480,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -6640,7 +6577,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -6737,7 +6674,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -6834,7 +6771,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="50">
         <v>29</v>
       </c>
@@ -6931,7 +6868,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="50">
         <v>30</v>
       </c>
@@ -7028,7 +6965,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="50">
         <v>31</v>
       </c>
@@ -7125,7 +7062,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="50">
         <v>32</v>
       </c>
@@ -7222,7 +7159,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="50">
         <v>33</v>
       </c>
@@ -7319,7 +7256,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="50">
         <v>34</v>
       </c>
@@ -7416,7 +7353,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="50">
         <v>35</v>
       </c>
@@ -7513,7 +7450,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="50">
         <v>36</v>
       </c>
@@ -7610,7 +7547,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="50">
         <v>37</v>
       </c>
@@ -7707,7 +7644,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="50">
         <v>38</v>
       </c>
@@ -7804,7 +7741,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="50">
         <v>39</v>
       </c>
@@ -7901,7 +7838,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="50">
         <v>40</v>
       </c>
@@ -7998,7 +7935,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="50">
         <v>41</v>
       </c>
@@ -8095,7 +8032,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="50">
         <v>42</v>
       </c>
@@ -8192,7 +8129,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="50">
         <v>43</v>
       </c>
@@ -8289,7 +8226,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="50">
         <v>44</v>
       </c>
@@ -8386,7 +8323,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="50">
         <v>45</v>
       </c>
@@ -8483,7 +8420,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="50">
         <v>46</v>
       </c>
@@ -8580,7 +8517,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="50">
         <v>47</v>
       </c>
@@ -8677,7 +8614,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="50">
         <v>48</v>
       </c>
@@ -8774,7 +8711,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="50">
         <v>49</v>
       </c>
@@ -8871,7 +8808,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="50">
         <v>50</v>
       </c>
@@ -8968,7 +8905,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="50">
         <v>51</v>
       </c>
@@ -9065,7 +9002,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="50">
         <v>52</v>
       </c>
@@ -9162,7 +9099,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="50">
         <v>53</v>
       </c>
@@ -9259,7 +9196,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="50">
         <v>54</v>
       </c>
@@ -9356,7 +9293,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="50">
         <v>55</v>
       </c>
@@ -9453,7 +9390,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="50">
         <v>56</v>
       </c>
@@ -9550,7 +9487,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="50">
         <v>57</v>
       </c>
@@ -9647,7 +9584,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="50">
         <v>58</v>
       </c>
@@ -9744,7 +9681,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="50">
         <v>59</v>
       </c>
@@ -9841,7 +9778,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="50">
         <v>60</v>
       </c>
@@ -9938,7 +9875,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="50">
         <v>61</v>
       </c>
@@ -10035,7 +9972,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="50">
         <v>62</v>
       </c>
@@ -10132,7 +10069,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="50">
         <v>63</v>
       </c>
@@ -10229,7 +10166,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="50">
         <v>64</v>
       </c>
@@ -10326,7 +10263,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="50">
         <v>65</v>
       </c>
@@ -10423,7 +10360,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="50">
         <v>66</v>
       </c>
@@ -10520,7 +10457,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="50">
         <v>67</v>
       </c>
@@ -10617,7 +10554,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="50">
         <v>68</v>
       </c>
@@ -10714,7 +10651,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="50">
         <v>69</v>
       </c>
@@ -10811,7 +10748,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="50">
         <v>70</v>
       </c>
@@ -10908,7 +10845,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="50">
         <v>71</v>
       </c>
@@ -11005,7 +10942,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="50">
         <v>72</v>
       </c>
@@ -11102,7 +11039,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="50">
         <v>73</v>
       </c>
@@ -11199,7 +11136,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="50">
         <v>74</v>
       </c>
@@ -11296,7 +11233,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="50">
         <v>75</v>
       </c>
@@ -11393,7 +11330,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="50">
         <v>76</v>
       </c>
@@ -11490,7 +11427,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="50">
         <v>77</v>
       </c>
@@ -11587,7 +11524,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="50">
         <v>78</v>
       </c>
@@ -11684,7 +11621,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="50">
         <v>79</v>
       </c>
@@ -11781,7 +11718,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="50">
         <v>80</v>
       </c>
@@ -11878,7 +11815,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="50">
         <v>81</v>
       </c>
@@ -11975,7 +11912,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="50">
         <v>82</v>
       </c>
@@ -12072,7 +12009,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="50">
         <v>83</v>
       </c>
@@ -12169,7 +12106,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="50">
         <v>84</v>
       </c>
@@ -12266,7 +12203,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="85" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="50">
         <v>85</v>
       </c>
@@ -12277,10 +12214,10 @@
         <v>560</v>
       </c>
       <c r="D85" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="E85" s="61" t="s">
         <v>561</v>
-      </c>
-      <c r="E85" s="61" t="s">
-        <v>562</v>
       </c>
       <c r="F85" s="61" t="s">
         <v>563</v>
@@ -12306,11 +12243,11 @@
       </c>
       <c r="M85" s="35" t="str">
         <f t="shared" si="20"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N85" s="35" t="str">
         <f t="shared" si="20"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O85" s="35" t="str">
         <f t="shared" si="20"/>
@@ -12336,11 +12273,11 @@
       </c>
       <c r="U85" s="30" t="str">
         <f t="shared" si="23"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V85" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W85" s="30" t="s">
         <v>209</v>
@@ -12365,7 +12302,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="50">
         <v>86</v>
       </c>
@@ -12464,7 +12401,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="50">
         <v>87</v>
       </c>
@@ -12563,7 +12500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="50">
         <v>88</v>
       </c>
@@ -12662,7 +12599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="50">
         <v>89</v>
       </c>
@@ -12761,7 +12698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="50">
         <v>90</v>
       </c>
@@ -12860,7 +12797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="50">
         <v>91</v>
       </c>
@@ -12959,7 +12896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="50">
         <v>92</v>
       </c>
@@ -13058,7 +12995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="50">
         <v>93</v>
       </c>
@@ -13158,139 +13095,139 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B85:B93 A2:A93">
-    <cfRule type="cellIs" dxfId="89" priority="18" operator="equal">
+  <conditionalFormatting sqref="A2:A93 B85:B93">
+    <cfRule type="cellIs" dxfId="80" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:F82 L50:Q82 T50:V82 Y50:Y82 AA50:AA82 E83:E84">
-    <cfRule type="cellIs" dxfId="88" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="50" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="87" priority="2333"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="2333"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4">
-    <cfRule type="duplicateValues" dxfId="86" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F15">
-    <cfRule type="duplicateValues" dxfId="84" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F43 F47:F84">
-    <cfRule type="duplicateValues" dxfId="83" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F17 F83:F84">
-    <cfRule type="duplicateValues" dxfId="82" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F17">
-    <cfRule type="duplicateValues" dxfId="81" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F24">
-    <cfRule type="duplicateValues" dxfId="80" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F26">
-    <cfRule type="duplicateValues" dxfId="76" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F28">
-    <cfRule type="duplicateValues" dxfId="74" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F43">
-    <cfRule type="duplicateValues" dxfId="70" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F43">
-    <cfRule type="duplicateValues" dxfId="69" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:F46 L44:R46 T44:V46 Y44:Y46 AA44:AA46 AD44:XFD46">
-    <cfRule type="cellIs" dxfId="67" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:F46">
-    <cfRule type="duplicateValues" dxfId="66" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F49">
-    <cfRule type="duplicateValues" dxfId="56" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50:F82">
-    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84 F5:F43 F47:F49">
-    <cfRule type="duplicateValues" dxfId="43" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84 F16:F26">
-    <cfRule type="duplicateValues" dxfId="42" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84">
-    <cfRule type="duplicateValues" dxfId="41" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F85:F93">
+    <cfRule type="duplicateValues" dxfId="31" priority="2347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="40" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="2335"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="2335"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94:F1048576 F1:F84">
-    <cfRule type="duplicateValues" dxfId="38" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94:F1048576">
-    <cfRule type="duplicateValues" dxfId="36" priority="2338"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="2340"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="2341"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="2342"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="2338"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2340"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2341"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2342"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q85:Q93">
+    <cfRule type="duplicateValues" dxfId="22" priority="2353"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2354"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2355"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2356"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="32" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R43 R47:R84">
-    <cfRule type="cellIs" dxfId="31" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F85:F93">
-    <cfRule type="duplicateValues" dxfId="30" priority="2347"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q85:Q93">
-    <cfRule type="duplicateValues" dxfId="29" priority="2353"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="2354"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="2355"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="2356"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="R85:R93">
-    <cfRule type="duplicateValues" dxfId="25" priority="2361"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2362"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2363"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="2364"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2362"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2363"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2364"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -13300,15 +13237,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="1.3046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="15.45" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -13373,7 +13310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -13438,7 +13375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -13505,7 +13442,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13521,15 +13458,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.15234375" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -13552,7 +13489,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -13578,22 +13515,22 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:G1 C2:G2">
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:G1048576">
-    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13605,37 +13542,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AI10"/>
-  <sheetFormatPr defaultColWidth="64.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="64.3046875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="4.5703125" style="46" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" style="46" customWidth="1"/>
-    <col min="17" max="17" width="6.140625" customWidth="1"/>
-    <col min="18" max="18" width="6.85546875" customWidth="1"/>
-    <col min="19" max="19" width="44.140625" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" customWidth="1"/>
-    <col min="21" max="21" width="62.7109375" customWidth="1"/>
-    <col min="22" max="22" width="5.85546875" customWidth="1"/>
-    <col min="23" max="23" width="7.85546875" customWidth="1"/>
-    <col min="24" max="24" width="6.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="35" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.84375" customWidth="1"/>
+    <col min="4" max="4" width="7.3828125" customWidth="1"/>
+    <col min="5" max="5" width="5.3828125" customWidth="1"/>
+    <col min="6" max="6" width="4.84375" customWidth="1"/>
+    <col min="7" max="7" width="37.15234375" customWidth="1"/>
+    <col min="8" max="8" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.84375" customWidth="1"/>
+    <col min="10" max="10" width="4.53515625" style="46" customWidth="1"/>
+    <col min="11" max="11" width="11.84375" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.3046875" style="46" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.53515625" customWidth="1"/>
+    <col min="16" max="16" width="7.3046875" style="46" customWidth="1"/>
+    <col min="17" max="17" width="6.15234375" customWidth="1"/>
+    <col min="18" max="18" width="6.84375" customWidth="1"/>
+    <col min="19" max="19" width="44.15234375" customWidth="1"/>
+    <col min="20" max="20" width="5.3046875" customWidth="1"/>
+    <col min="21" max="21" width="62.69140625" customWidth="1"/>
+    <col min="22" max="22" width="5.84375" customWidth="1"/>
+    <col min="23" max="23" width="7.84375" customWidth="1"/>
+    <col min="24" max="24" width="6.69140625" customWidth="1"/>
+    <col min="25" max="25" width="7.69140625" customWidth="1"/>
+    <col min="26" max="35" width="2.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="46" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="46" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -13742,7 +13679,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -13849,7 +13786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19">
         <v>3</v>
       </c>
@@ -13956,7 +13893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19">
         <v>4</v>
       </c>
@@ -14063,7 +14000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19">
         <v>5</v>
       </c>
@@ -14170,7 +14107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19">
         <v>6</v>
       </c>
@@ -14278,7 +14215,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19">
         <v>7</v>
       </c>
@@ -14386,7 +14323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19">
         <v>8</v>
       </c>
@@ -14494,7 +14431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19">
         <v>9</v>
       </c>
@@ -14602,7 +14539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19">
         <v>10</v>
       </c>
@@ -14712,30 +14649,23 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B3:B5">
-    <cfRule type="duplicateValues" dxfId="14" priority="2248"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V4:W5 AJ4:XFD5">
-    <cfRule type="cellIs" dxfId="13" priority="31" operator="equal">
+  <conditionalFormatting sqref="B3:B5 D3:F5">
+    <cfRule type="cellIs" dxfId="5" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:U5 B3:B5 D3:F5">
-    <cfRule type="cellIs" dxfId="12" priority="19" operator="equal">
+  <conditionalFormatting sqref="B3:B5">
+    <cfRule type="duplicateValues" dxfId="4" priority="2248"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B10">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2 I3:I5 R3:W5 AJ3:XFD5">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V3:W3 AJ3:XFD3 I3:I5 K2">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B10">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B10">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Versão5/SIS/Ontologia_Avac.xlsx
+++ b/Versão5/SIS/Ontologia_Avac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3284A1-BDFF-4CDE-85D1-CA7F24C74A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D65202-3B67-43BE-A49C-E7F148EC2262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2331" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="646">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1762,12 +1762,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
     <t>Projeto de instalação de exaustão mecânica.</t>
   </si>
   <si>
@@ -1949,6 +1943,72 @@
   </si>
   <si>
     <t>Ar.Retornado</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2040,7 +2100,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2197,6 +2257,12 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -2297,7 +2363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2499,11 +2565,14 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
+  <dxfs count="84">
     <dxf>
       <font>
         <b val="0"/>
@@ -2677,6 +2746,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3278,6 +3357,24 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
@@ -3725,14 +3822,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="44" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>43</v>
       </c>
@@ -3743,7 +3840,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>45</v>
       </c>
@@ -3754,7 +3851,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>47</v>
       </c>
@@ -3765,7 +3862,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>48</v>
       </c>
@@ -3776,7 +3873,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>49</v>
       </c>
@@ -3788,7 +3885,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>50</v>
       </c>
@@ -3800,7 +3897,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>51</v>
       </c>
@@ -3811,7 +3908,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>53</v>
       </c>
@@ -3822,7 +3919,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>54</v>
       </c>
@@ -3833,7 +3930,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>56</v>
       </c>
@@ -3844,7 +3941,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>58</v>
       </c>
@@ -3855,7 +3952,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>59</v>
       </c>
@@ -3866,7 +3963,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>60</v>
       </c>
@@ -3877,7 +3974,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>61</v>
       </c>
@@ -3888,7 +3985,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>62</v>
       </c>
@@ -3899,7 +3996,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>63</v>
       </c>
@@ -3910,7 +4007,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>64</v>
       </c>
@@ -3921,19 +4018,19 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46264.570104513892</v>
+        <v>46268.700787037036</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>203</v>
       </c>
@@ -3944,7 +4041,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>205</v>
       </c>
@@ -3956,7 +4053,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>206</v>
       </c>
@@ -3968,7 +4065,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>66</v>
       </c>
@@ -3979,7 +4076,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>67</v>
       </c>
@@ -3990,7 +4087,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>68</v>
       </c>
@@ -4001,7 +4098,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>69</v>
       </c>
@@ -4012,7 +4109,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>197</v>
       </c>
@@ -4032,38 +4129,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC93"/>
-  <sheetFormatPr defaultColWidth="7.84375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD97"/>
+  <sheetFormatPr defaultColWidth="7.85546875" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="51" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.15234375" style="46" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.3828125" style="46" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="5.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.15234375" style="46" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="90.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="68.84375" style="46" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="88.3828125" style="46" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.15234375" style="46" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.69140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.53515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.84375" style="46" customWidth="1"/>
-    <col min="27" max="27" width="22.3046875" style="46" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" style="51" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="5.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="90.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="68.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="88.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="46" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.5703125" style="46" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="46" customWidth="1"/>
+    <col min="27" max="27" width="22.28515625" style="46" customWidth="1"/>
     <col min="28" max="28" width="6" style="46" customWidth="1"/>
-    <col min="29" max="29" width="5.53515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="7.84375" style="46"/>
+    <col min="29" max="30" width="5.5703125" style="46" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="7.85546875" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="56" customFormat="1" ht="30.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" s="56" customFormat="1" ht="30.4" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="53">
         <v>1</v>
       </c>
@@ -4151,8 +4248,11 @@
       <c r="AC1" s="40" t="s">
         <v>195</v>
       </c>
+      <c r="AD1" s="40" t="s">
+        <v>645</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -4160,13 +4260,13 @@
         <v>468</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>445</v>
@@ -4248,8 +4348,11 @@
       <c r="AC2" s="30" t="s">
         <v>266</v>
       </c>
+      <c r="AD2" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -4257,13 +4360,13 @@
         <v>468</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F3" s="47" t="s">
         <v>446</v>
@@ -4345,8 +4448,11 @@
       <c r="AC3" s="30" t="s">
         <v>266</v>
       </c>
+      <c r="AD3" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -4354,13 +4460,13 @@
         <v>468</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E4" s="47" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F4" s="47" t="s">
         <v>447</v>
@@ -4442,8 +4548,11 @@
       <c r="AC4" s="30" t="s">
         <v>266</v>
       </c>
+      <c r="AD4" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -4451,13 +4560,13 @@
         <v>468</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D5" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="E5" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F5" s="34" t="s">
         <v>175</v>
@@ -4539,8 +4648,11 @@
       <c r="AC5" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD5" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -4548,13 +4660,13 @@
         <v>468</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D6" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="E6" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F6" s="34" t="s">
         <v>118</v>
@@ -4636,8 +4748,11 @@
       <c r="AC6" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD6" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -4645,13 +4760,13 @@
         <v>468</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D7" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="E7" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F7" s="34" t="s">
         <v>437</v>
@@ -4733,8 +4848,11 @@
       <c r="AC7" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD7" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -4742,13 +4860,13 @@
         <v>468</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D8" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="E8" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F8" s="34" t="s">
         <v>179</v>
@@ -4830,8 +4948,11 @@
       <c r="AC8" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD8" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -4839,13 +4960,13 @@
         <v>468</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D9" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="E9" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F9" s="34" t="s">
         <v>180</v>
@@ -4927,8 +5048,11 @@
       <c r="AC9" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD9" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -4936,13 +5060,13 @@
         <v>468</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D10" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="E10" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F10" s="34" t="s">
         <v>176</v>
@@ -5024,8 +5148,11 @@
       <c r="AC10" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD10" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -5033,13 +5160,13 @@
         <v>468</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D11" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="E11" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>171</v>
@@ -5121,8 +5248,11 @@
       <c r="AC11" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD11" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -5130,13 +5260,13 @@
         <v>468</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D12" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="E12" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F12" s="34" t="s">
         <v>177</v>
@@ -5218,8 +5348,11 @@
       <c r="AC12" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD12" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -5227,13 +5360,13 @@
         <v>468</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D13" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="E13" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F13" s="34" t="s">
         <v>443</v>
@@ -5315,8 +5448,11 @@
       <c r="AC13" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD13" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -5324,13 +5460,13 @@
         <v>468</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D14" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="E14" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F14" s="34" t="s">
         <v>444</v>
@@ -5412,8 +5548,11 @@
       <c r="AC14" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD14" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -5421,13 +5560,13 @@
         <v>468</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D15" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="E15" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="F15" s="34" t="s">
         <v>178</v>
@@ -5509,8 +5648,11 @@
       <c r="AC15" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD15" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -5518,7 +5660,7 @@
         <v>468</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>434</v>
@@ -5606,8 +5748,11 @@
       <c r="AC16" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD16" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -5615,7 +5760,7 @@
         <v>468</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>434</v>
@@ -5703,8 +5848,11 @@
       <c r="AC17" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD17" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -5712,7 +5860,7 @@
         <v>468</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>434</v>
@@ -5800,8 +5948,11 @@
       <c r="AC18" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD18" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -5809,7 +5960,7 @@
         <v>468</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>434</v>
@@ -5897,8 +6048,11 @@
       <c r="AC19" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD19" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -5906,7 +6060,7 @@
         <v>468</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>434</v>
@@ -5994,8 +6148,11 @@
       <c r="AC20" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD20" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -6003,7 +6160,7 @@
         <v>468</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>434</v>
@@ -6091,8 +6248,11 @@
       <c r="AC21" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD21" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -6100,7 +6260,7 @@
         <v>468</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>434</v>
@@ -6188,8 +6348,11 @@
       <c r="AC22" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD22" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -6197,7 +6360,7 @@
         <v>468</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>434</v>
@@ -6285,8 +6448,11 @@
       <c r="AC23" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD23" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -6294,7 +6460,7 @@
         <v>468</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>434</v>
@@ -6382,8 +6548,11 @@
       <c r="AC24" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD24" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -6391,7 +6560,7 @@
         <v>468</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>434</v>
@@ -6479,8 +6648,11 @@
       <c r="AC25" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD25" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -6488,7 +6660,7 @@
         <v>468</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>434</v>
@@ -6576,8 +6748,11 @@
       <c r="AC26" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD26" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -6585,10 +6760,10 @@
         <v>468</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>396</v>
@@ -6673,8 +6848,11 @@
       <c r="AC27" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD27" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -6682,10 +6860,10 @@
         <v>468</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>396</v>
@@ -6770,8 +6948,11 @@
       <c r="AC28" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD28" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="50">
         <v>29</v>
       </c>
@@ -6779,10 +6960,10 @@
         <v>468</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>396</v>
@@ -6867,8 +7048,11 @@
       <c r="AC29" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD29" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="50">
         <v>30</v>
       </c>
@@ -6876,10 +7060,10 @@
         <v>468</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>396</v>
@@ -6964,8 +7148,11 @@
       <c r="AC30" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD30" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="50">
         <v>31</v>
       </c>
@@ -6973,10 +7160,10 @@
         <v>468</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>396</v>
@@ -7061,8 +7248,11 @@
       <c r="AC31" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD31" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="50">
         <v>32</v>
       </c>
@@ -7070,10 +7260,10 @@
         <v>468</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>396</v>
@@ -7158,8 +7348,11 @@
       <c r="AC32" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD32" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="50">
         <v>33</v>
       </c>
@@ -7167,10 +7360,10 @@
         <v>468</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>396</v>
@@ -7255,8 +7448,11 @@
       <c r="AC33" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD33" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="50">
         <v>34</v>
       </c>
@@ -7264,10 +7460,10 @@
         <v>468</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>396</v>
@@ -7352,8 +7548,11 @@
       <c r="AC34" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD34" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="50">
         <v>35</v>
       </c>
@@ -7361,10 +7560,10 @@
         <v>468</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>396</v>
@@ -7449,8 +7648,11 @@
       <c r="AC35" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD35" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="50">
         <v>36</v>
       </c>
@@ -7458,10 +7660,10 @@
         <v>468</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>396</v>
@@ -7546,8 +7748,11 @@
       <c r="AC36" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD36" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="50">
         <v>37</v>
       </c>
@@ -7555,10 +7760,10 @@
         <v>468</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>396</v>
@@ -7643,8 +7848,11 @@
       <c r="AC37" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD37" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="50">
         <v>38</v>
       </c>
@@ -7652,10 +7860,10 @@
         <v>468</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>396</v>
@@ -7740,8 +7948,11 @@
       <c r="AC38" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD38" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="50">
         <v>39</v>
       </c>
@@ -7749,10 +7960,10 @@
         <v>468</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>396</v>
@@ -7837,8 +8048,11 @@
       <c r="AC39" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD39" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="50">
         <v>40</v>
       </c>
@@ -7846,10 +8060,10 @@
         <v>468</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>396</v>
@@ -7934,8 +8148,11 @@
       <c r="AC40" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD40" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="50">
         <v>41</v>
       </c>
@@ -7943,10 +8160,10 @@
         <v>468</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>396</v>
@@ -8031,8 +8248,11 @@
       <c r="AC41" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD41" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="50">
         <v>42</v>
       </c>
@@ -8040,10 +8260,10 @@
         <v>468</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>396</v>
@@ -8128,8 +8348,11 @@
       <c r="AC42" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD42" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50">
         <v>43</v>
       </c>
@@ -8137,10 +8360,10 @@
         <v>468</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>396</v>
@@ -8225,8 +8448,11 @@
       <c r="AC43" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD43" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50">
         <v>44</v>
       </c>
@@ -8234,10 +8460,10 @@
         <v>468</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>455</v>
@@ -8322,8 +8548,11 @@
       <c r="AC44" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD44" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50">
         <v>45</v>
       </c>
@@ -8331,10 +8560,10 @@
         <v>468</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>455</v>
@@ -8419,8 +8648,11 @@
       <c r="AC45" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD45" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="50">
         <v>46</v>
       </c>
@@ -8428,10 +8660,10 @@
         <v>468</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>455</v>
@@ -8516,8 +8748,11 @@
       <c r="AC46" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD46" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="50">
         <v>47</v>
       </c>
@@ -8525,7 +8760,7 @@
         <v>468</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D47" s="33" t="s">
         <v>435</v>
@@ -8613,8 +8848,11 @@
       <c r="AC47" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD47" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="50">
         <v>48</v>
       </c>
@@ -8622,7 +8860,7 @@
         <v>468</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D48" s="33" t="s">
         <v>435</v>
@@ -8710,8 +8948,11 @@
       <c r="AC48" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD48" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="50">
         <v>49</v>
       </c>
@@ -8719,7 +8960,7 @@
         <v>468</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D49" s="33" t="s">
         <v>435</v>
@@ -8807,8 +9048,11 @@
       <c r="AC49" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD49" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="50">
         <v>50</v>
       </c>
@@ -8816,7 +9060,7 @@
         <v>468</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>436</v>
@@ -8904,8 +9148,11 @@
       <c r="AC50" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD50" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="50">
         <v>51</v>
       </c>
@@ -8913,7 +9160,7 @@
         <v>468</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>436</v>
@@ -9001,8 +9248,11 @@
       <c r="AC51" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD51" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="50">
         <v>52</v>
       </c>
@@ -9010,7 +9260,7 @@
         <v>468</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>436</v>
@@ -9098,8 +9348,11 @@
       <c r="AC52" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD52" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="50">
         <v>53</v>
       </c>
@@ -9107,7 +9360,7 @@
         <v>468</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>436</v>
@@ -9195,8 +9448,11 @@
       <c r="AC53" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD53" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="50">
         <v>54</v>
       </c>
@@ -9204,7 +9460,7 @@
         <v>468</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>436</v>
@@ -9292,8 +9548,11 @@
       <c r="AC54" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD54" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="50">
         <v>55</v>
       </c>
@@ -9301,7 +9560,7 @@
         <v>468</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>436</v>
@@ -9389,8 +9648,11 @@
       <c r="AC55" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD55" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="50">
         <v>56</v>
       </c>
@@ -9398,7 +9660,7 @@
         <v>468</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>436</v>
@@ -9486,8 +9748,11 @@
       <c r="AC56" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD56" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="50">
         <v>57</v>
       </c>
@@ -9495,7 +9760,7 @@
         <v>468</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>436</v>
@@ -9583,8 +9848,11 @@
       <c r="AC57" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD57" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="50">
         <v>58</v>
       </c>
@@ -9592,7 +9860,7 @@
         <v>468</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>436</v>
@@ -9680,8 +9948,11 @@
       <c r="AC58" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD58" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="50">
         <v>59</v>
       </c>
@@ -9689,7 +9960,7 @@
         <v>468</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>436</v>
@@ -9777,8 +10048,11 @@
       <c r="AC59" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD59" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="50">
         <v>60</v>
       </c>
@@ -9786,7 +10060,7 @@
         <v>468</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>436</v>
@@ -9874,8 +10148,11 @@
       <c r="AC60" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD60" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="50">
         <v>61</v>
       </c>
@@ -9883,7 +10160,7 @@
         <v>468</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>436</v>
@@ -9971,8 +10248,11 @@
       <c r="AC61" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD61" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="50">
         <v>62</v>
       </c>
@@ -9980,7 +10260,7 @@
         <v>468</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>436</v>
@@ -10050,7 +10330,7 @@
         <v>209</v>
       </c>
       <c r="X62" s="49" t="str">
-        <f t="shared" ref="X62:X91" si="17">CONCATENATE("Key-AVAC-",A62)</f>
+        <f t="shared" ref="X62:X90" si="17">CONCATENATE("Key-AVAC-",A62)</f>
         <v>Key-AVAC-62</v>
       </c>
       <c r="Y62" s="30" t="s">
@@ -10068,8 +10348,11 @@
       <c r="AC62" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD62" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="50">
         <v>63</v>
       </c>
@@ -10077,7 +10360,7 @@
         <v>468</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>436</v>
@@ -10165,8 +10448,11 @@
       <c r="AC63" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD63" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="50">
         <v>64</v>
       </c>
@@ -10174,7 +10460,7 @@
         <v>468</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>436</v>
@@ -10262,8 +10548,11 @@
       <c r="AC64" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD64" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="50">
         <v>65</v>
       </c>
@@ -10271,7 +10560,7 @@
         <v>468</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>436</v>
@@ -10359,8 +10648,11 @@
       <c r="AC65" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD65" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="50">
         <v>66</v>
       </c>
@@ -10368,7 +10660,7 @@
         <v>468</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>436</v>
@@ -10456,8 +10748,11 @@
       <c r="AC66" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD66" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="50">
         <v>67</v>
       </c>
@@ -10465,7 +10760,7 @@
         <v>468</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>436</v>
@@ -10553,8 +10848,11 @@
       <c r="AC67" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD67" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="50">
         <v>68</v>
       </c>
@@ -10562,7 +10860,7 @@
         <v>468</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>436</v>
@@ -10650,8 +10948,11 @@
       <c r="AC68" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD68" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="50">
         <v>69</v>
       </c>
@@ -10659,7 +10960,7 @@
         <v>468</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>436</v>
@@ -10747,8 +11048,11 @@
       <c r="AC69" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD69" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="50">
         <v>70</v>
       </c>
@@ -10756,7 +11060,7 @@
         <v>468</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>436</v>
@@ -10844,8 +11148,11 @@
       <c r="AC70" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD70" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="50">
         <v>71</v>
       </c>
@@ -10853,7 +11160,7 @@
         <v>468</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>436</v>
@@ -10941,8 +11248,11 @@
       <c r="AC71" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD71" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="50">
         <v>72</v>
       </c>
@@ -10950,7 +11260,7 @@
         <v>468</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>436</v>
@@ -11038,8 +11348,11 @@
       <c r="AC72" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD72" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="50">
         <v>73</v>
       </c>
@@ -11047,7 +11360,7 @@
         <v>468</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>436</v>
@@ -11135,8 +11448,11 @@
       <c r="AC73" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD73" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="50">
         <v>74</v>
       </c>
@@ -11144,7 +11460,7 @@
         <v>468</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>436</v>
@@ -11232,8 +11548,11 @@
       <c r="AC74" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD74" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="50">
         <v>75</v>
       </c>
@@ -11241,7 +11560,7 @@
         <v>468</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>436</v>
@@ -11329,8 +11648,11 @@
       <c r="AC75" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD75" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="50">
         <v>76</v>
       </c>
@@ -11338,7 +11660,7 @@
         <v>468</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>436</v>
@@ -11426,8 +11748,11 @@
       <c r="AC76" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD76" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="50">
         <v>77</v>
       </c>
@@ -11435,7 +11760,7 @@
         <v>468</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>436</v>
@@ -11523,8 +11848,11 @@
       <c r="AC77" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD77" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="50">
         <v>78</v>
       </c>
@@ -11532,7 +11860,7 @@
         <v>468</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>436</v>
@@ -11620,8 +11948,11 @@
       <c r="AC78" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD78" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="50">
         <v>79</v>
       </c>
@@ -11629,7 +11960,7 @@
         <v>468</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>436</v>
@@ -11717,8 +12048,11 @@
       <c r="AC79" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD79" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="50">
         <v>80</v>
       </c>
@@ -11726,7 +12060,7 @@
         <v>468</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>436</v>
@@ -11814,8 +12148,11 @@
       <c r="AC80" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD80" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="50">
         <v>81</v>
       </c>
@@ -11823,7 +12160,7 @@
         <v>468</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>436</v>
@@ -11911,8 +12248,11 @@
       <c r="AC81" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD81" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="50">
         <v>82</v>
       </c>
@@ -11920,7 +12260,7 @@
         <v>468</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>436</v>
@@ -12008,8 +12348,11 @@
       <c r="AC82" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD82" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="50">
         <v>83</v>
       </c>
@@ -12017,7 +12360,7 @@
         <v>468</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>448</v>
@@ -12105,8 +12448,11 @@
       <c r="AC83" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD83" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="50">
         <v>84</v>
       </c>
@@ -12114,7 +12460,7 @@
         <v>468</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>448</v>
@@ -12202,8 +12548,11 @@
       <c r="AC84" s="30" t="s">
         <v>264</v>
       </c>
+      <c r="AD84" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="50">
         <v>85</v>
       </c>
@@ -12211,16 +12560,16 @@
         <v>559</v>
       </c>
       <c r="C85" s="61" t="s">
-        <v>560</v>
+        <v>469</v>
       </c>
       <c r="D85" s="61" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="E85" s="61" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="F85" s="61" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="G85" s="52" t="s">
         <v>9</v>
@@ -12238,52 +12587,52 @@
         <v>9</v>
       </c>
       <c r="L85" s="35" t="str">
-        <f t="shared" ref="L85:O87" si="20">SUBSTITUTE(CONCATENATE("", C85), ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" ref="L85:O86" si="20">SUBSTITUTE(CONCATENATE("", C85), ".", " ")</f>
+        <v>De Climatização</v>
       </c>
       <c r="M85" s="35" t="str">
         <f t="shared" si="20"/>
-        <v>Macros</v>
+        <v>Qualidade de Ar</v>
       </c>
       <c r="N85" s="35" t="str">
         <f t="shared" si="20"/>
-        <v>Métodos</v>
+        <v>Circulação de Ar Interior</v>
       </c>
       <c r="O85" s="35" t="str">
         <f t="shared" si="20"/>
-        <v>API Revit</v>
+        <v>Ar Aquecido</v>
       </c>
       <c r="P85" s="30" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="Q85" s="57" t="str">
-        <f t="shared" ref="Q85:Q87" si="21">_xlfn.TRANSLATE(P85,"pt","es")</f>
-        <v>Aplicación Revit</v>
+        <f t="shared" ref="Q85:Q86" si="21">_xlfn.TRANSLATE(P85,"pt","es")</f>
+        <v>Proyecto de instalación de calefacción de aire.</v>
       </c>
       <c r="R85" s="57" t="str">
-        <f t="shared" ref="R85:R87" si="22">_xlfn.TRANSLATE(P85,"pt","en")</f>
-        <v>Revit App</v>
+        <f t="shared" ref="R85:R86" si="22">_xlfn.TRANSLATE(P85,"pt","en")</f>
+        <v>Air heating installation project.</v>
       </c>
       <c r="S85" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T85" s="30" t="str">
-        <f t="shared" ref="T85:V87" si="23">SUBSTITUTE(C85, ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" ref="T85:V86" si="23">SUBSTITUTE(C85, ".", " ")</f>
+        <v>De Climatização</v>
       </c>
       <c r="U85" s="30" t="str">
         <f t="shared" si="23"/>
-        <v>Macros</v>
+        <v>Qualidade de Ar</v>
       </c>
       <c r="V85" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Métodos</v>
+        <v>Circulação de Ar Interior</v>
       </c>
       <c r="W85" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X85" s="49" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="X85:X86" si="24">CONCATENATE("Key-AVAC-",A85)</f>
         <v>Key-AVAC-85</v>
       </c>
       <c r="Y85" s="59" t="s">
@@ -12301,8 +12650,11 @@
       <c r="AC85" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AD85" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="50">
         <v>86</v>
       </c>
@@ -12313,13 +12665,13 @@
         <v>469</v>
       </c>
       <c r="D86" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="E86" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E86" s="61" t="s">
-        <v>586</v>
-      </c>
       <c r="F86" s="61" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="G86" s="52" t="s">
         <v>9</v>
@@ -12350,18 +12702,18 @@
       </c>
       <c r="O86" s="35" t="str">
         <f t="shared" si="20"/>
-        <v>Ar Aquecido</v>
+        <v>Ar Insuflado</v>
       </c>
       <c r="P86" s="30" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="Q86" s="57" t="str">
         <f t="shared" si="21"/>
-        <v>Proyecto de instalación de calefacción de aire.</v>
+        <v>Proyecto de instalación de refrigeración por aire (inflado).</v>
       </c>
       <c r="R86" s="57" t="str">
         <f t="shared" si="22"/>
-        <v>Air heating installation project.</v>
+        <v>Air cooling installation project (Inflated).</v>
       </c>
       <c r="S86" s="30" t="s">
         <v>9</v>
@@ -12382,7 +12734,7 @@
         <v>209</v>
       </c>
       <c r="X86" s="49" t="str">
-        <f t="shared" ref="X86:X87" si="24">CONCATENATE("Key-AVAC-",A86)</f>
+        <f t="shared" si="24"/>
         <v>Key-AVAC-86</v>
       </c>
       <c r="Y86" s="59" t="s">
@@ -12400,8 +12752,11 @@
       <c r="AC86" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AD86" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="50">
         <v>87</v>
       </c>
@@ -12412,13 +12767,13 @@
         <v>469</v>
       </c>
       <c r="D87" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="E87" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E87" s="61" t="s">
-        <v>586</v>
-      </c>
       <c r="F87" s="61" t="s">
-        <v>577</v>
+        <v>623</v>
       </c>
       <c r="G87" s="52" t="s">
         <v>9</v>
@@ -12436,52 +12791,52 @@
         <v>9</v>
       </c>
       <c r="L87" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="L87:L90" si="25">SUBSTITUTE(CONCATENATE("", C87), ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="M87" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="M87:M90" si="26">SUBSTITUTE(CONCATENATE("", D87), ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N87" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="N87:N90" si="27">SUBSTITUTE(CONCATENATE("", E87), ".", " ")</f>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="O87" s="35" t="str">
-        <f t="shared" si="20"/>
-        <v>Ar Insuflado</v>
+        <f t="shared" ref="O87:O90" si="28">SUBSTITUTE(CONCATENATE("", F87), ".", " ")</f>
+        <v>Ar Retornado</v>
       </c>
       <c r="P87" s="30" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Q87" s="57" t="str">
-        <f t="shared" si="21"/>
-        <v>Proyecto de instalación de refrigeración por aire (inflado).</v>
+        <f t="shared" ref="Q87:Q90" si="29">_xlfn.TRANSLATE(P87,"pt","es")</f>
+        <v>Proyecto de instalación de refrigeración por aire (Retorno).</v>
       </c>
       <c r="R87" s="57" t="str">
-        <f t="shared" si="22"/>
-        <v>Air cooling installation project (Inflated).</v>
+        <f t="shared" ref="R87:R90" si="30">_xlfn.TRANSLATE(P87,"pt","en")</f>
+        <v>Air Cooling Installation Project (Return).</v>
       </c>
       <c r="S87" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T87" s="30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="T87:T90" si="31">SUBSTITUTE(C87, ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="U87" s="30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="U87:U90" si="32">SUBSTITUTE(D87, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="V87" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="V87:V90" si="33">SUBSTITUTE(E87, ".", " ")</f>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="W87" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X87" s="49" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="17"/>
         <v>Key-AVAC-87</v>
       </c>
       <c r="Y87" s="59" t="s">
@@ -12499,8 +12854,11 @@
       <c r="AC87" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AD87" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="50">
         <v>88</v>
       </c>
@@ -12511,14 +12869,14 @@
         <v>469</v>
       </c>
       <c r="D88" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="E88" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E88" s="61" t="s">
+      <c r="F88" s="61" t="s">
         <v>586</v>
       </c>
-      <c r="F88" s="61" t="s">
-        <v>625</v>
-      </c>
       <c r="G88" s="52" t="s">
         <v>9</v>
       </c>
@@ -12535,45 +12893,45 @@
         <v>9</v>
       </c>
       <c r="L88" s="35" t="str">
-        <f t="shared" ref="L88:L91" si="25">SUBSTITUTE(CONCATENATE("", C88), ".", " ")</f>
+        <f t="shared" si="25"/>
         <v>De Climatização</v>
       </c>
       <c r="M88" s="35" t="str">
-        <f t="shared" ref="M88:M91" si="26">SUBSTITUTE(CONCATENATE("", D88), ".", " ")</f>
+        <f t="shared" si="26"/>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N88" s="35" t="str">
-        <f t="shared" ref="N88:N91" si="27">SUBSTITUTE(CONCATENATE("", E88), ".", " ")</f>
+        <f t="shared" si="27"/>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="O88" s="35" t="str">
-        <f t="shared" ref="O88:O91" si="28">SUBSTITUTE(CONCATENATE("", F88), ".", " ")</f>
-        <v>Ar Retornado</v>
+        <f t="shared" si="28"/>
+        <v>Ar Exaustão</v>
       </c>
       <c r="P88" s="30" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="Q88" s="57" t="str">
-        <f t="shared" ref="Q88:Q91" si="29">_xlfn.TRANSLATE(P88,"pt","es")</f>
-        <v>Proyecto de instalación de refrigeración por aire (Retorno).</v>
+        <f t="shared" si="29"/>
+        <v>Proyecto de instalación de escapes mecánicos.</v>
       </c>
       <c r="R88" s="57" t="str">
-        <f t="shared" ref="R88:R91" si="30">_xlfn.TRANSLATE(P88,"pt","en")</f>
-        <v>Air Cooling Installation Project (Return).</v>
+        <f t="shared" si="30"/>
+        <v>Mechanical exhaust installation project.</v>
       </c>
       <c r="S88" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T88" s="30" t="str">
-        <f t="shared" ref="T88:T91" si="31">SUBSTITUTE(C88, ".", " ")</f>
+        <f t="shared" si="31"/>
         <v>De Climatização</v>
       </c>
       <c r="U88" s="30" t="str">
-        <f t="shared" ref="U88:U91" si="32">SUBSTITUTE(D88, ".", " ")</f>
+        <f t="shared" si="32"/>
         <v>Qualidade de Ar</v>
       </c>
       <c r="V88" s="58" t="str">
-        <f t="shared" ref="V88:V91" si="33">SUBSTITUTE(E88, ".", " ")</f>
+        <f t="shared" si="33"/>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="W88" s="30" t="s">
@@ -12598,8 +12956,11 @@
       <c r="AC88" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AD88" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="50">
         <v>89</v>
       </c>
@@ -12610,13 +12971,13 @@
         <v>469</v>
       </c>
       <c r="D89" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="E89" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="E89" s="61" t="s">
-        <v>586</v>
-      </c>
       <c r="F89" s="61" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="G89" s="52" t="s">
         <v>9</v>
@@ -12634,151 +12995,154 @@
         <v>9</v>
       </c>
       <c r="L89" s="35" t="str">
+        <f t="shared" ref="L89" si="34">SUBSTITUTE(CONCATENATE("", C89), ".", " ")</f>
+        <v>De Climatização</v>
+      </c>
+      <c r="M89" s="35" t="str">
+        <f t="shared" ref="M89" si="35">SUBSTITUTE(CONCATENATE("", D89), ".", " ")</f>
+        <v>Qualidade de Ar</v>
+      </c>
+      <c r="N89" s="35" t="str">
+        <f t="shared" ref="N89" si="36">SUBSTITUTE(CONCATENATE("", E89), ".", " ")</f>
+        <v>Circulação de Ar Interior</v>
+      </c>
+      <c r="O89" s="35" t="str">
+        <f t="shared" ref="O89" si="37">SUBSTITUTE(CONCATENATE("", F89), ".", " ")</f>
+        <v>Ar Ventilação</v>
+      </c>
+      <c r="P89" s="30" t="s">
+        <v>573</v>
+      </c>
+      <c r="Q89" s="57" t="str">
+        <f t="shared" ref="Q89" si="38">_xlfn.TRANSLATE(P89,"pt","es")</f>
+        <v>Proyecto de instalación de ventilación del aire interior.</v>
+      </c>
+      <c r="R89" s="57" t="str">
+        <f t="shared" ref="R89" si="39">_xlfn.TRANSLATE(P89,"pt","en")</f>
+        <v>Indoor air ventilation installation project.</v>
+      </c>
+      <c r="S89" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T89" s="30" t="str">
+        <f t="shared" ref="T89" si="40">SUBSTITUTE(C89, ".", " ")</f>
+        <v>De Climatização</v>
+      </c>
+      <c r="U89" s="30" t="str">
+        <f t="shared" ref="U89" si="41">SUBSTITUTE(D89, ".", " ")</f>
+        <v>Qualidade de Ar</v>
+      </c>
+      <c r="V89" s="58" t="str">
+        <f t="shared" ref="V89" si="42">SUBSTITUTE(E89, ".", " ")</f>
+        <v>Circulação de Ar Interior</v>
+      </c>
+      <c r="W89" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="X89" s="49" t="str">
+        <f t="shared" ref="X89" si="43">CONCATENATE("Key-AVAC-",A89)</f>
+        <v>Key-AVAC-89</v>
+      </c>
+      <c r="Y89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC89" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD89" s="59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="50">
+        <v>90</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C90" s="61" t="s">
+        <v>469</v>
+      </c>
+      <c r="D90" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="E90" s="61" t="s">
+        <v>584</v>
+      </c>
+      <c r="F90" s="61" t="s">
+        <v>576</v>
+      </c>
+      <c r="G90" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H90" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I90" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J90" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K90" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L90" s="35" t="str">
         <f t="shared" si="25"/>
         <v>De Climatização</v>
       </c>
-      <c r="M89" s="35" t="str">
+      <c r="M90" s="35" t="str">
         <f t="shared" si="26"/>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="N89" s="35" t="str">
+      <c r="N90" s="35" t="str">
         <f t="shared" si="27"/>
         <v>Circulação de Ar Interior</v>
       </c>
-      <c r="O89" s="35" t="str">
+      <c r="O90" s="35" t="str">
         <f t="shared" si="28"/>
-        <v>Ar Exaustão</v>
-      </c>
-      <c r="P89" s="30" t="s">
-        <v>565</v>
-      </c>
-      <c r="Q89" s="57" t="str">
+        <v>Ar Filtrado Interno</v>
+      </c>
+      <c r="P90" s="30" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q90" s="57" t="str">
         <f t="shared" si="29"/>
-        <v>Proyecto de instalación de escapes mecánicos.</v>
-      </c>
-      <c r="R89" s="57" t="str">
+        <v>Proyecto de instalación de filtración de aire interior.</v>
+      </c>
+      <c r="R90" s="57" t="str">
         <f t="shared" si="30"/>
-        <v>Mechanical exhaust installation project.</v>
-      </c>
-      <c r="S89" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T89" s="30" t="str">
+        <v>Indoor air filtration installation project.</v>
+      </c>
+      <c r="S90" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T90" s="30" t="str">
         <f t="shared" si="31"/>
         <v>De Climatização</v>
       </c>
-      <c r="U89" s="30" t="str">
+      <c r="U90" s="30" t="str">
         <f t="shared" si="32"/>
         <v>Qualidade de Ar</v>
       </c>
-      <c r="V89" s="58" t="str">
+      <c r="V90" s="58" t="str">
         <f t="shared" si="33"/>
         <v>Circulação de Ar Interior</v>
       </c>
-      <c r="W89" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="X89" s="49" t="str">
-        <f t="shared" si="17"/>
-        <v>Key-AVAC-89</v>
-      </c>
-      <c r="Y89" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z89" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA89" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB89" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC89" s="59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="50">
-        <v>90</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="C90" s="61" t="s">
-        <v>469</v>
-      </c>
-      <c r="D90" s="61" t="s">
-        <v>584</v>
-      </c>
-      <c r="E90" s="61" t="s">
-        <v>586</v>
-      </c>
-      <c r="F90" s="61" t="s">
-        <v>573</v>
-      </c>
-      <c r="G90" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H90" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I90" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J90" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K90" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L90" s="35" t="str">
-        <f t="shared" ref="L90" si="34">SUBSTITUTE(CONCATENATE("", C90), ".", " ")</f>
-        <v>De Climatização</v>
-      </c>
-      <c r="M90" s="35" t="str">
-        <f t="shared" ref="M90" si="35">SUBSTITUTE(CONCATENATE("", D90), ".", " ")</f>
-        <v>Qualidade de Ar</v>
-      </c>
-      <c r="N90" s="35" t="str">
-        <f t="shared" ref="N90" si="36">SUBSTITUTE(CONCATENATE("", E90), ".", " ")</f>
-        <v>Circulação de Ar Interior</v>
-      </c>
-      <c r="O90" s="35" t="str">
-        <f t="shared" ref="O90" si="37">SUBSTITUTE(CONCATENATE("", F90), ".", " ")</f>
-        <v>Ar Ventilação</v>
-      </c>
-      <c r="P90" s="30" t="s">
-        <v>575</v>
-      </c>
-      <c r="Q90" s="57" t="str">
-        <f t="shared" ref="Q90" si="38">_xlfn.TRANSLATE(P90,"pt","es")</f>
-        <v>Proyecto de instalación de ventilación del aire interior.</v>
-      </c>
-      <c r="R90" s="57" t="str">
-        <f t="shared" ref="R90" si="39">_xlfn.TRANSLATE(P90,"pt","en")</f>
-        <v>Indoor air ventilation installation project.</v>
-      </c>
-      <c r="S90" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T90" s="30" t="str">
-        <f t="shared" ref="T90" si="40">SUBSTITUTE(C90, ".", " ")</f>
-        <v>De Climatização</v>
-      </c>
-      <c r="U90" s="30" t="str">
-        <f t="shared" ref="U90" si="41">SUBSTITUTE(D90, ".", " ")</f>
-        <v>Qualidade de Ar</v>
-      </c>
-      <c r="V90" s="58" t="str">
-        <f t="shared" ref="V90" si="42">SUBSTITUTE(E90, ".", " ")</f>
-        <v>Circulação de Ar Interior</v>
-      </c>
       <c r="W90" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X90" s="49" t="str">
-        <f t="shared" ref="X90" si="43">CONCATENATE("Key-AVAC-",A90)</f>
+        <f t="shared" si="17"/>
         <v>Key-AVAC-90</v>
       </c>
       <c r="Y90" s="59" t="s">
@@ -12796,8 +13160,11 @@
       <c r="AC90" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AD90" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="50">
         <v>91</v>
       </c>
@@ -12808,13 +13175,13 @@
         <v>469</v>
       </c>
       <c r="D91" s="61" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E91" s="61" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="F91" s="61" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G91" s="52" t="s">
         <v>9</v>
@@ -12832,52 +13199,52 @@
         <v>9</v>
       </c>
       <c r="L91" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="L91" si="44">SUBSTITUTE(CONCATENATE("", C91), ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="M91" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="M91" si="45">SUBSTITUTE(CONCATENATE("", D91), ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N91" s="35" t="str">
-        <f t="shared" si="27"/>
-        <v>Circulação de Ar Interior</v>
+        <f t="shared" ref="N91" si="46">SUBSTITUTE(CONCATENATE("", E91), ".", " ")</f>
+        <v>Captação de Ar Exterior</v>
       </c>
       <c r="O91" s="35" t="str">
-        <f t="shared" si="28"/>
-        <v>Ar Filtrado Interno</v>
+        <f t="shared" ref="O91" si="47">SUBSTITUTE(CONCATENATE("", F91), ".", " ")</f>
+        <v>Ar Filtrado Externo</v>
       </c>
       <c r="P91" s="30" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="Q91" s="57" t="str">
-        <f t="shared" si="29"/>
-        <v>Proyecto de instalación de filtración de aire interior.</v>
+        <f t="shared" ref="Q91" si="48">_xlfn.TRANSLATE(P91,"pt","es")</f>
+        <v>Proyecto de instalación de filtración de aire exterior.</v>
       </c>
       <c r="R91" s="57" t="str">
-        <f t="shared" si="30"/>
-        <v>Indoor air filtration installation project.</v>
+        <f t="shared" ref="R91" si="49">_xlfn.TRANSLATE(P91,"pt","en")</f>
+        <v>Outdoor air filtration installation project.</v>
       </c>
       <c r="S91" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T91" s="30" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="T91" si="50">SUBSTITUTE(C91, ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="U91" s="30" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="U91" si="51">SUBSTITUTE(D91, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="V91" s="58" t="str">
-        <f t="shared" si="33"/>
-        <v>Circulação de Ar Interior</v>
+        <f t="shared" ref="V91" si="52">SUBSTITUTE(E91, ".", " ")</f>
+        <v>Captação de Ar Exterior</v>
       </c>
       <c r="W91" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X91" s="49" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="X91:X97" si="53">CONCATENATE("Key-AVAC-",A91)</f>
         <v>Key-AVAC-91</v>
       </c>
       <c r="Y91" s="59" t="s">
@@ -12895,8 +13262,11 @@
       <c r="AC91" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AD91" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="50">
         <v>92</v>
       </c>
@@ -12907,14 +13277,14 @@
         <v>469</v>
       </c>
       <c r="D92" s="61" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E92" s="61" t="s">
+        <v>583</v>
+      </c>
+      <c r="F92" s="61" t="s">
         <v>585</v>
       </c>
-      <c r="F92" s="61" t="s">
-        <v>579</v>
-      </c>
       <c r="G92" s="52" t="s">
         <v>9</v>
       </c>
@@ -12931,52 +13301,52 @@
         <v>9</v>
       </c>
       <c r="L92" s="35" t="str">
-        <f t="shared" ref="L92" si="44">SUBSTITUTE(CONCATENATE("", C92), ".", " ")</f>
+        <f t="shared" ref="L92:O97" si="54">SUBSTITUTE(CONCATENATE("", C92), ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="M92" s="35" t="str">
-        <f t="shared" ref="M92" si="45">SUBSTITUTE(CONCATENATE("", D92), ".", " ")</f>
+        <f t="shared" ref="M92" si="55">SUBSTITUTE(CONCATENATE("", D92), ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N92" s="35" t="str">
-        <f t="shared" ref="N92" si="46">SUBSTITUTE(CONCATENATE("", E92), ".", " ")</f>
+        <f t="shared" ref="N92" si="56">SUBSTITUTE(CONCATENATE("", E92), ".", " ")</f>
         <v>Captação de Ar Exterior</v>
       </c>
       <c r="O92" s="35" t="str">
-        <f t="shared" ref="O92" si="47">SUBSTITUTE(CONCATENATE("", F92), ".", " ")</f>
-        <v>Ar Filtrado Externo</v>
+        <f t="shared" ref="O92" si="57">SUBSTITUTE(CONCATENATE("", F92), ".", " ")</f>
+        <v>Ar Captador</v>
       </c>
       <c r="P92" s="30" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="Q92" s="57" t="str">
-        <f t="shared" ref="Q92" si="48">_xlfn.TRANSLATE(P92,"pt","es")</f>
-        <v>Proyecto de instalación de filtración de aire exterior.</v>
+        <f t="shared" ref="Q92" si="58">_xlfn.TRANSLATE(P92,"pt","es")</f>
+        <v>Proyecto de instalación de la toma de aire exterior.</v>
       </c>
       <c r="R92" s="57" t="str">
-        <f t="shared" ref="R92" si="49">_xlfn.TRANSLATE(P92,"pt","en")</f>
-        <v>Outdoor air filtration installation project.</v>
+        <f t="shared" ref="R92" si="59">_xlfn.TRANSLATE(P92,"pt","en")</f>
+        <v>Outdoor air intake installation project.</v>
       </c>
       <c r="S92" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T92" s="30" t="str">
-        <f t="shared" ref="T92" si="50">SUBSTITUTE(C92, ".", " ")</f>
+        <f t="shared" ref="T92:V97" si="60">SUBSTITUTE(C92, ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="U92" s="30" t="str">
-        <f t="shared" ref="U92" si="51">SUBSTITUTE(D92, ".", " ")</f>
+        <f t="shared" ref="U92" si="61">SUBSTITUTE(D92, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="V92" s="58" t="str">
-        <f t="shared" ref="V92" si="52">SUBSTITUTE(E92, ".", " ")</f>
+        <f t="shared" ref="V92" si="62">SUBSTITUTE(E92, ".", " ")</f>
         <v>Captação de Ar Exterior</v>
       </c>
       <c r="W92" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X92" s="49" t="str">
-        <f t="shared" ref="X92" si="53">CONCATENATE("Key-AVAC-",A92)</f>
+        <f t="shared" si="53"/>
         <v>Key-AVAC-92</v>
       </c>
       <c r="Y92" s="59" t="s">
@@ -12994,8 +13364,11 @@
       <c r="AC92" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AD92" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="50">
         <v>93</v>
       </c>
@@ -13003,16 +13376,16 @@
         <v>559</v>
       </c>
       <c r="C93" s="61" t="s">
-        <v>469</v>
+        <v>560</v>
       </c>
       <c r="D93" s="61" t="s">
-        <v>584</v>
+        <v>562</v>
       </c>
       <c r="E93" s="61" t="s">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="F93" s="61" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="G93" s="52" t="s">
         <v>9</v>
@@ -13030,52 +13403,50 @@
         <v>9</v>
       </c>
       <c r="L93" s="35" t="str">
-        <f t="shared" ref="L93" si="54">SUBSTITUTE(CONCATENATE("", C93), ".", " ")</f>
-        <v>De Climatização</v>
+        <f t="shared" si="54"/>
+        <v>De API</v>
       </c>
       <c r="M93" s="35" t="str">
-        <f t="shared" ref="M93" si="55">SUBSTITUTE(CONCATENATE("", D93), ".", " ")</f>
-        <v>Qualidade de Ar</v>
+        <f t="shared" si="54"/>
+        <v>Macros</v>
       </c>
       <c r="N93" s="35" t="str">
-        <f t="shared" ref="N93" si="56">SUBSTITUTE(CONCATENATE("", E93), ".", " ")</f>
-        <v>Captação de Ar Exterior</v>
+        <f t="shared" si="54"/>
+        <v>Métodos</v>
       </c>
       <c r="O93" s="35" t="str">
-        <f t="shared" ref="O93" si="57">SUBSTITUTE(CONCATENATE("", F93), ".", " ")</f>
-        <v>Ar Captador</v>
+        <f t="shared" si="54"/>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P93" s="30" t="s">
-        <v>583</v>
-      </c>
-      <c r="Q93" s="57" t="str">
-        <f t="shared" ref="Q93" si="58">_xlfn.TRANSLATE(P93,"pt","es")</f>
-        <v>Proyecto de instalación de la toma de aire exterior.</v>
-      </c>
-      <c r="R93" s="57" t="str">
-        <f t="shared" ref="R93" si="59">_xlfn.TRANSLATE(P93,"pt","en")</f>
-        <v>Outdoor air intake installation project.</v>
+        <v>625</v>
+      </c>
+      <c r="Q93" s="30" t="s">
+        <v>626</v>
+      </c>
+      <c r="R93" s="30" t="s">
+        <v>627</v>
       </c>
       <c r="S93" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T93" s="30" t="str">
-        <f t="shared" ref="T93" si="60">SUBSTITUTE(C93, ".", " ")</f>
-        <v>De Climatização</v>
+        <f t="shared" si="60"/>
+        <v>De API</v>
       </c>
       <c r="U93" s="30" t="str">
-        <f t="shared" ref="U93" si="61">SUBSTITUTE(D93, ".", " ")</f>
-        <v>Qualidade de Ar</v>
+        <f t="shared" si="60"/>
+        <v>Macros</v>
       </c>
       <c r="V93" s="58" t="str">
-        <f t="shared" ref="V93" si="62">SUBSTITUTE(E93, ".", " ")</f>
-        <v>Captação de Ar Exterior</v>
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
       </c>
       <c r="W93" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X93" s="49" t="str">
-        <f t="shared" ref="X93" si="63">CONCATENATE("Key-AVAC-",A93)</f>
+        <f t="shared" si="53"/>
         <v>Key-AVAC-93</v>
       </c>
       <c r="Y93" s="59" t="s">
@@ -13091,143 +13462,557 @@
         <v>9</v>
       </c>
       <c r="AC93" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD93" s="59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="50">
+        <v>94</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C94" s="61" t="s">
+        <v>560</v>
+      </c>
+      <c r="D94" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="E94" s="61" t="s">
+        <v>561</v>
+      </c>
+      <c r="F94" s="61" t="s">
+        <v>628</v>
+      </c>
+      <c r="G94" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H94" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I94" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J94" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K94" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L94" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>De API</v>
+      </c>
+      <c r="M94" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Macros</v>
+      </c>
+      <c r="N94" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O94" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P94" s="30" t="s">
+        <v>629</v>
+      </c>
+      <c r="Q94" s="30" t="s">
+        <v>630</v>
+      </c>
+      <c r="R94" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="S94" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T94" s="30" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="U94" s="30" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="V94" s="58" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W94" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="X94" s="49" t="str">
+        <f t="shared" si="53"/>
+        <v>Key-AVAC-94</v>
+      </c>
+      <c r="Y94" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z94" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA94" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB94" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC94" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD94" s="59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="50">
+        <v>95</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C95" s="61" t="s">
+        <v>560</v>
+      </c>
+      <c r="D95" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="E95" s="61" t="s">
+        <v>561</v>
+      </c>
+      <c r="F95" s="61" t="s">
+        <v>632</v>
+      </c>
+      <c r="G95" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H95" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I95" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J95" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K95" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L95" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>De API</v>
+      </c>
+      <c r="M95" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Macros</v>
+      </c>
+      <c r="N95" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O95" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P95" s="30" t="s">
+        <v>633</v>
+      </c>
+      <c r="Q95" s="30" t="s">
+        <v>634</v>
+      </c>
+      <c r="R95" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="S95" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T95" s="30" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="U95" s="30" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="V95" s="58" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W95" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="X95" s="49" t="str">
+        <f t="shared" si="53"/>
+        <v>Key-AVAC-95</v>
+      </c>
+      <c r="Y95" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z95" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA95" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB95" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC95" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD95" s="59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="50">
+        <v>96</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C96" s="61" t="s">
+        <v>560</v>
+      </c>
+      <c r="D96" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="E96" s="61" t="s">
+        <v>561</v>
+      </c>
+      <c r="F96" s="61" t="s">
+        <v>636</v>
+      </c>
+      <c r="G96" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H96" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I96" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J96" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K96" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L96" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>De API</v>
+      </c>
+      <c r="M96" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Macros</v>
+      </c>
+      <c r="N96" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O96" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P96" s="30" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q96" s="30" t="s">
+        <v>638</v>
+      </c>
+      <c r="R96" s="30" t="s">
+        <v>639</v>
+      </c>
+      <c r="S96" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T96" s="30" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="U96" s="30" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="V96" s="58" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W96" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="X96" s="49" t="str">
+        <f t="shared" si="53"/>
+        <v>Key-AVAC-96</v>
+      </c>
+      <c r="Y96" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z96" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA96" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB96" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC96" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD96" s="59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="50">
+        <v>97</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C97" s="61" t="s">
+        <v>560</v>
+      </c>
+      <c r="D97" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="E97" s="61" t="s">
+        <v>640</v>
+      </c>
+      <c r="F97" s="61" t="s">
+        <v>641</v>
+      </c>
+      <c r="G97" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H97" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I97" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J97" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K97" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L97" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>De API</v>
+      </c>
+      <c r="M97" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Macros</v>
+      </c>
+      <c r="N97" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O97" s="35" t="str">
+        <f t="shared" si="54"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P97" s="30" t="s">
+        <v>642</v>
+      </c>
+      <c r="Q97" s="30" t="s">
+        <v>643</v>
+      </c>
+      <c r="R97" s="30" t="s">
+        <v>644</v>
+      </c>
+      <c r="S97" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T97" s="30" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="U97" s="30" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="V97" s="58" t="str">
+        <f t="shared" si="60"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W97" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="X97" s="49" t="str">
+        <f t="shared" si="53"/>
+        <v>Key-AVAC-97</v>
+      </c>
+      <c r="Y97" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z97" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA97" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB97" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC97" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD97" s="59" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A93 B85:B93">
-    <cfRule type="cellIs" dxfId="80" priority="18" operator="equal">
+  <conditionalFormatting sqref="A2:A97">
+    <cfRule type="cellIs" dxfId="83" priority="21" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85:B97">
+    <cfRule type="cellIs" dxfId="82" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:F82 L50:Q82 T50:V82 Y50:Y82 AA50:AA82 E83:E84">
-    <cfRule type="cellIs" dxfId="79" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="53" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E97:F97">
+    <cfRule type="duplicateValues" dxfId="80" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="78" priority="2333"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="2336"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4">
-    <cfRule type="duplicateValues" dxfId="77" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F15">
-    <cfRule type="duplicateValues" dxfId="75" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F43 F47:F84">
-    <cfRule type="duplicateValues" dxfId="74" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F17 F83:F84">
-    <cfRule type="duplicateValues" dxfId="73" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F17">
-    <cfRule type="duplicateValues" dxfId="72" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F24">
-    <cfRule type="duplicateValues" dxfId="71" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F26">
-    <cfRule type="duplicateValues" dxfId="67" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F28">
-    <cfRule type="duplicateValues" dxfId="65" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F43">
-    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F43">
-    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F44:F46 L44:R46 T44:V46 Y44:Y46 AA44:AA46 AD44:XFD46">
-    <cfRule type="cellIs" dxfId="58" priority="22" operator="equal">
+  <conditionalFormatting sqref="F44:F46 L44:R46 T44:V46 Y44:Y46 AA44:AA46 AE44:XFD46">
+    <cfRule type="cellIs" dxfId="59" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:F46">
-    <cfRule type="duplicateValues" dxfId="57" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="27"/>
     <cfRule type="duplicateValues" dxfId="54" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47:F49">
-    <cfRule type="duplicateValues" dxfId="47" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50:F82">
-    <cfRule type="duplicateValues" dxfId="40" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84 F5:F43 F47:F49">
-    <cfRule type="duplicateValues" dxfId="34" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84 F16:F26">
-    <cfRule type="duplicateValues" dxfId="33" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F84">
-    <cfRule type="duplicateValues" dxfId="32" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F85:F93">
-    <cfRule type="duplicateValues" dxfId="31" priority="2347"/>
+  <conditionalFormatting sqref="F85:F92">
+    <cfRule type="duplicateValues" dxfId="32" priority="2371"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F94:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="30" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="2335"/>
+  <conditionalFormatting sqref="F93:F96">
+    <cfRule type="duplicateValues" dxfId="31" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F94:F1048576 F1:F84">
-    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="20"/>
+  <conditionalFormatting sqref="F98:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="30" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="2338"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F94:F1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="2338"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="2340"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2341"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2342"/>
+  <conditionalFormatting sqref="F98:F1048576 F1:F84">
+    <cfRule type="duplicateValues" dxfId="28" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q85:Q93">
-    <cfRule type="duplicateValues" dxfId="22" priority="2353"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2354"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="2355"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="2356"/>
+  <conditionalFormatting sqref="F98:F1048576">
+    <cfRule type="duplicateValues" dxfId="26" priority="2341"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2343"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2344"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2345"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q85:Q92">
+    <cfRule type="duplicateValues" dxfId="22" priority="2376"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2377"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2378"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R43 R47:R84">
-    <cfRule type="cellIs" dxfId="17" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R85:R93">
-    <cfRule type="duplicateValues" dxfId="16" priority="2361"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2362"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="2363"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2364"/>
+  <conditionalFormatting sqref="R85:R92">
+    <cfRule type="duplicateValues" dxfId="16" priority="2380"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2381"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2382"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2383"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -13237,15 +14022,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.3046875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.15234375" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.53515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="1.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="15.45" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -13310,7 +14095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -13375,7 +14160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -13458,15 +14243,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.15234375" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -13489,7 +14274,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -13542,37 +14327,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AI10"/>
-  <sheetFormatPr defaultColWidth="64.3046875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="64.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.84375" customWidth="1"/>
-    <col min="4" max="4" width="7.3828125" customWidth="1"/>
-    <col min="5" max="5" width="5.3828125" customWidth="1"/>
-    <col min="6" max="6" width="4.84375" customWidth="1"/>
-    <col min="7" max="7" width="37.15234375" customWidth="1"/>
-    <col min="8" max="8" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.84375" customWidth="1"/>
-    <col min="10" max="10" width="4.53515625" style="46" customWidth="1"/>
-    <col min="11" max="11" width="11.84375" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.69140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.3046875" style="46" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.53515625" customWidth="1"/>
-    <col min="16" max="16" width="7.3046875" style="46" customWidth="1"/>
-    <col min="17" max="17" width="6.15234375" customWidth="1"/>
-    <col min="18" max="18" width="6.84375" customWidth="1"/>
-    <col min="19" max="19" width="44.15234375" customWidth="1"/>
-    <col min="20" max="20" width="5.3046875" customWidth="1"/>
-    <col min="21" max="21" width="62.69140625" customWidth="1"/>
-    <col min="22" max="22" width="5.84375" customWidth="1"/>
-    <col min="23" max="23" width="7.84375" customWidth="1"/>
-    <col min="24" max="24" width="6.69140625" customWidth="1"/>
-    <col min="25" max="25" width="7.69140625" customWidth="1"/>
-    <col min="26" max="35" width="2.84375" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" customWidth="1"/>
+    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" style="46" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" style="46" customWidth="1"/>
+    <col min="17" max="17" width="6.140625" customWidth="1"/>
+    <col min="18" max="18" width="6.85546875" customWidth="1"/>
+    <col min="19" max="19" width="44.140625" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" customWidth="1"/>
+    <col min="21" max="21" width="62.7109375" customWidth="1"/>
+    <col min="22" max="22" width="5.85546875" customWidth="1"/>
+    <col min="23" max="23" width="7.85546875" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="35" width="2.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="46" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:35" s="46" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -13679,7 +14464,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -13708,10 +14493,10 @@
         <v>165</v>
       </c>
       <c r="J2" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K2" s="23" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L2" s="37" t="s">
         <v>74</v>
@@ -13786,15 +14571,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>3</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D3" s="39" t="s">
         <v>167</v>
@@ -13806,37 +14591,37 @@
         <v>73</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H3" s="37" t="s">
         <v>76</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J3" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K3" s="21" t="s">
+        <v>617</v>
+      </c>
+      <c r="L3" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="62" t="s">
         <v>619</v>
       </c>
-      <c r="L3" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="62" t="s">
+      <c r="Q3" s="23" t="s">
         <v>621</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>623</v>
       </c>
       <c r="R3" s="38" t="s">
         <v>207</v>
@@ -13893,15 +14678,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>4</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D4" s="39" t="s">
         <v>167</v>
@@ -13913,37 +14698,37 @@
         <v>73</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H4" s="37" t="s">
         <v>76</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J4" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K4" s="21" t="s">
+        <v>617</v>
+      </c>
+      <c r="L4" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="62" t="s">
         <v>619</v>
       </c>
-      <c r="L4" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="62" t="s">
-        <v>621</v>
-      </c>
       <c r="Q4" s="23" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="R4" s="38" t="s">
         <v>207</v>
@@ -14000,15 +14785,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:35" s="45" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>5</v>
       </c>
       <c r="B5" s="67" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D5" s="39" t="s">
         <v>167</v>
@@ -14020,19 +14805,19 @@
         <v>73</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="H5" s="37" t="s">
         <v>76</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J5" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="L5" s="62" t="s">
         <v>9</v>
@@ -14047,10 +14832,10 @@
         <v>9</v>
       </c>
       <c r="P5" s="62" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="R5" s="38" t="s">
         <v>207</v>
@@ -14107,15 +14892,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>6</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>596</v>
-      </c>
-      <c r="C6" s="61" t="s">
-        <v>563</v>
+        <v>594</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>636</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>9</v>
@@ -14127,20 +14912,20 @@
         <v>73</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H6" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I6" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="J6" s="62" t="s">
+        <v>596</v>
+      </c>
+      <c r="K6" s="23" t="s">
         <v>597</v>
       </c>
-      <c r="J6" s="62" t="s">
-        <v>598</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>599</v>
-      </c>
       <c r="L6" s="62" t="s">
         <v>9</v>
       </c>
@@ -14148,10 +14933,10 @@
         <v>9</v>
       </c>
       <c r="N6" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="P6" s="37" t="s">
         <v>9</v>
@@ -14182,7 +14967,7 @@
         <v>método.revit</v>
       </c>
       <c r="Y6" s="65" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="Z6" s="39" t="s">
         <v>9</v>
@@ -14215,15 +15000,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>7</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>602</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>563</v>
+        <v>600</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>636</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>9</v>
@@ -14235,19 +15020,19 @@
         <v>73</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H7" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J7" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="L7" s="62" t="s">
         <v>9</v>
@@ -14256,10 +15041,10 @@
         <v>9</v>
       </c>
       <c r="N7" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="P7" s="37" t="s">
         <v>9</v>
@@ -14290,7 +15075,7 @@
         <v>método.revit</v>
       </c>
       <c r="Y7" s="65" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Z7" s="39" t="s">
         <v>9</v>
@@ -14323,15 +15108,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>606</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>563</v>
+        <v>604</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>636</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>9</v>
@@ -14343,19 +15128,19 @@
         <v>73</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H8" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J8" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="L8" s="62" t="s">
         <v>9</v>
@@ -14364,10 +15149,10 @@
         <v>9</v>
       </c>
       <c r="N8" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="P8" s="37" t="s">
         <v>9</v>
@@ -14398,7 +15183,7 @@
         <v>método.revit</v>
       </c>
       <c r="Y8" s="65" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Z8" s="39" t="s">
         <v>9</v>
@@ -14431,15 +15216,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>9</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>610</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>563</v>
+        <v>608</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>636</v>
       </c>
       <c r="D9" s="39" t="s">
         <v>9</v>
@@ -14451,19 +15236,19 @@
         <v>73</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H9" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J9" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="L9" s="62" t="s">
         <v>9</v>
@@ -14472,10 +15257,10 @@
         <v>9</v>
       </c>
       <c r="N9" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="P9" s="37" t="s">
         <v>9</v>
@@ -14506,7 +15291,7 @@
         <v>método.revit</v>
       </c>
       <c r="Y9" s="65" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="Z9" s="39" t="s">
         <v>9</v>
@@ -14539,15 +15324,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>10</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>614</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>563</v>
+        <v>612</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>636</v>
       </c>
       <c r="D10" s="39" t="s">
         <v>9</v>
@@ -14559,19 +15344,19 @@
         <v>73</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H10" s="62" t="s">
         <v>76</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J10" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="L10" s="62" t="s">
         <v>9</v>
@@ -14580,10 +15365,10 @@
         <v>9</v>
       </c>
       <c r="N10" s="62" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="P10" s="37" t="s">
         <v>9</v>
@@ -14614,7 +15399,7 @@
         <v>método.revit</v>
       </c>
       <c r="Y10" s="65" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="Z10" s="39" t="s">
         <v>9</v>
@@ -14650,20 +15435,20 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B3:B5 D3:F5">
-    <cfRule type="cellIs" dxfId="5" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B5">
-    <cfRule type="duplicateValues" dxfId="4" priority="2248"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B10">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2 I3:I5 R3:W5 AJ3:XFD5">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Avac.xlsx
+++ b/Versão5/SIS/Ontologia_Avac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF2AC5E-93C3-4A96-A0D9-F6169DFA0094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59502758-D1F5-44D3-A69B-AAD1BEDDB0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2977" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="749">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2249,6 +2249,75 @@
   </si>
   <si>
     <t>[ OST_Materials : OST_PipeMaterials : OST_DuctInsulations : OST_DuctLinings : OST_FabricationDuctwork ]</t>
+  </si>
+  <si>
+    <t>Used in centralized systems and chillers for conducting chilled water and condensing water in larger diameters, due to low large-scale cost and high mechanical strength.</t>
+  </si>
+  <si>
+    <t>Used as the most common sheet metal for the fabrication of air distribution ducts. Zinc coating protects steel from rust in standard indoor environments.</t>
+  </si>
+  <si>
+    <t>Used in industrial, pharmaceutical or food facilities that require extreme corrosion resistance, as well as high hygiene and long durability.</t>
+  </si>
+  <si>
+    <t>Used when there is a need for light ducts or in environments with higher humidity and corrosive agents (such as coastal regions or laboratories).</t>
+  </si>
+  <si>
+    <t>Used as standard material for grilles, diffusers and outdoor air intakes for durability and ease of finishing.</t>
+  </si>
+  <si>
+    <t>Used in angles, tie rods and fixing brackets to absorb vibrations from compressors and fans, preventing the transmission of noise to the building structure.</t>
+  </si>
+  <si>
+    <t>Used as flexible closed cell structure material applied in the insulation of refrigerant and chilled water pipelines. Avoids surface condensation and loss of efficiency.</t>
+  </si>
+  <si>
+    <t>Used as a material for refrigerant piping (liquid and suction lines). It has excellent thermal conductivity, high resistance to internal corrosion, and good malleability for bending and silver/foscoper welding.</t>
+  </si>
+  <si>
+    <t>Used as boards composed of polyurethane or polyisocyanurate coated with aluminum sheets on both sides. They replace the traditional metal duct, adding thermal insulation to the panel itself and reducing structural weight.</t>
+  </si>
+  <si>
+    <t>Used as rigid or flexible blankets applied around metal ducts or large pipes for thermal and acoustic insulation, fire resistance.</t>
+  </si>
+  <si>
+    <t>Used in aluminum spirals wrapped by glass wool and outer plastic film, used in the final connections between rigid ducts and air diffusers.</t>
+  </si>
+  <si>
+    <t>Used as a flexible sealant, resistant to temperature and humidity. Applied at the junction of ducts and pipe passages to prevent air leaks.</t>
+  </si>
+  <si>
+    <t>Used for the manufacture of grilles, diffusers and external air outlets for its durability and ease of finishing.</t>
+  </si>
+  <si>
+    <t>Used in pre-insulated piping or gap filling in thermal assemblies to prevent heat exchange.</t>
+  </si>
+  <si>
+    <t>Used to conduct chilled or hot water and in condensate drain lines, as they are immune to corrosion and prevent internal fouling.</t>
+  </si>
+  <si>
+    <t>Air heating installation project.</t>
+  </si>
+  <si>
+    <t>Air cooling installation project (Inflated).</t>
+  </si>
+  <si>
+    <t>Air Cooling Installation Project (Return).</t>
+  </si>
+  <si>
+    <t>Mechanical exhaust installation project.</t>
+  </si>
+  <si>
+    <t>Indoor air ventilation installation project.</t>
+  </si>
+  <si>
+    <t>Indoor air filtration installation project.</t>
+  </si>
+  <si>
+    <t>Outdoor air filtration installation project.</t>
+  </si>
+  <si>
+    <t>Outdoor air intake installation project.</t>
   </si>
 </sst>
 </file>
@@ -3717,7 +3786,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46270.887375694445</v>
+        <v>46270.894008564814</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>200</v>
@@ -4898,11 +4967,12 @@
       <c r="P11" s="71" t="s">
         <v>705</v>
       </c>
-      <c r="Q11" s="30" t="s">
-        <v>689</v>
+      <c r="Q11" s="30" t="str">
+        <f>_xlfn.TRANSLATE(P11,"pt","es")</f>
+        <v>Se utiliza en sistemas centralizados y enfriadores para conducir agua fría y condensar agua en diámetros mayores, debido a su bajo coste a gran escala y alta resistencia mecánica.</v>
       </c>
       <c r="R11" s="30" t="s">
-        <v>690</v>
+        <v>726</v>
       </c>
       <c r="S11" s="30" t="s">
         <v>9</v>
@@ -4998,11 +5068,12 @@
       <c r="P12" s="71" t="s">
         <v>704</v>
       </c>
-      <c r="Q12" s="30" t="s">
-        <v>689</v>
+      <c r="Q12" s="30" t="str">
+        <f t="shared" ref="Q12:R28" si="3">_xlfn.TRANSLATE(P12,"pt","es")</f>
+        <v>Se utiliza como la chapa metálica más común para la fabricación de conductos de distribución de aire. El recubrimiento de zinc protege el acero del óxido en ambientes interiores estándar.</v>
       </c>
       <c r="R12" s="30" t="s">
-        <v>690</v>
+        <v>727</v>
       </c>
       <c r="S12" s="30" t="s">
         <v>9</v>
@@ -5098,11 +5169,12 @@
       <c r="P13" s="71" t="s">
         <v>703</v>
       </c>
-      <c r="Q13" s="30" t="s">
-        <v>689</v>
+      <c r="Q13" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza en instalaciones industriales, farmacéuticas o alimentarias que requieren una resistencia extrema a la corrosión, así como alta higiene y larga durabilidad.</v>
       </c>
       <c r="R13" s="30" t="s">
-        <v>690</v>
+        <v>728</v>
       </c>
       <c r="S13" s="30" t="s">
         <v>9</v>
@@ -5198,11 +5270,12 @@
       <c r="P14" s="71" t="s">
         <v>702</v>
       </c>
-      <c r="Q14" s="30" t="s">
-        <v>689</v>
+      <c r="Q14" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza cuando se necesitan conductos de luz o en entornos con mayor humedad y agentes corrosivos (como regiones costeras o laboratorios).</v>
       </c>
       <c r="R14" s="30" t="s">
-        <v>690</v>
+        <v>729</v>
       </c>
       <c r="S14" s="30" t="s">
         <v>9</v>
@@ -5298,11 +5371,12 @@
       <c r="P15" s="71" t="s">
         <v>701</v>
       </c>
-      <c r="Q15" s="30" t="s">
-        <v>689</v>
+      <c r="Q15" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza como material estándar para rejillas, difusores y tomas de aire exteriores para mayor durabilidad y facilidad de acabado.</v>
       </c>
       <c r="R15" s="30" t="s">
-        <v>690</v>
+        <v>730</v>
       </c>
       <c r="S15" s="30" t="s">
         <v>9</v>
@@ -5398,11 +5472,12 @@
       <c r="P16" s="71" t="s">
         <v>700</v>
       </c>
-      <c r="Q16" s="30" t="s">
-        <v>689</v>
+      <c r="Q16" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza en ángulos, tirantes y soportes de fijación para absorber las vibraciones de compresores y ventiladores, evitando la transmisión de ruido a la estructura del edificio.</v>
       </c>
       <c r="R16" s="30" t="s">
-        <v>690</v>
+        <v>731</v>
       </c>
       <c r="S16" s="30" t="s">
         <v>9</v>
@@ -5498,11 +5573,12 @@
       <c r="P17" s="71" t="s">
         <v>699</v>
       </c>
-      <c r="Q17" s="30" t="s">
-        <v>689</v>
+      <c r="Q17" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza como material flexible para estructura de celda cerrada aplicado en el aislamiento de tuberías de refrigerante y agua fría. Evita la condensación superficial y la pérdida de eficiencia.</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>690</v>
+        <v>732</v>
       </c>
       <c r="S17" s="30" t="s">
         <v>9</v>
@@ -5580,43 +5656,44 @@
         <v>9</v>
       </c>
       <c r="L18" s="35" t="str">
-        <f t="shared" ref="L18:O28" si="3">SUBSTITUTE(CONCATENATE("", C18), ".", " ")</f>
+        <f t="shared" ref="L18:O28" si="4">SUBSTITUTE(CONCATENATE("", C18), ".", " ")</f>
         <v>De Materialidade</v>
       </c>
       <c r="M18" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N18" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O18" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Cobre</v>
       </c>
       <c r="P18" s="71" t="s">
         <v>697</v>
       </c>
-      <c r="Q18" s="30" t="s">
-        <v>689</v>
+      <c r="Q18" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza como material para tuberías de refrigerante (líquidos y líneas de succión). Tiene una excelente conductividad térmica, alta resistencia a la corrosión interna y buena maleabilidad para flexión y soldadura de plata/foscoper.</v>
       </c>
       <c r="R18" s="30" t="s">
-        <v>690</v>
+        <v>733</v>
       </c>
       <c r="S18" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T18" s="30" t="str">
-        <f t="shared" ref="T18:V28" si="4">SUBSTITUTE(C18, ".", " ")</f>
+        <f t="shared" ref="T18:V28" si="5">SUBSTITUTE(C18, ".", " ")</f>
         <v>De Materialidade</v>
       </c>
       <c r="U18" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V18" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W18" s="30" t="s">
@@ -5680,43 +5757,44 @@
         <v>9</v>
       </c>
       <c r="L19" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M19" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N19" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O19" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Espumado MPU</v>
       </c>
       <c r="P19" s="71" t="s">
         <v>698</v>
       </c>
-      <c r="Q19" s="30" t="s">
-        <v>689</v>
+      <c r="Q19" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utilizan como paneles compuestos de poliuretano o poliisocianurato recubiertos con láminas de aluminio en ambos lados. Sustituyen el tradicional conducto metálico, añadiendo aislamiento térmico al propio panel y reduciendo el peso estructural.</v>
       </c>
       <c r="R19" s="30" t="s">
-        <v>690</v>
+        <v>734</v>
       </c>
       <c r="S19" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T19" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U19" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V19" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W19" s="30" t="s">
@@ -5780,43 +5858,44 @@
         <v>9</v>
       </c>
       <c r="L20" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M20" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N20" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O20" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Espumado PIR</v>
       </c>
       <c r="P20" s="71" t="s">
         <v>698</v>
       </c>
-      <c r="Q20" s="30" t="s">
-        <v>689</v>
+      <c r="Q20" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utilizan como paneles compuestos de poliuretano o poliisocianurato recubiertos con láminas de aluminio en ambos lados. Sustituyen el tradicional conducto metálico, añadiendo aislamiento térmico al propio panel y reduciendo el peso estructural.</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>690</v>
+        <v>734</v>
       </c>
       <c r="S20" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T20" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U20" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V20" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W20" s="30" t="s">
@@ -5880,43 +5959,44 @@
         <v>9</v>
       </c>
       <c r="L21" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M21" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N21" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O21" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">Mat Lã de Rocha </v>
       </c>
       <c r="P21" s="71" t="s">
         <v>696</v>
       </c>
-      <c r="Q21" s="30" t="s">
-        <v>689</v>
+      <c r="Q21" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza como mantas rígidas o flexibles aplicadas alrededor de conductos metálicos o tuberías grandes para aislamiento térmico y acústico, resistencia al fuego.</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="S21" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T21" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U21" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V21" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W21" s="30" t="s">
@@ -5980,43 +6060,44 @@
         <v>9</v>
       </c>
       <c r="L22" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M22" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N22" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O22" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">Mat Lã de Vidro </v>
       </c>
       <c r="P22" s="71" t="s">
         <v>695</v>
       </c>
-      <c r="Q22" s="30" t="s">
-        <v>689</v>
+      <c r="Q22" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Utilizado en espirales de aluminio envueltas en lana de vidrio y película plástica exterior, empleado en las conexiones finales entre conductos rígidos y difusores de aire.</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>690</v>
+        <v>736</v>
       </c>
       <c r="S22" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T22" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U22" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V22" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W22" s="30" t="s">
@@ -6080,43 +6161,44 @@
         <v>9</v>
       </c>
       <c r="L23" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M23" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N23" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O23" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Mastique</v>
       </c>
       <c r="P23" s="71" t="s">
         <v>692</v>
       </c>
-      <c r="Q23" s="30" t="s">
-        <v>689</v>
+      <c r="Q23" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza como sellador flexible, resistente a la temperatura y la humedad. Se aplica en la unión de conductos y conductos de tubería para evitar fugas de aire.</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>690</v>
+        <v>737</v>
       </c>
       <c r="S23" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T23" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U23" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V23" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W23" s="30" t="s">
@@ -6180,43 +6262,44 @@
         <v>9</v>
       </c>
       <c r="L24" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M24" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N24" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O24" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Plástico ABS</v>
       </c>
       <c r="P24" s="71" t="s">
         <v>694</v>
       </c>
-      <c r="Q24" s="30" t="s">
-        <v>689</v>
+      <c r="Q24" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza para la fabricación de rejillas, difusores y salidas de aire exteriores por su durabilidad y facilidad de acabado.</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>690</v>
+        <v>738</v>
       </c>
       <c r="S24" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T24" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U24" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V24" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W24" s="30" t="s">
@@ -6280,43 +6363,44 @@
         <v>9</v>
       </c>
       <c r="L25" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M25" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N25" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O25" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Poliuretano Expandido PU</v>
       </c>
       <c r="P25" s="71" t="s">
         <v>693</v>
       </c>
-      <c r="Q25" s="30" t="s">
-        <v>689</v>
+      <c r="Q25" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza en tuberías preaisladas o en relleno de huecos en conjuntos térmicos para evitar el intercambio de calor.</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>690</v>
+        <v>739</v>
       </c>
       <c r="S25" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T25" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U25" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V25" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W25" s="30" t="s">
@@ -6380,43 +6464,44 @@
         <v>9</v>
       </c>
       <c r="L26" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M26" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N26" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O26" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Silicone</v>
       </c>
       <c r="P26" s="71" t="s">
         <v>692</v>
       </c>
-      <c r="Q26" s="30" t="s">
-        <v>689</v>
+      <c r="Q26" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza como sellador flexible, resistente a la temperatura y la humedad. Se aplica en la unión de conductos y conductos de tubería para evitar fugas de aire.</v>
       </c>
       <c r="R26" s="30" t="s">
-        <v>690</v>
+        <v>737</v>
       </c>
       <c r="S26" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T26" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U26" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V26" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W26" s="30" t="s">
@@ -6480,43 +6565,44 @@
         <v>9</v>
       </c>
       <c r="L27" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M27" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N27" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O27" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Termoplástico PEX</v>
       </c>
       <c r="P27" s="71" t="s">
         <v>691</v>
       </c>
-      <c r="Q27" s="30" t="s">
-        <v>689</v>
+      <c r="Q27" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza para conducir agua fría o caliente y en tuberías de drenaje de condensados, ya que son inmunes a la corrosión y previenen incrustaciones internas.</v>
       </c>
       <c r="R27" s="30" t="s">
-        <v>690</v>
+        <v>740</v>
       </c>
       <c r="S27" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T27" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U27" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V27" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W27" s="30" t="s">
@@ -6580,43 +6666,44 @@
         <v>9</v>
       </c>
       <c r="L28" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>De Materialidade</v>
       </c>
       <c r="M28" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materialidades</v>
       </c>
       <c r="N28" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Materiais</v>
       </c>
       <c r="O28" s="35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Mat Termoplástico PPR</v>
       </c>
       <c r="P28" s="71" t="s">
         <v>691</v>
       </c>
-      <c r="Q28" s="30" t="s">
-        <v>689</v>
+      <c r="Q28" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Se utiliza para conducir agua fría o caliente y en tuberías de drenaje de condensados, ya que son inmunes a la corrosión y previenen incrustaciones internas.</v>
       </c>
       <c r="R28" s="30" t="s">
-        <v>690</v>
+        <v>740</v>
       </c>
       <c r="S28" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T28" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>De Materialidade</v>
       </c>
       <c r="U28" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materialidades</v>
       </c>
       <c r="V28" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Materiais</v>
       </c>
       <c r="W28" s="30" t="s">
@@ -6680,19 +6767,19 @@
         <v>9</v>
       </c>
       <c r="L29" s="35" t="str">
-        <f t="shared" ref="L29:M39" si="5">CONCATENATE("", C29)</f>
+        <f t="shared" ref="L29:M39" si="6">CONCATENATE("", C29)</f>
         <v>De.AVAC</v>
       </c>
       <c r="M29" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Elétricos.de.Avac</v>
       </c>
       <c r="N29" s="35" t="str">
-        <f t="shared" ref="N29:N39" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E29),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N29:N39" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E29),"."," ")," De "," de "))</f>
         <v>Elétrica de Avac</v>
       </c>
       <c r="O29" s="30" t="str">
-        <f t="shared" ref="O29:O31" si="7">IF(ISNUMBER(FIND("Ifc",F29)),CONCATENATE("Classe IFC:   ",F29),CONCATENATE("",F29))</f>
+        <f t="shared" ref="O29:O31" si="8">IF(ISNUMBER(FIND("Ifc",F29)),CONCATENATE("Classe IFC:   ",F29),CONCATENATE("",F29))</f>
         <v>Circuito.Elétrico.de.Ar.Condicionado</v>
       </c>
       <c r="P29" s="47" t="s">
@@ -6708,22 +6795,22 @@
         <v>9</v>
       </c>
       <c r="T29" s="30" t="str">
-        <f t="shared" ref="T29:V44" si="8">SUBSTITUTE(C29, "_", " ")</f>
+        <f t="shared" ref="T29:V44" si="9">SUBSTITUTE(C29, "_", " ")</f>
         <v>De.AVAC</v>
       </c>
       <c r="U29" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Elétricos.de.Avac</v>
       </c>
       <c r="V29" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Elétrica.de.Avac</v>
       </c>
       <c r="W29" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X29" s="48" t="str">
-        <f t="shared" ref="X29:X88" si="9">CONCATENATE("Key-AVAC-",A29)</f>
+        <f t="shared" ref="X29:X88" si="10">CONCATENATE("Key-AVAC-",A29)</f>
         <v>Key-AVAC-29</v>
       </c>
       <c r="Y29" s="29" t="s">
@@ -6780,19 +6867,19 @@
         <v>9</v>
       </c>
       <c r="L30" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M30" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Elétricos.de.Avac</v>
       </c>
       <c r="N30" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Elétrica de Avac</v>
       </c>
       <c r="O30" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Circuito.Elétrico.de.Aquecimento</v>
       </c>
       <c r="P30" s="47" t="s">
@@ -6808,22 +6895,22 @@
         <v>9</v>
       </c>
       <c r="T30" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U30" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Elétricos.de.Avac</v>
       </c>
       <c r="V30" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Elétrica.de.Avac</v>
       </c>
       <c r="W30" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X30" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-30</v>
       </c>
       <c r="Y30" s="29" t="s">
@@ -6880,19 +6967,19 @@
         <v>9</v>
       </c>
       <c r="L31" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M31" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.Elétricos.de.Avac</v>
       </c>
       <c r="N31" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Elétrica de Avac</v>
       </c>
       <c r="O31" s="30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Circuito.Elétrico.de.Exaustão</v>
       </c>
       <c r="P31" s="47" t="s">
@@ -6908,22 +6995,22 @@
         <v>9</v>
       </c>
       <c r="T31" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U31" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.Elétricos.de.Avac</v>
       </c>
       <c r="V31" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Elétrica.de.Avac</v>
       </c>
       <c r="W31" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X31" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-31</v>
       </c>
       <c r="Y31" s="29" t="s">
@@ -6980,19 +7067,19 @@
         <v>9</v>
       </c>
       <c r="L32" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M32" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="N32" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistema Avac</v>
       </c>
       <c r="O32" s="30" t="str">
-        <f t="shared" ref="O32:O76" si="10">IF(ISNUMBER(FIND("Ifc",F32)),CONCATENATE("",F32),CONCATENATE("",F32))</f>
+        <f t="shared" ref="O32:O76" si="11">IF(ISNUMBER(FIND("Ifc",F32)),CONCATENATE("",F32),CONCATENATE("",F32))</f>
         <v>Ar.Condicionado</v>
       </c>
       <c r="P32" s="30" t="s">
@@ -7008,22 +7095,22 @@
         <v>9</v>
       </c>
       <c r="T32" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U32" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V32" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W32" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X32" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-32</v>
       </c>
       <c r="Y32" s="30" t="s">
@@ -7080,19 +7167,19 @@
         <v>9</v>
       </c>
       <c r="L33" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M33" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="N33" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistema Avac</v>
       </c>
       <c r="O33" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Água.Gelada</v>
       </c>
       <c r="P33" s="30" t="s">
@@ -7108,22 +7195,22 @@
         <v>9</v>
       </c>
       <c r="T33" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U33" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V33" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W33" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X33" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-33</v>
       </c>
       <c r="Y33" s="30" t="s">
@@ -7180,19 +7267,19 @@
         <v>9</v>
       </c>
       <c r="L34" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M34" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="N34" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistema Avac</v>
       </c>
       <c r="O34" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Água.Condensador</v>
       </c>
       <c r="P34" s="30" t="s">
@@ -7208,22 +7295,22 @@
         <v>9</v>
       </c>
       <c r="T34" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U34" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V34" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W34" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X34" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-34</v>
       </c>
       <c r="Y34" s="30" t="s">
@@ -7280,19 +7367,19 @@
         <v>9</v>
       </c>
       <c r="L35" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M35" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="N35" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistema Avac</v>
       </c>
       <c r="O35" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Ar.Comprimido</v>
       </c>
       <c r="P35" s="30" t="s">
@@ -7308,22 +7395,22 @@
         <v>9</v>
       </c>
       <c r="T35" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U35" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V35" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W35" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X35" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-35</v>
       </c>
       <c r="Y35" s="30" t="s">
@@ -7380,19 +7467,19 @@
         <v>9</v>
       </c>
       <c r="L36" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M36" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="N36" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistema Avac</v>
       </c>
       <c r="O36" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Exaustão</v>
       </c>
       <c r="P36" s="30" t="s">
@@ -7408,22 +7495,22 @@
         <v>9</v>
       </c>
       <c r="T36" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U36" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V36" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W36" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X36" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-36</v>
       </c>
       <c r="Y36" s="30" t="s">
@@ -7480,19 +7567,19 @@
         <v>9</v>
       </c>
       <c r="L37" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M37" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="N37" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistema Avac</v>
       </c>
       <c r="O37" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Aquecimento</v>
       </c>
       <c r="P37" s="30" t="s">
@@ -7508,22 +7595,22 @@
         <v>9</v>
       </c>
       <c r="T37" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U37" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V37" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W37" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X37" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-37</v>
       </c>
       <c r="Y37" s="30" t="s">
@@ -7580,19 +7667,19 @@
         <v>9</v>
       </c>
       <c r="L38" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M38" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="N38" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistema Avac</v>
       </c>
       <c r="O38" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Ventilação</v>
       </c>
       <c r="P38" s="30" t="s">
@@ -7608,22 +7695,22 @@
         <v>9</v>
       </c>
       <c r="T38" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U38" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V38" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W38" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X38" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-38</v>
       </c>
       <c r="Y38" s="30" t="s">
@@ -7680,19 +7767,19 @@
         <v>9</v>
       </c>
       <c r="L39" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>De.AVAC</v>
       </c>
       <c r="M39" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="N39" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistema Avac</v>
       </c>
       <c r="O39" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Refrigeração</v>
       </c>
       <c r="P39" s="30" t="s">
@@ -7708,22 +7795,22 @@
         <v>9</v>
       </c>
       <c r="T39" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U39" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V39" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W39" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X39" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-39</v>
       </c>
       <c r="Y39" s="30" t="s">
@@ -7780,19 +7867,19 @@
         <v>9</v>
       </c>
       <c r="L40" s="35" t="str">
-        <f t="shared" ref="L40:M58" si="11">CONCATENATE("", C40)</f>
+        <f t="shared" ref="L40:M58" si="12">CONCATENATE("", C40)</f>
         <v>De.AVAC</v>
       </c>
       <c r="M40" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Sistemas.de.Avac</v>
+      </c>
+      <c r="N40" s="35" t="str">
+        <f t="shared" ref="N40:O85" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E40),"."," ")," De "," de "))</f>
+        <v>Sistema Avac</v>
+      </c>
+      <c r="O40" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>Sistemas.de.Avac</v>
-      </c>
-      <c r="N40" s="35" t="str">
-        <f t="shared" ref="N40:O85" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E40),"."," ")," De "," de "))</f>
-        <v>Sistema Avac</v>
-      </c>
-      <c r="O40" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Insuflamento</v>
       </c>
       <c r="P40" s="30" t="s">
@@ -7808,22 +7895,22 @@
         <v>9</v>
       </c>
       <c r="T40" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U40" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V40" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W40" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X40" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-40</v>
       </c>
       <c r="Y40" s="30" t="s">
@@ -7880,19 +7967,19 @@
         <v>9</v>
       </c>
       <c r="L41" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M41" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Sistemas.de.Avac</v>
+      </c>
+      <c r="N41" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema Avac</v>
+      </c>
+      <c r="O41" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M41" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistemas.de.Avac</v>
-      </c>
-      <c r="N41" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Sistema Avac</v>
-      </c>
-      <c r="O41" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Retorno</v>
       </c>
       <c r="P41" s="30" t="s">
@@ -7908,22 +7995,22 @@
         <v>9</v>
       </c>
       <c r="T41" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U41" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V41" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W41" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X41" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-41</v>
       </c>
       <c r="Y41" s="30" t="s">
@@ -7980,19 +8067,19 @@
         <v>9</v>
       </c>
       <c r="L42" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M42" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Sistemas.de.Avac</v>
+      </c>
+      <c r="N42" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema Avac</v>
+      </c>
+      <c r="O42" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M42" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistemas.de.Avac</v>
-      </c>
-      <c r="N42" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Sistema Avac</v>
-      </c>
-      <c r="O42" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Vácuo</v>
       </c>
       <c r="P42" s="30" t="s">
@@ -8008,22 +8095,22 @@
         <v>9</v>
       </c>
       <c r="T42" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U42" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistemas.de.Avac</v>
       </c>
       <c r="V42" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Sistema.Avac</v>
       </c>
       <c r="W42" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X42" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-42</v>
       </c>
       <c r="Y42" s="30" t="s">
@@ -8080,19 +8167,19 @@
         <v>9</v>
       </c>
       <c r="L43" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M43" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N43" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Dutos</v>
+      </c>
+      <c r="O43" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M43" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N43" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Dutos</v>
-      </c>
-      <c r="O43" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Duto.Conexão</v>
       </c>
       <c r="P43" s="30" t="s">
@@ -8108,22 +8195,22 @@
         <v>9</v>
       </c>
       <c r="T43" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U43" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V43" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Avac.Dutos</v>
       </c>
       <c r="W43" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X43" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-43</v>
       </c>
       <c r="Y43" s="30" t="s">
@@ -8180,19 +8267,19 @@
         <v>9</v>
       </c>
       <c r="L44" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M44" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N44" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Dutos</v>
+      </c>
+      <c r="O44" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M44" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N44" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Dutos</v>
-      </c>
-      <c r="O44" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Duto.Flexível</v>
       </c>
       <c r="P44" s="30" t="s">
@@ -8208,22 +8295,22 @@
         <v>9</v>
       </c>
       <c r="T44" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>De.AVAC</v>
       </c>
       <c r="U44" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V44" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Avac.Dutos</v>
       </c>
       <c r="W44" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X44" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-44</v>
       </c>
       <c r="Y44" s="30" t="s">
@@ -8280,19 +8367,19 @@
         <v>9</v>
       </c>
       <c r="L45" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M45" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N45" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Dutos</v>
+      </c>
+      <c r="O45" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M45" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N45" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Dutos</v>
-      </c>
-      <c r="O45" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Duto.Segmento</v>
       </c>
       <c r="P45" s="30" t="s">
@@ -8308,22 +8395,22 @@
         <v>9</v>
       </c>
       <c r="T45" s="30" t="str">
-        <f t="shared" ref="T45:V60" si="13">SUBSTITUTE(C45, "_", " ")</f>
+        <f t="shared" ref="T45:V60" si="14">SUBSTITUTE(C45, "_", " ")</f>
         <v>De.AVAC</v>
       </c>
       <c r="U45" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V45" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Dutos</v>
       </c>
       <c r="W45" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X45" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-45</v>
       </c>
       <c r="Y45" s="30" t="s">
@@ -8380,19 +8467,19 @@
         <v>9</v>
       </c>
       <c r="L46" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M46" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N46" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Dutos</v>
+      </c>
+      <c r="O46" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M46" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N46" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Dutos</v>
-      </c>
-      <c r="O46" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Duto.Silenciador</v>
       </c>
       <c r="P46" s="30" t="s">
@@ -8408,22 +8495,22 @@
         <v>9</v>
       </c>
       <c r="T46" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U46" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V46" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Dutos</v>
       </c>
       <c r="W46" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X46" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-46</v>
       </c>
       <c r="Y46" s="30" t="s">
@@ -8480,19 +8567,19 @@
         <v>9</v>
       </c>
       <c r="L47" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M47" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N47" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Dutos</v>
+      </c>
+      <c r="O47" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M47" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N47" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Dutos</v>
-      </c>
-      <c r="O47" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Duto.Silenciador.Conexão</v>
       </c>
       <c r="P47" s="30" t="s">
@@ -8508,22 +8595,22 @@
         <v>9</v>
       </c>
       <c r="T47" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U47" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V47" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Dutos</v>
       </c>
       <c r="W47" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X47" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-47</v>
       </c>
       <c r="Y47" s="30" t="s">
@@ -8580,19 +8667,19 @@
         <v>9</v>
       </c>
       <c r="L48" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M48" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N48" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Tubos</v>
+      </c>
+      <c r="O48" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M48" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N48" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Tubos</v>
-      </c>
-      <c r="O48" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Tubo.Conexão</v>
       </c>
       <c r="P48" s="30" t="s">
@@ -8608,22 +8695,22 @@
         <v>9</v>
       </c>
       <c r="T48" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U48" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V48" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Tubos</v>
       </c>
       <c r="W48" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X48" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-48</v>
       </c>
       <c r="Y48" s="30" t="s">
@@ -8680,19 +8767,19 @@
         <v>9</v>
       </c>
       <c r="L49" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M49" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N49" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Tubos</v>
+      </c>
+      <c r="O49" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M49" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N49" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Tubos</v>
-      </c>
-      <c r="O49" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Tubo.Segmento</v>
       </c>
       <c r="P49" s="30" t="s">
@@ -8708,22 +8795,22 @@
         <v>9</v>
       </c>
       <c r="T49" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U49" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V49" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Tubos</v>
       </c>
       <c r="W49" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X49" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-49</v>
       </c>
       <c r="Y49" s="30" t="s">
@@ -8780,19 +8867,19 @@
         <v>9</v>
       </c>
       <c r="L50" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M50" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N50" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Tubos</v>
+      </c>
+      <c r="O50" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M50" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N50" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Tubos</v>
-      </c>
-      <c r="O50" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Tubo.Válvula</v>
       </c>
       <c r="P50" s="30" t="s">
@@ -8808,22 +8895,22 @@
         <v>9</v>
       </c>
       <c r="T50" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U50" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V50" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Tubos</v>
       </c>
       <c r="W50" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X50" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-50</v>
       </c>
       <c r="Y50" s="30" t="s">
@@ -8880,19 +8967,19 @@
         <v>9</v>
       </c>
       <c r="L51" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M51" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N51" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Terminais</v>
+      </c>
+      <c r="O51" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M51" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N51" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Terminais</v>
-      </c>
-      <c r="O51" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Duto.Terminal</v>
       </c>
       <c r="P51" s="30" t="s">
@@ -8908,22 +8995,22 @@
         <v>9</v>
       </c>
       <c r="T51" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U51" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V51" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Terminais</v>
       </c>
       <c r="W51" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X51" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-51</v>
       </c>
       <c r="Y51" s="30" t="s">
@@ -8980,19 +9067,19 @@
         <v>9</v>
       </c>
       <c r="L52" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M52" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N52" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Terminais</v>
+      </c>
+      <c r="O52" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M52" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N52" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Terminais</v>
-      </c>
-      <c r="O52" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Caixa.Junção</v>
       </c>
       <c r="P52" s="30" t="s">
@@ -9008,22 +9095,22 @@
         <v>9</v>
       </c>
       <c r="T52" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U52" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V52" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Terminais</v>
       </c>
       <c r="W52" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X52" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-52</v>
       </c>
       <c r="Y52" s="30" t="s">
@@ -9080,19 +9167,19 @@
         <v>9</v>
       </c>
       <c r="L53" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M53" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Dutagem</v>
+      </c>
+      <c r="N53" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Terminais</v>
+      </c>
+      <c r="O53" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M53" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Dutagem</v>
-      </c>
-      <c r="N53" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Terminais</v>
-      </c>
-      <c r="O53" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Caixa.Terminal</v>
       </c>
       <c r="P53" s="30" t="s">
@@ -9108,22 +9195,22 @@
         <v>9</v>
       </c>
       <c r="T53" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U53" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Dutagem</v>
       </c>
       <c r="V53" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Terminais</v>
       </c>
       <c r="W53" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X53" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-53</v>
       </c>
       <c r="Y53" s="30" t="s">
@@ -9180,19 +9267,19 @@
         <v>9</v>
       </c>
       <c r="L54" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M54" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Avac</v>
+      </c>
+      <c r="N54" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Equipamentos</v>
+      </c>
+      <c r="O54" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M54" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Avac</v>
-      </c>
-      <c r="N54" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Equipamentos</v>
-      </c>
-      <c r="O54" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Compressor</v>
       </c>
       <c r="P54" s="30" t="s">
@@ -9208,22 +9295,22 @@
         <v>9</v>
       </c>
       <c r="T54" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U54" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V54" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W54" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X54" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-54</v>
       </c>
       <c r="Y54" s="29" t="s">
@@ -9280,19 +9367,19 @@
         <v>9</v>
       </c>
       <c r="L55" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M55" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Avac</v>
+      </c>
+      <c r="N55" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Equipamentos</v>
+      </c>
+      <c r="O55" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M55" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Avac</v>
-      </c>
-      <c r="N55" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Equipamentos</v>
-      </c>
-      <c r="O55" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Filtro</v>
       </c>
       <c r="P55" s="30" t="s">
@@ -9308,22 +9395,22 @@
         <v>9</v>
       </c>
       <c r="T55" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U55" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V55" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W55" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X55" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-55</v>
       </c>
       <c r="Y55" s="29" t="s">
@@ -9380,19 +9467,19 @@
         <v>9</v>
       </c>
       <c r="L56" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M56" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Avac</v>
+      </c>
+      <c r="N56" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Equipamentos</v>
+      </c>
+      <c r="O56" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M56" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Avac</v>
-      </c>
-      <c r="N56" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Equipamentos</v>
-      </c>
-      <c r="O56" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Unitário</v>
       </c>
       <c r="P56" s="30" t="s">
@@ -9408,22 +9495,22 @@
         <v>9</v>
       </c>
       <c r="T56" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U56" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V56" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W56" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X56" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-56</v>
       </c>
       <c r="Y56" s="29" t="s">
@@ -9480,19 +9567,19 @@
         <v>9</v>
       </c>
       <c r="L57" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M57" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Avac</v>
+      </c>
+      <c r="N57" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Equipamentos</v>
+      </c>
+      <c r="O57" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M57" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Avac</v>
-      </c>
-      <c r="N57" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Equipamentos</v>
-      </c>
-      <c r="O57" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Bobina.de.Tubos</v>
       </c>
       <c r="P57" s="30" t="s">
@@ -9508,22 +9595,22 @@
         <v>9</v>
       </c>
       <c r="T57" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U57" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V57" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W57" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X57" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-57</v>
       </c>
       <c r="Y57" s="29" t="s">
@@ -9580,19 +9667,19 @@
         <v>9</v>
       </c>
       <c r="L58" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M58" s="35" t="str">
+        <f t="shared" si="12"/>
+        <v>Elementos.de.Avac</v>
+      </c>
+      <c r="N58" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Equipamentos</v>
+      </c>
+      <c r="O58" s="30" t="str">
         <f t="shared" si="11"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="M58" s="35" t="str">
-        <f t="shared" si="11"/>
-        <v>Elementos.de.Avac</v>
-      </c>
-      <c r="N58" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Equipamentos</v>
-      </c>
-      <c r="O58" s="30" t="str">
-        <f t="shared" si="10"/>
         <v>Avac.Caldeira</v>
       </c>
       <c r="P58" s="30" t="s">
@@ -9608,22 +9695,22 @@
         <v>9</v>
       </c>
       <c r="T58" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
       <c r="U58" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V58" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W58" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X58" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-58</v>
       </c>
       <c r="Y58" s="29" t="s">
@@ -9680,50 +9767,50 @@
         <v>9</v>
       </c>
       <c r="L59" s="35" t="str">
-        <f t="shared" ref="L59:M111" si="14">CONCATENATE("", C59)</f>
+        <f t="shared" ref="L59:M111" si="15">CONCATENATE("", C59)</f>
         <v>De.AVAC</v>
       </c>
       <c r="M59" s="35" t="str">
+        <f t="shared" si="15"/>
+        <v>Elementos.de.Avac</v>
+      </c>
+      <c r="N59" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Equipamentos</v>
+      </c>
+      <c r="O59" s="30" t="str">
+        <f t="shared" si="11"/>
+        <v>Avac.Chaminé</v>
+      </c>
+      <c r="P59" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q59" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="R59" s="30" t="s">
+        <v>501</v>
+      </c>
+      <c r="S59" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T59" s="30" t="str">
+        <f t="shared" si="14"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="U59" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Elementos.de.Avac</v>
       </c>
-      <c r="N59" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Equipamentos</v>
-      </c>
-      <c r="O59" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Avac.Chaminé</v>
-      </c>
-      <c r="P59" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q59" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="R59" s="30" t="s">
-        <v>501</v>
-      </c>
-      <c r="S59" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T59" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="U59" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Elementos.de.Avac</v>
-      </c>
       <c r="V59" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W59" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X59" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-59</v>
       </c>
       <c r="Y59" s="29" t="s">
@@ -9780,50 +9867,50 @@
         <v>9</v>
       </c>
       <c r="L60" s="35" t="str">
+        <f t="shared" si="15"/>
+        <v>De.AVAC</v>
+      </c>
+      <c r="M60" s="35" t="str">
+        <f t="shared" si="15"/>
+        <v>Elementos.de.Avac</v>
+      </c>
+      <c r="N60" s="35" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Equipamentos</v>
+      </c>
+      <c r="O60" s="30" t="str">
+        <f t="shared" si="11"/>
+        <v>Avac.Chiller</v>
+      </c>
+      <c r="P60" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q60" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="R60" s="30" t="s">
+        <v>502</v>
+      </c>
+      <c r="S60" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T60" s="30" t="str">
         <f t="shared" si="14"/>
         <v>De.AVAC</v>
       </c>
-      <c r="M60" s="35" t="str">
+      <c r="U60" s="30" t="str">
         <f t="shared" si="14"/>
         <v>Elementos.de.Avac</v>
       </c>
-      <c r="N60" s="35" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac Equipamentos</v>
-      </c>
-      <c r="O60" s="30" t="str">
-        <f t="shared" si="10"/>
-        <v>Avac.Chiller</v>
-      </c>
-      <c r="P60" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q60" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="R60" s="30" t="s">
-        <v>502</v>
-      </c>
-      <c r="S60" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T60" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>De.AVAC</v>
-      </c>
-      <c r="U60" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Elementos.de.Avac</v>
-      </c>
       <c r="V60" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W60" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X60" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-60</v>
       </c>
       <c r="Y60" s="29" t="s">
@@ -9880,19 +9967,19 @@
         <v>9</v>
       </c>
       <c r="L61" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M61" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N61" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O61" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Condensador</v>
       </c>
       <c r="P61" s="30" t="s">
@@ -9908,22 +9995,22 @@
         <v>9</v>
       </c>
       <c r="T61" s="30" t="str">
-        <f t="shared" ref="T61:V76" si="15">SUBSTITUTE(C61, "_", " ")</f>
+        <f t="shared" ref="T61:V76" si="16">SUBSTITUTE(C61, "_", " ")</f>
         <v>De.AVAC</v>
       </c>
       <c r="U61" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V61" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W61" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X61" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-61</v>
       </c>
       <c r="Y61" s="29" t="s">
@@ -9980,19 +10067,19 @@
         <v>9</v>
       </c>
       <c r="L62" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M62" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N62" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O62" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Evaporador</v>
       </c>
       <c r="P62" s="30" t="s">
@@ -10008,22 +10095,22 @@
         <v>9</v>
       </c>
       <c r="T62" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U62" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V62" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W62" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X62" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-62</v>
       </c>
       <c r="Y62" s="29" t="s">
@@ -10080,19 +10167,19 @@
         <v>9</v>
       </c>
       <c r="L63" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M63" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N63" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O63" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Queimador</v>
       </c>
       <c r="P63" s="30" t="s">
@@ -10108,22 +10195,22 @@
         <v>9</v>
       </c>
       <c r="T63" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U63" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V63" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W63" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X63" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-63</v>
       </c>
       <c r="Y63" s="29" t="s">
@@ -10180,19 +10267,19 @@
         <v>9</v>
       </c>
       <c r="L64" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M64" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N64" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O64" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Recuperador.Ar-Ar</v>
       </c>
       <c r="P64" s="30" t="s">
@@ -10208,22 +10295,22 @@
         <v>9</v>
       </c>
       <c r="T64" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U64" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V64" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W64" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X64" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-64</v>
       </c>
       <c r="Y64" s="29" t="s">
@@ -10280,19 +10367,19 @@
         <v>9</v>
       </c>
       <c r="L65" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M65" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N65" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O65" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Resfriador.Evaporativo</v>
       </c>
       <c r="P65" s="30" t="s">
@@ -10308,22 +10395,22 @@
         <v>9</v>
       </c>
       <c r="T65" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U65" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V65" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W65" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X65" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-65</v>
       </c>
       <c r="Y65" s="29" t="s">
@@ -10380,19 +10467,19 @@
         <v>9</v>
       </c>
       <c r="L66" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M66" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N66" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O66" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Serpentina</v>
       </c>
       <c r="P66" s="30" t="s">
@@ -10408,22 +10495,22 @@
         <v>9</v>
       </c>
       <c r="T66" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U66" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V66" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W66" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X66" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-66</v>
       </c>
       <c r="Y66" s="29" t="s">
@@ -10480,19 +10567,19 @@
         <v>9</v>
       </c>
       <c r="L67" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M67" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N67" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O67" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Torre.Arrefecimento</v>
       </c>
       <c r="P67" s="30" t="s">
@@ -10508,22 +10595,22 @@
         <v>9</v>
       </c>
       <c r="T67" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U67" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V67" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W67" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X67" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-67</v>
       </c>
       <c r="Y67" s="29" t="s">
@@ -10580,19 +10667,19 @@
         <v>9</v>
       </c>
       <c r="L68" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M68" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N68" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O68" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Trocador.de.Calor</v>
       </c>
       <c r="P68" s="30" t="s">
@@ -10608,22 +10695,22 @@
         <v>9</v>
       </c>
       <c r="T68" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U68" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V68" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W68" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X68" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-68</v>
       </c>
       <c r="Y68" s="29" t="s">
@@ -10680,19 +10767,19 @@
         <v>9</v>
       </c>
       <c r="L69" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M69" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N69" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O69" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Umidificador</v>
       </c>
       <c r="P69" s="30" t="s">
@@ -10708,22 +10795,22 @@
         <v>9</v>
       </c>
       <c r="T69" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U69" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V69" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W69" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X69" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-69</v>
       </c>
       <c r="Y69" s="29" t="s">
@@ -10780,19 +10867,19 @@
         <v>9</v>
       </c>
       <c r="L70" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M70" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N70" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos</v>
       </c>
       <c r="O70" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Ventilador</v>
       </c>
       <c r="P70" s="30" t="s">
@@ -10808,22 +10895,22 @@
         <v>9</v>
       </c>
       <c r="T70" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U70" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="V70" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Equipamentos</v>
       </c>
       <c r="W70" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X70" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-70</v>
       </c>
       <c r="Y70" s="29" t="s">
@@ -10880,19 +10967,19 @@
         <v>9</v>
       </c>
       <c r="L71" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M71" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N71" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="O71" s="35" t="str">
-        <f t="shared" ref="O71:O73" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F71),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O71:O73" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F71),"."," ")," De "," de "))</f>
         <v>Avac Aquecedor de Ambiente</v>
       </c>
       <c r="P71" s="30" t="s">
@@ -10908,22 +10995,22 @@
         <v>9</v>
       </c>
       <c r="T71" s="30" t="str">
-        <f t="shared" ref="T71:T73" si="17">SUBSTITUTE(C71, ".", " ")</f>
+        <f t="shared" ref="T71:T73" si="18">SUBSTITUTE(C71, ".", " ")</f>
         <v>De AVAC</v>
       </c>
       <c r="U71" s="30" t="str">
-        <f t="shared" ref="U71:U73" si="18">SUBSTITUTE(D71, ".", " ")</f>
+        <f t="shared" ref="U71:U73" si="19">SUBSTITUTE(D71, ".", " ")</f>
         <v>Elementos de Avac</v>
       </c>
       <c r="V71" s="30" t="str">
-        <f t="shared" ref="V71:V73" si="19">SUBSTITUTE(E71, ".", " ")</f>
+        <f t="shared" ref="V71:V73" si="20">SUBSTITUTE(E71, ".", " ")</f>
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="W71" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X71" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-71</v>
       </c>
       <c r="Y71" s="30" t="s">
@@ -10980,19 +11067,19 @@
         <v>9</v>
       </c>
       <c r="L72" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M72" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N72" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="O72" s="35" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>Avac Aquecedor Convector</v>
       </c>
       <c r="P72" s="30" t="s">
@@ -11008,22 +11095,22 @@
         <v>9</v>
       </c>
       <c r="T72" s="30" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>De AVAC</v>
       </c>
       <c r="U72" s="30" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>Elementos de Avac</v>
       </c>
       <c r="V72" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="W72" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X72" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-72</v>
       </c>
       <c r="Y72" s="30" t="s">
@@ -11080,19 +11167,19 @@
         <v>9</v>
       </c>
       <c r="L73" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M73" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Avac</v>
       </c>
       <c r="N73" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="O73" s="35" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>Avac Aquecedor Radiação</v>
       </c>
       <c r="P73" s="30" t="s">
@@ -11108,22 +11195,22 @@
         <v>9</v>
       </c>
       <c r="T73" s="30" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>De AVAC</v>
       </c>
       <c r="U73" s="30" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>Elementos de Avac</v>
       </c>
       <c r="V73" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="W73" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X73" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-73</v>
       </c>
       <c r="Y73" s="30" t="s">
@@ -11180,19 +11267,19 @@
         <v>9</v>
       </c>
       <c r="L74" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M74" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="N74" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Dampers</v>
       </c>
       <c r="O74" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Amortecedor</v>
       </c>
       <c r="P74" s="30" t="s">
@@ -11208,22 +11295,22 @@
         <v>9</v>
       </c>
       <c r="T74" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U74" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="V74" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Dampers</v>
       </c>
       <c r="W74" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X74" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-74</v>
       </c>
       <c r="Y74" s="30" t="s">
@@ -11280,19 +11367,19 @@
         <v>9</v>
       </c>
       <c r="L75" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M75" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="N75" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Dampers</v>
       </c>
       <c r="O75" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Vibração.Amortecedor</v>
       </c>
       <c r="P75" s="30" t="s">
@@ -11308,22 +11395,22 @@
         <v>9</v>
       </c>
       <c r="T75" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U75" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="V75" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Dampers</v>
       </c>
       <c r="W75" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X75" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-75</v>
       </c>
       <c r="Y75" s="30" t="s">
@@ -11380,19 +11467,19 @@
         <v>9</v>
       </c>
       <c r="L76" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M76" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="N76" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Dampers</v>
       </c>
       <c r="O76" s="30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Avac.Vibração.Isolador</v>
       </c>
       <c r="P76" s="30" t="s">
@@ -11408,22 +11495,22 @@
         <v>9</v>
       </c>
       <c r="T76" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>De.AVAC</v>
       </c>
       <c r="U76" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="V76" s="30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Avac.Dampers</v>
       </c>
       <c r="W76" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X76" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-76</v>
       </c>
       <c r="Y76" s="30" t="s">
@@ -11480,19 +11567,19 @@
         <v>9</v>
       </c>
       <c r="L77" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M77" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N77" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O77" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor</v>
       </c>
       <c r="P77" s="30" t="s">
@@ -11508,22 +11595,22 @@
         <v>9</v>
       </c>
       <c r="T77" s="30" t="str">
-        <f t="shared" ref="T77:V109" si="20">SUBSTITUTE(C77, ".", " ")</f>
+        <f t="shared" ref="T77:V109" si="21">SUBSTITUTE(C77, ".", " ")</f>
         <v>De AVAC</v>
       </c>
       <c r="U77" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V77" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W77" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X77" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-77</v>
       </c>
       <c r="Y77" s="30" t="s">
@@ -11580,19 +11667,19 @@
         <v>9</v>
       </c>
       <c r="L78" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M78" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N78" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O78" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor de Monóxido Carbono</v>
       </c>
       <c r="P78" s="30" t="s">
@@ -11608,22 +11695,22 @@
         <v>9</v>
       </c>
       <c r="T78" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U78" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V78" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W78" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X78" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-78</v>
       </c>
       <c r="Y78" s="30" t="s">
@@ -11680,19 +11767,19 @@
         <v>9</v>
       </c>
       <c r="L79" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M79" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N79" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O79" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor de Dióxido Carbono</v>
       </c>
       <c r="P79" s="30" t="s">
@@ -11708,22 +11795,22 @@
         <v>9</v>
       </c>
       <c r="T79" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U79" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V79" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W79" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X79" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-79</v>
       </c>
       <c r="Y79" s="30" t="s">
@@ -11780,19 +11867,19 @@
         <v>9</v>
       </c>
       <c r="L80" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M80" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N80" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O80" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor de Condutância</v>
       </c>
       <c r="P80" s="30" t="s">
@@ -11808,22 +11895,22 @@
         <v>9</v>
       </c>
       <c r="T80" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U80" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V80" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W80" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X80" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-80</v>
       </c>
       <c r="Y80" s="30" t="s">
@@ -11880,19 +11967,19 @@
         <v>9</v>
       </c>
       <c r="L81" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M81" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N81" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O81" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor de Contato</v>
       </c>
       <c r="P81" s="30" t="s">
@@ -11908,22 +11995,22 @@
         <v>9</v>
       </c>
       <c r="T81" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U81" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V81" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W81" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X81" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-81</v>
       </c>
       <c r="Y81" s="30" t="s">
@@ -11980,19 +12067,19 @@
         <v>9</v>
       </c>
       <c r="L82" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M82" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N82" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O82" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor de Sismos</v>
       </c>
       <c r="P82" s="30" t="s">
@@ -12008,22 +12095,22 @@
         <v>9</v>
       </c>
       <c r="T82" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U82" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V82" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W82" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X82" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-82</v>
       </c>
       <c r="Y82" s="30" t="s">
@@ -12080,19 +12167,19 @@
         <v>9</v>
       </c>
       <c r="L83" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M83" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N83" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O83" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor de Incêndio</v>
       </c>
       <c r="P83" s="30" t="s">
@@ -12108,22 +12195,22 @@
         <v>9</v>
       </c>
       <c r="T83" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U83" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V83" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W83" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X83" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-83</v>
       </c>
       <c r="Y83" s="30" t="s">
@@ -12180,19 +12267,19 @@
         <v>9</v>
       </c>
       <c r="L84" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M84" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N84" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O84" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor de Fluxo</v>
       </c>
       <c r="P84" s="30" t="s">
@@ -12208,22 +12295,22 @@
         <v>9</v>
       </c>
       <c r="T84" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U84" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V84" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W84" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X84" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-84</v>
       </c>
       <c r="Y84" s="30" t="s">
@@ -12280,19 +12367,19 @@
         <v>9</v>
       </c>
       <c r="L85" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M85" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N85" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O85" s="35" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Avac Sensor de Detecção Objeto Estranho</v>
       </c>
       <c r="P85" s="30" t="s">
@@ -12308,22 +12395,22 @@
         <v>9</v>
       </c>
       <c r="T85" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U85" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V85" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W85" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X85" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-85</v>
       </c>
       <c r="Y85" s="30" t="s">
@@ -12380,19 +12467,19 @@
         <v>9</v>
       </c>
       <c r="L86" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M86" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N86" s="35" t="str">
-        <f t="shared" ref="N86:O111" si="21">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E86),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N86:O111" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E86),"."," ")," De "," de "))</f>
         <v>Avac Sensores</v>
       </c>
       <c r="O86" s="35" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>Avac Sensor de Geada</v>
       </c>
       <c r="P86" s="30" t="s">
@@ -12408,22 +12495,22 @@
         <v>9</v>
       </c>
       <c r="T86" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>De AVAC</v>
       </c>
       <c r="U86" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="V86" s="30" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
       <c r="W86" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X86" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-86</v>
       </c>
       <c r="Y86" s="30" t="s">
@@ -12480,50 +12567,50 @@
         <v>9</v>
       </c>
       <c r="L87" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M87" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N87" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O87" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Gás</v>
+      </c>
+      <c r="P87" s="30" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q87" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="R87" s="30" t="s">
+        <v>529</v>
+      </c>
+      <c r="S87" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T87" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U87" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V87" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O87" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Gás</v>
-      </c>
-      <c r="P87" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q87" s="30" t="s">
-        <v>284</v>
-      </c>
-      <c r="R87" s="30" t="s">
-        <v>529</v>
-      </c>
-      <c r="S87" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T87" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U87" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V87" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W87" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X87" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-87</v>
       </c>
       <c r="Y87" s="30" t="s">
@@ -12580,50 +12667,50 @@
         <v>9</v>
       </c>
       <c r="L88" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M88" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N88" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O88" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Calor</v>
+      </c>
+      <c r="P88" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q88" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="R88" s="30" t="s">
+        <v>530</v>
+      </c>
+      <c r="S88" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T88" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U88" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V88" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O88" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Calor</v>
-      </c>
-      <c r="P88" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="Q88" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="R88" s="30" t="s">
-        <v>530</v>
-      </c>
-      <c r="S88" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T88" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U88" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V88" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W88" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X88" s="48" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Key-AVAC-88</v>
       </c>
       <c r="Y88" s="30" t="s">
@@ -12680,50 +12767,50 @@
         <v>9</v>
       </c>
       <c r="L89" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M89" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N89" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O89" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Umidade</v>
+      </c>
+      <c r="P89" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q89" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="R89" s="30" t="s">
+        <v>531</v>
+      </c>
+      <c r="S89" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T89" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U89" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V89" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O89" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Umidade</v>
-      </c>
-      <c r="P89" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q89" s="30" t="s">
-        <v>286</v>
-      </c>
-      <c r="R89" s="30" t="s">
-        <v>531</v>
-      </c>
-      <c r="S89" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T89" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U89" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V89" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W89" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X89" s="48" t="str">
-        <f t="shared" ref="X89:X117" si="22">CONCATENATE("Key-AVAC-",A89)</f>
+        <f t="shared" ref="X89:X117" si="23">CONCATENATE("Key-AVAC-",A89)</f>
         <v>Key-AVAC-89</v>
       </c>
       <c r="Y89" s="30" t="s">
@@ -12780,50 +12867,50 @@
         <v>9</v>
       </c>
       <c r="L90" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M90" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N90" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O90" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Identificação</v>
+      </c>
+      <c r="P90" s="30" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q90" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="R90" s="30" t="s">
+        <v>532</v>
+      </c>
+      <c r="S90" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T90" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U90" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V90" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O90" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Identificação</v>
-      </c>
-      <c r="P90" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q90" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="R90" s="30" t="s">
-        <v>532</v>
-      </c>
-      <c r="S90" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T90" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U90" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V90" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W90" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X90" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-90</v>
       </c>
       <c r="Y90" s="30" t="s">
@@ -12880,50 +12967,50 @@
         <v>9</v>
       </c>
       <c r="L91" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M91" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N91" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O91" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Concentração de Íons</v>
+      </c>
+      <c r="P91" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q91" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="R91" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="S91" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T91" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U91" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V91" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O91" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Concentração de Íons</v>
-      </c>
-      <c r="P91" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q91" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="R91" s="30" t="s">
-        <v>533</v>
-      </c>
-      <c r="S91" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T91" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U91" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V91" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W91" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X91" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-91</v>
       </c>
       <c r="Y91" s="30" t="s">
@@ -12980,50 +13067,50 @@
         <v>9</v>
       </c>
       <c r="L92" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M92" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N92" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O92" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Nível</v>
+      </c>
+      <c r="P92" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q92" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="R92" s="30" t="s">
+        <v>534</v>
+      </c>
+      <c r="S92" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T92" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U92" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V92" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O92" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Nível</v>
-      </c>
-      <c r="P92" s="30" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q92" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="R92" s="30" t="s">
-        <v>534</v>
-      </c>
-      <c r="S92" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T92" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U92" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V92" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W92" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X92" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-92</v>
       </c>
       <c r="Y92" s="30" t="s">
@@ -13080,50 +13167,50 @@
         <v>9</v>
       </c>
       <c r="L93" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M93" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N93" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O93" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Luz</v>
+      </c>
+      <c r="P93" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q93" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="R93" s="30" t="s">
+        <v>535</v>
+      </c>
+      <c r="S93" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T93" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U93" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V93" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O93" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Luz</v>
-      </c>
-      <c r="P93" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q93" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="R93" s="30" t="s">
-        <v>535</v>
-      </c>
-      <c r="S93" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T93" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U93" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V93" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W93" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X93" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-93</v>
       </c>
       <c r="Y93" s="30" t="s">
@@ -13180,50 +13267,50 @@
         <v>9</v>
       </c>
       <c r="L94" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M94" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N94" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O94" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Umidade do Solo</v>
+      </c>
+      <c r="P94" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q94" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="R94" s="30" t="s">
+        <v>536</v>
+      </c>
+      <c r="S94" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T94" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U94" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V94" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O94" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Umidade do Solo</v>
-      </c>
-      <c r="P94" s="30" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q94" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="R94" s="30" t="s">
-        <v>536</v>
-      </c>
-      <c r="S94" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T94" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U94" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V94" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W94" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X94" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-94</v>
       </c>
       <c r="Y94" s="30" t="s">
@@ -13280,50 +13367,50 @@
         <v>9</v>
       </c>
       <c r="L95" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M95" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N95" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O95" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Movimento</v>
+      </c>
+      <c r="P95" s="30" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q95" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="R95" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="S95" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T95" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U95" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V95" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O95" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Movimento</v>
-      </c>
-      <c r="P95" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="Q95" s="30" t="s">
-        <v>292</v>
-      </c>
-      <c r="R95" s="30" t="s">
-        <v>537</v>
-      </c>
-      <c r="S95" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T95" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U95" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V95" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W95" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X95" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-95</v>
       </c>
       <c r="Y95" s="30" t="s">
@@ -13380,50 +13467,50 @@
         <v>9</v>
       </c>
       <c r="L96" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M96" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N96" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O96" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Obstáculo</v>
+      </c>
+      <c r="P96" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q96" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="R96" s="30" t="s">
+        <v>538</v>
+      </c>
+      <c r="S96" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T96" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U96" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V96" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O96" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Obstáculo</v>
-      </c>
-      <c r="P96" s="30" t="s">
-        <v>421</v>
-      </c>
-      <c r="Q96" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="R96" s="30" t="s">
-        <v>538</v>
-      </c>
-      <c r="S96" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T96" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U96" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V96" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W96" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X96" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-96</v>
       </c>
       <c r="Y96" s="30" t="s">
@@ -13480,50 +13567,50 @@
         <v>9</v>
       </c>
       <c r="L97" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M97" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N97" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O97" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de pH</v>
+      </c>
+      <c r="P97" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q97" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="R97" s="30" t="s">
+        <v>539</v>
+      </c>
+      <c r="S97" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T97" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U97" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V97" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O97" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de pH</v>
-      </c>
-      <c r="P97" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="Q97" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="R97" s="30" t="s">
-        <v>539</v>
-      </c>
-      <c r="S97" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T97" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U97" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V97" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W97" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X97" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-97</v>
       </c>
       <c r="Y97" s="30" t="s">
@@ -13580,50 +13667,50 @@
         <v>9</v>
       </c>
       <c r="L98" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M98" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N98" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O98" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Pressão</v>
+      </c>
+      <c r="P98" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q98" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="R98" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="S98" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T98" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U98" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V98" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O98" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Pressão</v>
-      </c>
-      <c r="P98" s="30" t="s">
-        <v>422</v>
-      </c>
-      <c r="Q98" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="R98" s="30" t="s">
-        <v>540</v>
-      </c>
-      <c r="S98" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T98" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U98" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V98" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W98" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X98" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-98</v>
       </c>
       <c r="Y98" s="30" t="s">
@@ -13680,50 +13767,50 @@
         <v>9</v>
       </c>
       <c r="L99" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M99" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N99" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O99" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Radiação</v>
+      </c>
+      <c r="P99" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q99" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="R99" s="30" t="s">
+        <v>541</v>
+      </c>
+      <c r="S99" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T99" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U99" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V99" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O99" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Radiação</v>
-      </c>
-      <c r="P99" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q99" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="R99" s="30" t="s">
-        <v>541</v>
-      </c>
-      <c r="S99" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T99" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U99" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V99" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W99" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X99" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-99</v>
       </c>
       <c r="Y99" s="30" t="s">
@@ -13780,50 +13867,50 @@
         <v>9</v>
       </c>
       <c r="L100" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M100" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N100" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O100" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Radioatividade</v>
+      </c>
+      <c r="P100" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q100" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="R100" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="S100" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T100" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U100" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V100" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O100" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Radioatividade</v>
-      </c>
-      <c r="P100" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="Q100" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="R100" s="30" t="s">
-        <v>542</v>
-      </c>
-      <c r="S100" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T100" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U100" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V100" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W100" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X100" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-100</v>
       </c>
       <c r="Y100" s="30" t="s">
@@ -13880,50 +13967,50 @@
         <v>9</v>
       </c>
       <c r="L101" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M101" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N101" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O101" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Chuva</v>
+      </c>
+      <c r="P101" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q101" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="R101" s="30" t="s">
+        <v>543</v>
+      </c>
+      <c r="S101" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T101" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U101" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V101" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O101" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Chuva</v>
-      </c>
-      <c r="P101" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q101" s="30" t="s">
-        <v>298</v>
-      </c>
-      <c r="R101" s="30" t="s">
-        <v>543</v>
-      </c>
-      <c r="S101" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T101" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U101" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V101" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W101" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X101" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-101</v>
       </c>
       <c r="Y101" s="30" t="s">
@@ -13980,50 +14067,50 @@
         <v>9</v>
       </c>
       <c r="L102" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M102" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N102" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O102" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Fumaça</v>
+      </c>
+      <c r="P102" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q102" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="R102" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="S102" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T102" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U102" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V102" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O102" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Fumaça</v>
-      </c>
-      <c r="P102" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q102" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="R102" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="S102" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T102" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U102" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V102" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W102" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X102" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-102</v>
       </c>
       <c r="Y102" s="30" t="s">
@@ -14080,50 +14167,50 @@
         <v>9</v>
       </c>
       <c r="L103" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M103" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N103" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O103" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Profundidade da Neve</v>
+      </c>
+      <c r="P103" s="30" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q103" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="R103" s="30" t="s">
+        <v>545</v>
+      </c>
+      <c r="S103" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T103" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U103" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V103" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O103" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Profundidade da Neve</v>
-      </c>
-      <c r="P103" s="30" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q103" s="30" t="s">
-        <v>300</v>
-      </c>
-      <c r="R103" s="30" t="s">
-        <v>545</v>
-      </c>
-      <c r="S103" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T103" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U103" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V103" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W103" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X103" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-103</v>
       </c>
       <c r="Y103" s="30" t="s">
@@ -14180,50 +14267,50 @@
         <v>9</v>
       </c>
       <c r="L104" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M104" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N104" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O104" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Som</v>
+      </c>
+      <c r="P104" s="30" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q104" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="R104" s="30" t="s">
+        <v>546</v>
+      </c>
+      <c r="S104" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T104" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U104" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V104" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O104" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Som</v>
-      </c>
-      <c r="P104" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q104" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="R104" s="30" t="s">
-        <v>546</v>
-      </c>
-      <c r="S104" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T104" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U104" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V104" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W104" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X104" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-104</v>
       </c>
       <c r="Y104" s="30" t="s">
@@ -14280,50 +14367,50 @@
         <v>9</v>
       </c>
       <c r="L105" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M105" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N105" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O105" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Temperatura</v>
+      </c>
+      <c r="P105" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q105" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="R105" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="S105" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T105" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U105" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V105" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O105" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Temperatura</v>
-      </c>
-      <c r="P105" s="30" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q105" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="R105" s="30" t="s">
-        <v>547</v>
-      </c>
-      <c r="S105" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T105" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U105" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V105" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W105" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X105" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-105</v>
       </c>
       <c r="Y105" s="30" t="s">
@@ -14380,50 +14467,50 @@
         <v>9</v>
       </c>
       <c r="L106" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M106" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N106" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O106" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Trem</v>
+      </c>
+      <c r="P106" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q106" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="R106" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="S106" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T106" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U106" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V106" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O106" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Trem</v>
-      </c>
-      <c r="P106" s="30" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q106" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="R106" s="30" t="s">
-        <v>548</v>
-      </c>
-      <c r="S106" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T106" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U106" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V106" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W106" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X106" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-106</v>
       </c>
       <c r="Y106" s="30" t="s">
@@ -14480,50 +14567,50 @@
         <v>9</v>
       </c>
       <c r="L107" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M107" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N107" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O107" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Desvio Ferroviário</v>
+      </c>
+      <c r="P107" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q107" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="R107" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="S107" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T107" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U107" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V107" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O107" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Desvio Ferroviário</v>
-      </c>
-      <c r="P107" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q107" s="30" t="s">
-        <v>304</v>
-      </c>
-      <c r="R107" s="30" t="s">
-        <v>549</v>
-      </c>
-      <c r="S107" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T107" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U107" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V107" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W107" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X107" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-107</v>
       </c>
       <c r="Y107" s="30" t="s">
@@ -14580,50 +14667,50 @@
         <v>9</v>
       </c>
       <c r="L108" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M108" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N108" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O108" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Roda</v>
+      </c>
+      <c r="P108" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q108" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="R108" s="30" t="s">
+        <v>550</v>
+      </c>
+      <c r="S108" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T108" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U108" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V108" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O108" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Roda</v>
-      </c>
-      <c r="P108" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q108" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="R108" s="30" t="s">
-        <v>550</v>
-      </c>
-      <c r="S108" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T108" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U108" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V108" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W108" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X108" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-108</v>
       </c>
       <c r="Y108" s="30" t="s">
@@ -14680,50 +14767,50 @@
         <v>9</v>
       </c>
       <c r="L109" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M109" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N109" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O109" s="35" t="str">
+        <f t="shared" si="22"/>
+        <v>Avac Sensor de Vento</v>
+      </c>
+      <c r="P109" s="30" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q109" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="R109" s="30" t="s">
+        <v>551</v>
+      </c>
+      <c r="S109" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T109" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De AVAC</v>
+      </c>
+      <c r="U109" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="V109" s="30" t="str">
         <f t="shared" si="21"/>
         <v>Avac Sensores</v>
       </c>
-      <c r="O109" s="35" t="str">
-        <f t="shared" si="21"/>
-        <v>Avac Sensor de Vento</v>
-      </c>
-      <c r="P109" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q109" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="R109" s="30" t="s">
-        <v>551</v>
-      </c>
-      <c r="S109" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T109" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De AVAC</v>
-      </c>
-      <c r="U109" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Elementos de Sensorização</v>
-      </c>
-      <c r="V109" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>Avac Sensores</v>
-      </c>
       <c r="W109" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X109" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-109</v>
       </c>
       <c r="Y109" s="30" t="s">
@@ -14780,15 +14867,15 @@
         <v>9</v>
       </c>
       <c r="L110" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M110" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Acessórios</v>
       </c>
       <c r="N110" s="35" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>Avac Acessórios</v>
       </c>
       <c r="O110" s="30" t="str">
@@ -14808,22 +14895,22 @@
         <v>9</v>
       </c>
       <c r="T110" s="30" t="str">
-        <f t="shared" ref="T110:V111" si="23">SUBSTITUTE(C110, "_", " ")</f>
+        <f t="shared" ref="T110:V111" si="24">SUBSTITUTE(C110, "_", " ")</f>
         <v>De.AVAC</v>
       </c>
       <c r="U110" s="30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>Elementos.de.Acessórios</v>
       </c>
       <c r="V110" s="30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>Avac.Acessórios</v>
       </c>
       <c r="W110" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X110" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-110</v>
       </c>
       <c r="Y110" s="30" t="s">
@@ -14880,19 +14967,19 @@
         <v>9</v>
       </c>
       <c r="L111" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>De.AVAC</v>
       </c>
       <c r="M111" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Elementos.de.Acessórios</v>
       </c>
       <c r="N111" s="35" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>Avac Acessórios</v>
       </c>
       <c r="O111" s="30" t="str">
-        <f t="shared" ref="O111" si="24">IF(ISNUMBER(FIND("Ifc",F111)),CONCATENATE("",F111),CONCATENATE("",F111))</f>
+        <f t="shared" ref="O111" si="25">IF(ISNUMBER(FIND("Ifc",F111)),CONCATENATE("",F111),CONCATENATE("",F111))</f>
         <v>Avac.Acessório.Tubo.Avac</v>
       </c>
       <c r="P111" s="30" t="s">
@@ -14908,22 +14995,22 @@
         <v>9</v>
       </c>
       <c r="T111" s="30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>De.AVAC</v>
       </c>
       <c r="U111" s="30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>Elementos.de.Acessórios</v>
       </c>
       <c r="V111" s="30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>Avac.Acessórios</v>
       </c>
       <c r="W111" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X111" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-111</v>
       </c>
       <c r="Y111" s="30" t="s">
@@ -14980,31 +15067,30 @@
         <v>9</v>
       </c>
       <c r="L112" s="35" t="str">
-        <f t="shared" ref="L112:O113" si="25">SUBSTITUTE(CONCATENATE("", C112), ".", " ")</f>
+        <f t="shared" ref="L112:O113" si="26">SUBSTITUTE(CONCATENATE("", C112), ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="M112" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N112" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="O112" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Ar Aquecido</v>
       </c>
       <c r="P112" s="30" t="s">
         <v>571</v>
       </c>
       <c r="Q112" s="56" t="str">
-        <f t="shared" ref="Q112:Q113" si="26">_xlfn.TRANSLATE(P112,"pt","es")</f>
+        <f t="shared" ref="Q112:Q113" si="27">_xlfn.TRANSLATE(P112,"pt","es")</f>
         <v>Proyecto de instalación de calefacción de aire.</v>
       </c>
-      <c r="R112" s="56" t="str">
-        <f t="shared" ref="R112:R113" si="27">_xlfn.TRANSLATE(P112,"pt","en")</f>
-        <v>Air heating installation project.</v>
+      <c r="R112" s="56" t="s">
+        <v>741</v>
       </c>
       <c r="S112" s="30" t="s">
         <v>9</v>
@@ -15082,31 +15168,30 @@
         <v>9</v>
       </c>
       <c r="L113" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>De Climatização</v>
       </c>
       <c r="M113" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N113" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="O113" s="35" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Ar Insuflado</v>
       </c>
       <c r="P113" s="30" t="s">
         <v>577</v>
       </c>
       <c r="Q113" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>Proyecto de instalación de refrigeración por aire (inflado).</v>
       </c>
-      <c r="R113" s="56" t="str">
-        <f t="shared" si="27"/>
-        <v>Air cooling installation project (Inflated).</v>
+      <c r="R113" s="56" t="s">
+        <v>742</v>
       </c>
       <c r="S113" s="30" t="s">
         <v>9</v>
@@ -15206,30 +15291,29 @@
         <f t="shared" ref="Q114:Q117" si="34">_xlfn.TRANSLATE(P114,"pt","es")</f>
         <v>Proyecto de instalación de refrigeración por aire (Retorno).</v>
       </c>
-      <c r="R114" s="56" t="str">
-        <f t="shared" ref="R114:R117" si="35">_xlfn.TRANSLATE(P114,"pt","en")</f>
-        <v>Air Cooling Installation Project (Return).</v>
+      <c r="R114" s="56" t="s">
+        <v>743</v>
       </c>
       <c r="S114" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T114" s="30" t="str">
-        <f t="shared" ref="T114:T117" si="36">SUBSTITUTE(C114, ".", " ")</f>
+        <f t="shared" ref="T114:T117" si="35">SUBSTITUTE(C114, ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="U114" s="30" t="str">
-        <f t="shared" ref="U114:U117" si="37">SUBSTITUTE(D114, ".", " ")</f>
+        <f t="shared" ref="U114:U117" si="36">SUBSTITUTE(D114, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="V114" s="57" t="str">
-        <f t="shared" ref="V114:V117" si="38">SUBSTITUTE(E114, ".", " ")</f>
+        <f t="shared" ref="V114:V117" si="37">SUBSTITUTE(E114, ".", " ")</f>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="W114" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X114" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-114</v>
       </c>
       <c r="Y114" s="58" t="s">
@@ -15308,30 +15392,29 @@
         <f t="shared" si="34"/>
         <v>Proyecto de instalación de escapes mecánicos.</v>
       </c>
-      <c r="R115" s="56" t="str">
+      <c r="R115" s="56" t="s">
+        <v>744</v>
+      </c>
+      <c r="S115" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T115" s="30" t="str">
         <f t="shared" si="35"/>
-        <v>Mechanical exhaust installation project.</v>
-      </c>
-      <c r="S115" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T115" s="30" t="str">
+        <v>De Climatização</v>
+      </c>
+      <c r="U115" s="30" t="str">
         <f t="shared" si="36"/>
-        <v>De Climatização</v>
-      </c>
-      <c r="U115" s="30" t="str">
+        <v>Qualidade de Ar</v>
+      </c>
+      <c r="V115" s="57" t="str">
         <f t="shared" si="37"/>
-        <v>Qualidade de Ar</v>
-      </c>
-      <c r="V115" s="57" t="str">
-        <f t="shared" si="38"/>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="W115" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X115" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-115</v>
       </c>
       <c r="Y115" s="58" t="s">
@@ -15388,52 +15471,51 @@
         <v>9</v>
       </c>
       <c r="L116" s="35" t="str">
-        <f t="shared" ref="L116" si="39">SUBSTITUTE(CONCATENATE("", C116), ".", " ")</f>
+        <f t="shared" ref="L116" si="38">SUBSTITUTE(CONCATENATE("", C116), ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="M116" s="35" t="str">
-        <f t="shared" ref="M116" si="40">SUBSTITUTE(CONCATENATE("", D116), ".", " ")</f>
+        <f t="shared" ref="M116" si="39">SUBSTITUTE(CONCATENATE("", D116), ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N116" s="35" t="str">
-        <f t="shared" ref="N116" si="41">SUBSTITUTE(CONCATENATE("", E116), ".", " ")</f>
+        <f t="shared" ref="N116" si="40">SUBSTITUTE(CONCATENATE("", E116), ".", " ")</f>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="O116" s="35" t="str">
-        <f t="shared" ref="O116" si="42">SUBSTITUTE(CONCATENATE("", F116), ".", " ")</f>
+        <f t="shared" ref="O116" si="41">SUBSTITUTE(CONCATENATE("", F116), ".", " ")</f>
         <v>Ar Ventilação</v>
       </c>
       <c r="P116" s="30" t="s">
         <v>572</v>
       </c>
       <c r="Q116" s="56" t="str">
-        <f t="shared" ref="Q116" si="43">_xlfn.TRANSLATE(P116,"pt","es")</f>
+        <f t="shared" ref="Q116" si="42">_xlfn.TRANSLATE(P116,"pt","es")</f>
         <v>Proyecto de instalación de ventilación del aire interior.</v>
       </c>
-      <c r="R116" s="56" t="str">
-        <f t="shared" ref="R116" si="44">_xlfn.TRANSLATE(P116,"pt","en")</f>
-        <v>Indoor air ventilation installation project.</v>
+      <c r="R116" s="56" t="s">
+        <v>745</v>
       </c>
       <c r="S116" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T116" s="30" t="str">
-        <f t="shared" ref="T116" si="45">SUBSTITUTE(C116, ".", " ")</f>
+        <f t="shared" ref="T116" si="43">SUBSTITUTE(C116, ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="U116" s="30" t="str">
-        <f t="shared" ref="U116" si="46">SUBSTITUTE(D116, ".", " ")</f>
+        <f t="shared" ref="U116" si="44">SUBSTITUTE(D116, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="V116" s="57" t="str">
-        <f t="shared" ref="V116" si="47">SUBSTITUTE(E116, ".", " ")</f>
+        <f t="shared" ref="V116" si="45">SUBSTITUTE(E116, ".", " ")</f>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="W116" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X116" s="48" t="str">
-        <f t="shared" ref="X116" si="48">CONCATENATE("Key-AVAC-",A116)</f>
+        <f t="shared" ref="X116" si="46">CONCATENATE("Key-AVAC-",A116)</f>
         <v>Key-AVAC-116</v>
       </c>
       <c r="Y116" s="58" t="s">
@@ -15512,30 +15594,29 @@
         <f t="shared" si="34"/>
         <v>Proyecto de instalación de filtración de aire interior.</v>
       </c>
-      <c r="R117" s="56" t="str">
+      <c r="R117" s="56" t="s">
+        <v>746</v>
+      </c>
+      <c r="S117" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T117" s="30" t="str">
         <f t="shared" si="35"/>
-        <v>Indoor air filtration installation project.</v>
-      </c>
-      <c r="S117" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T117" s="30" t="str">
+        <v>De Climatização</v>
+      </c>
+      <c r="U117" s="30" t="str">
         <f t="shared" si="36"/>
-        <v>De Climatização</v>
-      </c>
-      <c r="U117" s="30" t="str">
+        <v>Qualidade de Ar</v>
+      </c>
+      <c r="V117" s="57" t="str">
         <f t="shared" si="37"/>
-        <v>Qualidade de Ar</v>
-      </c>
-      <c r="V117" s="57" t="str">
-        <f t="shared" si="38"/>
         <v>Circulação de Ar Interior</v>
       </c>
       <c r="W117" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X117" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>Key-AVAC-117</v>
       </c>
       <c r="Y117" s="58" t="s">
@@ -15592,52 +15673,51 @@
         <v>9</v>
       </c>
       <c r="L118" s="35" t="str">
-        <f t="shared" ref="L118" si="49">SUBSTITUTE(CONCATENATE("", C118), ".", " ")</f>
+        <f t="shared" ref="L118" si="47">SUBSTITUTE(CONCATENATE("", C118), ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="M118" s="35" t="str">
-        <f t="shared" ref="M118" si="50">SUBSTITUTE(CONCATENATE("", D118), ".", " ")</f>
+        <f t="shared" ref="M118" si="48">SUBSTITUTE(CONCATENATE("", D118), ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N118" s="35" t="str">
-        <f t="shared" ref="N118" si="51">SUBSTITUTE(CONCATENATE("", E118), ".", " ")</f>
+        <f t="shared" ref="N118" si="49">SUBSTITUTE(CONCATENATE("", E118), ".", " ")</f>
         <v>Captação de Ar Exterior</v>
       </c>
       <c r="O118" s="35" t="str">
-        <f t="shared" ref="O118" si="52">SUBSTITUTE(CONCATENATE("", F118), ".", " ")</f>
+        <f t="shared" ref="O118" si="50">SUBSTITUTE(CONCATENATE("", F118), ".", " ")</f>
         <v>Ar Filtrado Externo</v>
       </c>
       <c r="P118" s="30" t="s">
         <v>573</v>
       </c>
       <c r="Q118" s="56" t="str">
-        <f t="shared" ref="Q118" si="53">_xlfn.TRANSLATE(P118,"pt","es")</f>
+        <f t="shared" ref="Q118" si="51">_xlfn.TRANSLATE(P118,"pt","es")</f>
         <v>Proyecto de instalación de filtración de aire exterior.</v>
       </c>
-      <c r="R118" s="56" t="str">
-        <f t="shared" ref="R118" si="54">_xlfn.TRANSLATE(P118,"pt","en")</f>
-        <v>Outdoor air filtration installation project.</v>
+      <c r="R118" s="56" t="s">
+        <v>747</v>
       </c>
       <c r="S118" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T118" s="30" t="str">
-        <f t="shared" ref="T118" si="55">SUBSTITUTE(C118, ".", " ")</f>
+        <f t="shared" ref="T118" si="52">SUBSTITUTE(C118, ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="U118" s="30" t="str">
-        <f t="shared" ref="U118" si="56">SUBSTITUTE(D118, ".", " ")</f>
+        <f t="shared" ref="U118" si="53">SUBSTITUTE(D118, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="V118" s="57" t="str">
-        <f t="shared" ref="V118" si="57">SUBSTITUTE(E118, ".", " ")</f>
+        <f t="shared" ref="V118" si="54">SUBSTITUTE(E118, ".", " ")</f>
         <v>Captação de Ar Exterior</v>
       </c>
       <c r="W118" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X118" s="48" t="str">
-        <f t="shared" ref="X118:X124" si="58">CONCATENATE("Key-AVAC-",A118)</f>
+        <f t="shared" ref="X118:X124" si="55">CONCATENATE("Key-AVAC-",A118)</f>
         <v>Key-AVAC-118</v>
       </c>
       <c r="Y118" s="58" t="s">
@@ -15694,52 +15774,51 @@
         <v>9</v>
       </c>
       <c r="L119" s="35" t="str">
-        <f t="shared" ref="L119:O124" si="59">SUBSTITUTE(CONCATENATE("", C119), ".", " ")</f>
+        <f t="shared" ref="L119:O124" si="56">SUBSTITUTE(CONCATENATE("", C119), ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="M119" s="35" t="str">
-        <f t="shared" ref="M119" si="60">SUBSTITUTE(CONCATENATE("", D119), ".", " ")</f>
+        <f t="shared" ref="M119" si="57">SUBSTITUTE(CONCATENATE("", D119), ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="N119" s="35" t="str">
-        <f t="shared" ref="N119" si="61">SUBSTITUTE(CONCATENATE("", E119), ".", " ")</f>
+        <f t="shared" ref="N119" si="58">SUBSTITUTE(CONCATENATE("", E119), ".", " ")</f>
         <v>Captação de Ar Exterior</v>
       </c>
       <c r="O119" s="35" t="str">
-        <f t="shared" ref="O119" si="62">SUBSTITUTE(CONCATENATE("", F119), ".", " ")</f>
+        <f t="shared" ref="O119" si="59">SUBSTITUTE(CONCATENATE("", F119), ".", " ")</f>
         <v>Ar Captador</v>
       </c>
       <c r="P119" s="30" t="s">
         <v>580</v>
       </c>
       <c r="Q119" s="56" t="str">
-        <f t="shared" ref="Q119" si="63">_xlfn.TRANSLATE(P119,"pt","es")</f>
+        <f t="shared" ref="Q119" si="60">_xlfn.TRANSLATE(P119,"pt","es")</f>
         <v>Proyecto de instalación de la toma de aire exterior.</v>
       </c>
-      <c r="R119" s="56" t="str">
-        <f t="shared" ref="R119" si="64">_xlfn.TRANSLATE(P119,"pt","en")</f>
-        <v>Outdoor air intake installation project.</v>
+      <c r="R119" s="56" t="s">
+        <v>748</v>
       </c>
       <c r="S119" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T119" s="30" t="str">
-        <f t="shared" ref="T119:V124" si="65">SUBSTITUTE(C119, ".", " ")</f>
+        <f t="shared" ref="T119:V124" si="61">SUBSTITUTE(C119, ".", " ")</f>
         <v>De Climatização</v>
       </c>
       <c r="U119" s="30" t="str">
-        <f t="shared" ref="U119" si="66">SUBSTITUTE(D119, ".", " ")</f>
+        <f t="shared" ref="U119" si="62">SUBSTITUTE(D119, ".", " ")</f>
         <v>Qualidade de Ar</v>
       </c>
       <c r="V119" s="57" t="str">
-        <f t="shared" ref="V119" si="67">SUBSTITUTE(E119, ".", " ")</f>
+        <f t="shared" ref="V119" si="63">SUBSTITUTE(E119, ".", " ")</f>
         <v>Captação de Ar Exterior</v>
       </c>
       <c r="W119" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X119" s="48" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>Key-AVAC-119</v>
       </c>
       <c r="Y119" s="58" t="s">
@@ -15796,19 +15875,19 @@
         <v>9</v>
       </c>
       <c r="L120" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>De API</v>
       </c>
       <c r="M120" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
       <c r="N120" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Métodos</v>
       </c>
       <c r="O120" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Função Auxiliar</v>
       </c>
       <c r="P120" s="30" t="s">
@@ -15824,22 +15903,22 @@
         <v>9</v>
       </c>
       <c r="T120" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>De API</v>
       </c>
       <c r="U120" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Macros</v>
       </c>
       <c r="V120" s="57" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Métodos</v>
       </c>
       <c r="W120" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X120" s="48" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>Key-AVAC-120</v>
       </c>
       <c r="Y120" s="58" t="s">
@@ -15896,19 +15975,19 @@
         <v>9</v>
       </c>
       <c r="L121" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>De API</v>
       </c>
       <c r="M121" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
       <c r="N121" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Métodos</v>
       </c>
       <c r="O121" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Função Global</v>
       </c>
       <c r="P121" s="30" t="s">
@@ -15924,22 +16003,22 @@
         <v>9</v>
       </c>
       <c r="T121" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>De API</v>
       </c>
       <c r="U121" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Macros</v>
       </c>
       <c r="V121" s="57" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Métodos</v>
       </c>
       <c r="W121" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X121" s="48" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>Key-AVAC-121</v>
       </c>
       <c r="Y121" s="58" t="s">
@@ -15996,19 +16075,19 @@
         <v>9</v>
       </c>
       <c r="L122" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>De API</v>
       </c>
       <c r="M122" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
       <c r="N122" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Métodos</v>
       </c>
       <c r="O122" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Função Local</v>
       </c>
       <c r="P122" s="30" t="s">
@@ -16024,22 +16103,22 @@
         <v>9</v>
       </c>
       <c r="T122" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>De API</v>
       </c>
       <c r="U122" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Macros</v>
       </c>
       <c r="V122" s="57" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Métodos</v>
       </c>
       <c r="W122" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X122" s="48" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>Key-AVAC-122</v>
       </c>
       <c r="Y122" s="58" t="s">
@@ -16096,19 +16175,19 @@
         <v>9</v>
       </c>
       <c r="L123" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>De API</v>
       </c>
       <c r="M123" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
       <c r="N123" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Métodos</v>
       </c>
       <c r="O123" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Função Filtro</v>
       </c>
       <c r="P123" s="30" t="s">
@@ -16124,22 +16203,22 @@
         <v>9</v>
       </c>
       <c r="T123" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>De API</v>
       </c>
       <c r="U123" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Macros</v>
       </c>
       <c r="V123" s="57" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Métodos</v>
       </c>
       <c r="W123" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X123" s="48" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>Key-AVAC-123</v>
       </c>
       <c r="Y123" s="58" t="s">
@@ -16196,19 +16275,19 @@
         <v>9</v>
       </c>
       <c r="L124" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>De API</v>
       </c>
       <c r="M124" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
       <c r="N124" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Códigos Visuais</v>
       </c>
       <c r="O124" s="35" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v>Bloco de Código</v>
       </c>
       <c r="P124" s="30" t="s">
@@ -16224,22 +16303,22 @@
         <v>9</v>
       </c>
       <c r="T124" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>De API</v>
       </c>
       <c r="U124" s="30" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Macros</v>
       </c>
       <c r="V124" s="57" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>Códigos Visuais</v>
       </c>
       <c r="W124" s="30" t="s">
         <v>209</v>
       </c>
       <c r="X124" s="48" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>Key-AVAC-124</v>
       </c>
       <c r="Y124" s="58" t="s">
@@ -16294,7 +16373,7 @@
     <cfRule type="duplicateValues" dxfId="20" priority="2413"/>
     <cfRule type="duplicateValues" dxfId="19" priority="2414"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R28 Y2:Y28 AA2:AA28 AC2:AC28">
+  <conditionalFormatting sqref="R1:R10 Y2:Y28 AA2:AA28 AC2:AC28">
     <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
